--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC31A818-C5BE-4E9D-990E-23DC2AA19079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC7C175-55D7-4227-AB39-591AE2A3CEC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -326,10 +326,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>コンパス</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>TestMysteryItem02</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -367,6 +363,13 @@
   </si>
   <si>
     <t>Tutorial</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンパス。Compass.csでも使用する。</t>
+    <rPh sb="17" eb="19">
+      <t>シヨウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1111,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P9">
         <v>14</v>
@@ -1387,7 +1390,7 @@
         <v>54</v>
       </c>
       <c r="L14" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M14" s="1">
         <v>1</v>
@@ -1405,10 +1408,10 @@
         <v>56</v>
       </c>
       <c r="R14" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="56.25">
@@ -6506,13 +6509,13 @@
         <v>0</v>
       </c>
       <c r="I998" t="s">
+        <v>66</v>
+      </c>
+      <c r="J998">
+        <v>14</v>
+      </c>
+      <c r="K998" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="J998">
-        <v>14</v>
-      </c>
-      <c r="K998" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="L998">
         <v>14</v>
@@ -6524,19 +6527,19 @@
         <v>0</v>
       </c>
       <c r="O998" t="s">
+        <v>66</v>
+      </c>
+      <c r="P998">
+        <v>14</v>
+      </c>
+      <c r="Q998" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="P998">
-        <v>14</v>
-      </c>
-      <c r="Q998" s="1" t="s">
+      <c r="R998">
+        <v>14</v>
+      </c>
+      <c r="S998" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="R998">
-        <v>14</v>
-      </c>
-      <c r="S998" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="999" spans="1:19" ht="75">
@@ -6562,13 +6565,13 @@
         <v>0</v>
       </c>
       <c r="I999" t="s">
+        <v>69</v>
+      </c>
+      <c r="J999">
+        <v>14</v>
+      </c>
+      <c r="K999" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="J999">
-        <v>14</v>
-      </c>
-      <c r="K999" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="L999">
         <v>14</v>
@@ -6580,19 +6583,19 @@
         <v>0</v>
       </c>
       <c r="O999" t="s">
+        <v>69</v>
+      </c>
+      <c r="P999">
+        <v>14</v>
+      </c>
+      <c r="Q999" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="P999">
-        <v>14</v>
-      </c>
-      <c r="Q999" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="R999">
         <v>14</v>
       </c>
       <c r="S999" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1000" spans="1:19" ht="75">
@@ -6618,13 +6621,13 @@
         <v>0</v>
       </c>
       <c r="I1000" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J1000">
+        <v>14</v>
+      </c>
+      <c r="K1000" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="J1000">
-        <v>14</v>
-      </c>
-      <c r="K1000" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="L1000">
         <v>14</v>
@@ -6636,19 +6639,19 @@
         <v>0</v>
       </c>
       <c r="O1000" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P1000">
+        <v>14</v>
+      </c>
+      <c r="Q1000" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="P1000">
-        <v>14</v>
-      </c>
-      <c r="Q1000" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="R1000">
         <v>14</v>
       </c>
       <c r="S1000" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1001" spans="1:19">
@@ -6674,13 +6677,13 @@
         <v>0</v>
       </c>
       <c r="I1001" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1001">
+        <v>14</v>
+      </c>
+      <c r="K1001" t="s">
         <v>72</v>
-      </c>
-      <c r="J1001">
-        <v>14</v>
-      </c>
-      <c r="K1001" t="s">
-        <v>73</v>
       </c>
       <c r="L1001">
         <v>14</v>
@@ -6692,13 +6695,13 @@
         <v>0</v>
       </c>
       <c r="O1001" t="s">
+        <v>71</v>
+      </c>
+      <c r="P1001">
+        <v>14</v>
+      </c>
+      <c r="Q1001" t="s">
         <v>72</v>
-      </c>
-      <c r="P1001">
-        <v>14</v>
-      </c>
-      <c r="Q1001" t="s">
-        <v>73</v>
       </c>
       <c r="R1001">
         <v>14</v>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC7C175-55D7-4227-AB39-591AE2A3CEC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BABCE31-EE4F-4D2E-BCB3-F50693D31A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="80">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -370,6 +370,17 @@
     <rPh sb="17" eb="19">
       <t>シヨウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dammy</t>
+  </si>
+  <si>
+    <t>Dammy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DammyItem</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -838,7 +849,7 @@
         <v>22</v>
       </c>
       <c r="R3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>26</v>
@@ -6713,6 +6724,51 @@
     <row r="1002" spans="1:19">
       <c r="A1002">
         <v>1000</v>
+      </c>
+      <c r="C1002">
+        <v>0</v>
+      </c>
+      <c r="D1002">
+        <v>0</v>
+      </c>
+      <c r="E1002">
+        <v>0</v>
+      </c>
+      <c r="F1002">
+        <v>0</v>
+      </c>
+      <c r="G1002">
+        <v>0</v>
+      </c>
+      <c r="H1002">
+        <v>0</v>
+      </c>
+      <c r="I1002" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1002">
+        <v>0</v>
+      </c>
+      <c r="K1002" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L1002">
+        <v>0</v>
+      </c>
+      <c r="M1002">
+        <v>0</v>
+      </c>
+      <c r="N1002">
+        <v>0</v>
+      </c>
+      <c r="O1002" t="s">
+        <v>77</v>
+      </c>
+      <c r="P1002">
+        <v>0</v>
+      </c>
+      <c r="Q1002" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BABCE31-EE4F-4D2E-BCB3-F50693D31A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F37F1EC-07B6-4A40-B0DA-ECBF2E646D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="85">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -381,6 +381,32 @@
   </si>
   <si>
     <t>DammyItem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Miniature hospital bed</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"Disease" is inscribed on the back of the miniature.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>病院のベッドの模型</t>
+    <rPh sb="7" eb="9">
+      <t>モケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>模型の裏側には「病」と記載されている。</t>
+    <rPh sb="0" eb="2">
+      <t>モケイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -722,7 +748,7 @@
     <col min="6" max="6" width="15.125" customWidth="1"/>
     <col min="7" max="7" width="14.875" customWidth="1"/>
     <col min="8" max="8" width="15.5" customWidth="1"/>
-    <col min="9" max="9" width="17.125" customWidth="1"/>
+    <col min="9" max="9" width="26.75" customWidth="1"/>
     <col min="10" max="10" width="21.375" customWidth="1"/>
     <col min="11" max="11" width="22.375" customWidth="1"/>
     <col min="12" max="12" width="26.25" customWidth="1"/>
@@ -1470,14 +1496,62 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" ht="56.25">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" t="s">
+        <v>83</v>
+      </c>
+      <c r="J16" s="1">
+        <v>14</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L16" s="1">
+        <v>14</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P16" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="R16" s="1">
+        <v>14</v>
+      </c>
+      <c r="S16" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F37F1EC-07B6-4A40-B0DA-ECBF2E646D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67704636-BC6F-419E-BD94-C3C4975D215E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="89">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -407,6 +407,22 @@
     <rPh sb="0" eb="2">
       <t>モケイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>踏切の模型</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>模型の裏側には「轢」と記載されている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Miniature railroad crossing</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"Run-over" is inscribed on the back of the miniature.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1553,21 +1569,69 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:19" ht="56.25">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" t="s">
+        <v>85</v>
+      </c>
+      <c r="J17" s="1">
+        <v>14</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L17" s="1">
+        <v>14</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P17" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="R17" s="1">
+        <v>14</v>
+      </c>
+      <c r="S17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1576,67 +1640,67 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:19">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:19">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:19">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:19">
       <c r="A32">
         <v>30</v>
       </c>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67704636-BC6F-419E-BD94-C3C4975D215E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35532058-9F5A-4652-803F-A58CC445859A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="93">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -423,6 +423,22 @@
   </si>
   <si>
     <t>"Run-over" is inscribed on the back of the miniature.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>崩れたビルの模型</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>模型の裏側には「圧」と記載されている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Miniature of a collapsed building</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"Crushing" is inscribed on the back of the miniature.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1626,9 +1642,60 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" ht="56.25">
       <c r="A18">
         <v>16</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18" t="s">
+        <v>89</v>
+      </c>
+      <c r="J18" s="1">
+        <v>14</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L18" s="1">
+        <v>14</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="P18" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="R18" s="1">
+        <v>14</v>
+      </c>
+      <c r="S18" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:19">

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35532058-9F5A-4652-803F-A58CC445859A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDE792F-71D0-42FC-8F05-378564F0FF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="97">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -439,6 +439,22 @@
   </si>
   <si>
     <t>"Crushing" is inscribed on the back of the miniature.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>暖炉の模型</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>模型の裏側には「焼」と記載されている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Miniature fireplace</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"Burning" is inscribed on the back of the miniature.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1698,14 +1714,62 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" t="s">
+        <v>93</v>
+      </c>
+      <c r="J19" s="1">
+        <v>14</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L19" s="1">
+        <v>14</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="P19" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="R19" s="1">
+        <v>14</v>
+      </c>
+      <c r="S19" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20">

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDE792F-71D0-42FC-8F05-378564F0FF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBA35B7-96E1-4F0F-84C4-FB016A4B2F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="101">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -455,6 +455,22 @@
   </si>
   <si>
     <t>"Burning" is inscribed on the back of the miniature.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プールの模型</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>模型の裏側には「溺」と記載されている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Miniature swimming pool</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"Drowning" is inscribed on the back of the miniature.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1771,9 +1787,60 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" ht="56.25">
       <c r="A20">
         <v>18</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" t="s">
+        <v>97</v>
+      </c>
+      <c r="J20" s="1">
+        <v>14</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L20" s="1">
+        <v>14</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P20" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="R20" s="1">
+        <v>14</v>
+      </c>
+      <c r="S20" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:19">

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBA35B7-96E1-4F0F-84C4-FB016A4B2F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D4D175-0907-44B1-A189-5B5542D442C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="106">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -471,6 +471,26 @@
   </si>
   <si>
     <t>"Drowning" is inscribed on the back of the miniature.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラッカー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの前方近くにいる彷徨う者に対して使用することで、その者は一定時間ひるんで行動できない。前方近くに存在する者ならまとめてひるませることができるが、大きな音が鳴ってしまう。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Assets/Originals/Prefabs/MainScene/Items/UseItem/Cracker.prefab</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cracker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Using this against nearby wanderers in front of the player stuns them, leaving them unable to act for a certain period of time. It can stun multiple targets at once within close range ahead, but it will generate a loud noise.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1843,9 +1863,63 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" ht="257.25" customHeight="1">
       <c r="A21">
         <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21" t="s">
+        <v>101</v>
+      </c>
+      <c r="J21" s="1">
+        <v>14</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="L21" s="1">
+        <v>14</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21" s="1">
+        <v>8</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="P21" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="R21" s="1">
+        <v>14</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:19">

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D4D175-0907-44B1-A189-5B5542D442C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767D0E9F-14ED-4580-98C1-557A82F701E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -478,10 +477,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プレイヤーの前方近くにいる彷徨う者に対して使用することで、その者は一定時間ひるんで行動できない。前方近くに存在する者ならまとめてひるませることができるが、大きな音が鳴ってしまう。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Assets/Originals/Prefabs/MainScene/Items/UseItem/Cracker.prefab</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -490,7 +485,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Using this against nearby wanderers in front of the player stuns them, leaving them unable to act for a certain period of time. It can stun multiple targets at once within close range ahead, but it will generate a loud noise.</t>
+    <t>Using this against nearby wanderers in front of the player stuns them, leaving them unable to act for a certain period of time. However, it will generate a loud noise.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前方近くの彷徨う者に対して使用することで、その者は一定時間ひるんで行動できない。ただし、大きな音が鳴ってしまう。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1868,7 +1867,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1895,7 +1894,7 @@
         <v>14</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L21" s="1">
         <v>14</v>
@@ -1904,19 +1903,19 @@
         <v>1</v>
       </c>
       <c r="N21" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O21" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P21" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q21" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="P21" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="R21" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>65</v>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767D0E9F-14ED-4580-98C1-557A82F701E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B47010-AA3C-4E7C-82CE-10AD9D70E465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="110">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -106,10 +106,6 @@
   </si>
   <si>
     <t>itemDescriptionSizeEnglish</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ドキュメント</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -125,10 +121,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Document</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Breaking News! Body of young boy found in park! What was the murder weapon?
 In the early hours of [Month] [Day], the body of a young boy (estimated age 12–14) was discovered near △△ Park within the city.The scene is located along a promenade popular with locals, and the body was found by a passerby during their morning walk.
 The body showed no visible external injuries, and authorities state that "the possibility of foul play remains unclear." Furthermore, according to investigators, no weapon appears to have been found near the scene.
@@ -490,6 +482,40 @@
   </si>
   <si>
     <t>前方近くの彷徨う者に対して使用することで、その者は一定時間ひるんで行動できない。ただし、大きな音が鳴ってしまう。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>かつての親友へ
+小さい頃はいつも近くの△△公園で、一緒に遊んでいたのを覚えていますか？
+「ずっと一緒だよ」
+あの日、公園のベンチでそう言ってくれた言葉を、今でも鮮明に思い出します。
+だけど、季節が過ぎるたびに、君が公園に来られる日は少なくなっていっちゃって……。
+最後に会った時、冷たくなった君は横たわったままピクリとも動かず、いつもの優しい声で僕の名前を呼んでくれることもなかった…。
+君がいなくなってからの日々を耐えて過ごしてきたけど、苦しくてもう限界です。
+だから僕もそっちへ行きます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">A Story About a Certain Best Friend </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>To my former best friend, Do you remember how we used to always play together at the nearby △△ Park when we were little?
+"We'll be together forever." Even now, I can still vividly recall those words you said to me on that park bench that day.
+But as the seasons passed, the days you were able to come to the park became fewer and fewer... The last time we met, you were lying down, cold and completely still. You didn't even call my name in your usual gentle voice...
+I've endured the days since you've been gone, but the pain is too much, and I've reached my limit. So, I'm going to join you.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>公園に少年の死体</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Body of young boy found in park</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ある親友についてのお話</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -899,7 +925,7 @@
         <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -931,13 +957,13 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="J3">
         <v>14</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L3">
         <v>14</v>
@@ -948,20 +974,20 @@
       <c r="N3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>21</v>
+      <c r="O3" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="P3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R3">
         <v>12</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="93.75">
@@ -987,13 +1013,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J4">
         <v>14</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L4">
         <v>14</v>
@@ -1005,19 +1031,19 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P4">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P4">
-        <v>14</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="R4">
         <v>14</v>
       </c>
       <c r="S4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="37.5">
@@ -1043,13 +1069,13 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J5">
         <v>14</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L5">
         <v>14</v>
@@ -1061,19 +1087,19 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P5">
         <v>14</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="R5">
         <v>14</v>
       </c>
       <c r="S5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="37.5">
@@ -1099,13 +1125,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J6">
         <v>14</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L6">
         <v>14</v>
@@ -1117,19 +1143,19 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P6">
         <v>14</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R6">
         <v>14</v>
       </c>
       <c r="S6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1160,13 +1186,13 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J8">
         <v>14</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L8">
         <v>14</v>
@@ -1178,19 +1204,19 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P8">
         <v>14</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R8">
         <v>14</v>
       </c>
       <c r="S8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="168.75">
@@ -1216,13 +1242,13 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J9">
         <v>14</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L9">
         <v>14</v>
@@ -1234,19 +1260,19 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P9">
         <v>14</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R9">
         <v>14</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="56.25">
@@ -1272,13 +1298,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J10">
         <v>14</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L10">
         <v>14</v>
@@ -1290,19 +1316,19 @@
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P10">
         <v>14</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R10">
         <v>14</v>
       </c>
       <c r="S10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="37.5">
@@ -1328,13 +1354,13 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J11">
         <v>14</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L11">
         <v>14</v>
@@ -1346,19 +1372,19 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P11">
         <v>14</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R11">
         <v>14</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="37.5">
@@ -1385,13 +1411,13 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J12">
         <v>14</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L12">
         <v>14</v>
@@ -1403,19 +1429,19 @@
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P12">
         <v>14</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R12">
         <v>14</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="112.5">
@@ -1423,34 +1449,34 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13">
+        <v>14</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13" t="s">
-        <v>49</v>
-      </c>
-      <c r="J13">
-        <v>14</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="L13">
         <v>14</v>
@@ -1462,19 +1488,19 @@
         <v>60</v>
       </c>
       <c r="O13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="P13">
         <v>14</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R13">
         <v>14</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="112.5">
@@ -1501,13 +1527,13 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J14" s="1">
         <v>14</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L14" s="1">
         <v>12</v>
@@ -1519,19 +1545,19 @@
         <v>0</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P14" s="1">
         <v>14</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="R14" s="1">
         <v>12</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="56.25">
@@ -1576,7 +1602,7 @@
         <v>14</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="56.25">
@@ -1603,13 +1629,13 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J16" s="1">
         <v>14</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L16" s="1">
         <v>14</v>
@@ -1621,19 +1647,19 @@
         <v>0</v>
       </c>
       <c r="O16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P16" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="R16" s="1">
+        <v>14</v>
+      </c>
+      <c r="S16" t="s">
         <v>80</v>
-      </c>
-      <c r="P16" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="R16" s="1">
-        <v>14</v>
-      </c>
-      <c r="S16" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="56.25">
@@ -1660,13 +1686,13 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J17" s="1">
         <v>14</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L17" s="1">
         <v>14</v>
@@ -1678,19 +1704,19 @@
         <v>0</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P17" s="1">
         <v>14</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="R17" s="1">
         <v>14</v>
       </c>
       <c r="S17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="56.25">
@@ -1716,13 +1742,13 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J18" s="1">
         <v>14</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L18" s="1">
         <v>14</v>
@@ -1734,19 +1760,19 @@
         <v>0</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P18" s="1">
         <v>12</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="R18" s="1">
         <v>14</v>
       </c>
       <c r="S18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="56.25">
@@ -1773,13 +1799,13 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J19" s="1">
         <v>14</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L19" s="1">
         <v>14</v>
@@ -1791,19 +1817,19 @@
         <v>0</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P19" s="1">
         <v>14</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="R19" s="1">
         <v>14</v>
       </c>
       <c r="S19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="56.25">
@@ -1829,13 +1855,13 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J20" s="1">
         <v>14</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L20" s="1">
         <v>14</v>
@@ -1847,19 +1873,19 @@
         <v>0</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P20" s="1">
         <v>12</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R20" s="1">
         <v>14</v>
       </c>
       <c r="S20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="257.25" customHeight="1">
@@ -1867,7 +1893,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1888,13 +1914,13 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J21" s="1">
         <v>14</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L21" s="1">
         <v>14</v>
@@ -1906,24 +1932,75 @@
         <v>1</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P21" s="1">
         <v>14</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R21" s="1">
         <v>10</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="409.5">
       <c r="A22">
         <v>20</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22" t="s">
+        <v>109</v>
+      </c>
+      <c r="J22">
+        <v>12</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L22">
+        <v>14</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="P22">
+        <v>12</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R22">
+        <v>12</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -6814,13 +6891,13 @@
         <v>0</v>
       </c>
       <c r="I996" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J996">
         <v>14</v>
       </c>
       <c r="K996" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L996">
         <v>14</v>
@@ -6832,19 +6909,19 @@
         <v>0</v>
       </c>
       <c r="O996" t="s">
+        <v>56</v>
+      </c>
+      <c r="P996">
+        <v>14</v>
+      </c>
+      <c r="Q996" t="s">
+        <v>57</v>
+      </c>
+      <c r="R996">
+        <v>14</v>
+      </c>
+      <c r="S996" t="s">
         <v>58</v>
-      </c>
-      <c r="P996">
-        <v>14</v>
-      </c>
-      <c r="Q996" t="s">
-        <v>59</v>
-      </c>
-      <c r="R996">
-        <v>14</v>
-      </c>
-      <c r="S996" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="997" spans="1:19" ht="93.75">
@@ -6852,7 +6929,7 @@
         <v>995</v>
       </c>
       <c r="B997" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C997">
         <v>0</v>
@@ -6873,13 +6950,13 @@
         <v>0</v>
       </c>
       <c r="I997" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J997">
         <v>14</v>
       </c>
       <c r="K997" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L997">
         <v>14</v>
@@ -6891,19 +6968,19 @@
         <v>0</v>
       </c>
       <c r="O997" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P997">
         <v>14</v>
       </c>
       <c r="Q997" t="s">
+        <v>60</v>
+      </c>
+      <c r="R997">
+        <v>14</v>
+      </c>
+      <c r="S997" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="R997">
-        <v>14</v>
-      </c>
-      <c r="S997" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="998" spans="1:19" ht="75">
@@ -6929,13 +7006,13 @@
         <v>0</v>
       </c>
       <c r="I998" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J998">
         <v>14</v>
       </c>
       <c r="K998" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L998">
         <v>14</v>
@@ -6947,19 +7024,19 @@
         <v>0</v>
       </c>
       <c r="O998" t="s">
+        <v>64</v>
+      </c>
+      <c r="P998">
+        <v>14</v>
+      </c>
+      <c r="Q998" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="R998">
+        <v>14</v>
+      </c>
+      <c r="S998" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="P998">
-        <v>14</v>
-      </c>
-      <c r="Q998" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="R998">
-        <v>14</v>
-      </c>
-      <c r="S998" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="999" spans="1:19" ht="75">
@@ -6985,13 +7062,13 @@
         <v>0</v>
       </c>
       <c r="I999" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J999">
         <v>14</v>
       </c>
       <c r="K999" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L999">
         <v>14</v>
@@ -7003,19 +7080,19 @@
         <v>0</v>
       </c>
       <c r="O999" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P999">
         <v>14</v>
       </c>
       <c r="Q999" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R999">
         <v>14</v>
       </c>
       <c r="S999" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1000" spans="1:19" ht="75">
@@ -7041,13 +7118,13 @@
         <v>0</v>
       </c>
       <c r="I1000" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J1000">
         <v>14</v>
       </c>
       <c r="K1000" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L1000">
         <v>14</v>
@@ -7059,19 +7136,19 @@
         <v>0</v>
       </c>
       <c r="O1000" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P1000">
         <v>14</v>
       </c>
       <c r="Q1000" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R1000">
         <v>14</v>
       </c>
       <c r="S1000" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1001" spans="1:19">
@@ -7097,13 +7174,13 @@
         <v>0</v>
       </c>
       <c r="I1001" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J1001">
         <v>14</v>
       </c>
       <c r="K1001" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L1001">
         <v>14</v>
@@ -7115,19 +7192,19 @@
         <v>0</v>
       </c>
       <c r="O1001" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P1001">
         <v>14</v>
       </c>
       <c r="Q1001" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R1001">
         <v>14</v>
       </c>
       <c r="S1001" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1002" spans="1:19">
@@ -7153,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="I1002" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J1002">
         <v>0</v>
       </c>
       <c r="K1002" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L1002">
         <v>0</v>
@@ -7171,13 +7248,13 @@
         <v>0</v>
       </c>
       <c r="O1002" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P1002">
         <v>0</v>
       </c>
       <c r="Q1002" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B47010-AA3C-4E7C-82CE-10AD9D70E465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4608BF-3FD0-40EA-9A37-05C5E06EAF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1923,7 +1923,7 @@
         <v>103</v>
       </c>
       <c r="L21" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M21">
         <v>1</v>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4608BF-3FD0-40EA-9A37-05C5E06EAF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63FE3EB-2F17-4067-8C7D-A6CA71BBFE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -113,14 +113,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>速報！公園に少年の死体が！…使用された凶器は？
-〇月×日未明、市内の△△公園近くで、少年（推定年齢は12〜14歳）が遺体となって発見された。現場は地元の人々に親しまれる遊歩道沿いであり、朝の散歩中の通行人によって発見された。
-遺体には目立った外傷がなく、「事件性は不明」とされている。さらに捜査関係者によれば、現場近くから凶器は発見されていない模様だ。
-少年の身元はいまだ特定されておらず、警察は地域住民への聞き込みを進めている。
-捜査は難航としているが、今後の続報が待たれる。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Breaking News! Body of young boy found in park! What was the murder weapon?
 In the early hours of [Month] [Day], the body of a young boy (estimated age 12–14) was discovered near △△ Park within the city.The scene is located along a promenade popular with locals, and the body was found by a passerby during their morning walk.
 The body showed no visible external injuries, and authorities state that "the possibility of foul play remains unclear." Furthermore, according to investigators, no weapon appears to have been found near the scene.
@@ -128,17 +120,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>睡眠薬</t>
-    <rPh sb="0" eb="3">
-      <t>スイミンヤク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>就寝の1～2時間前に服薬することで寝不足を解消できる強力な睡眠薬。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Sleeping pills</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -155,10 +136,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>鋭い刃を持つ古びたナイフ。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Knife</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -171,11 +148,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">重厚な鉄製のハンマー。
-</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Hammer</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -188,10 +160,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>太く頑丈なロープで、端がほつれている。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Rope</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -201,11 +169,6 @@
   </si>
   <si>
     <t>チュートリアル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ある男性が自宅で殺害されていた。
-頭部を激しく殴られた痕があり、警察は鈍器による犯行と見て捜査を開始した。</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -220,17 +183,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>斧</t>
-    <rPh sb="0" eb="1">
-      <t>オノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>見た目以上に刃こぼれしている重々しい斧。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Axe</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -243,27 +195,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>スタミナ増強剤</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アイテム使用：プレイヤーのスタミナ消費量が一定時間小さくなり、スタミナ回復量が大きくなる。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Stamina Booster</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>On Use: Reduces player stamina consumption and increases stamina recovery rate for a certain period.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>不思議なコンパス</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>針に青玉の欠片が使用されており、常に裁きの青玉が存在する方向へ指し示す。</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -387,28 +323,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>病院のベッドの模型</t>
-    <rPh sb="7" eb="9">
-      <t>モケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>模型の裏側には「病」と記載されている。</t>
-    <rPh sb="0" eb="2">
-      <t>モケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>踏切の模型</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>模型の裏側には「轢」と記載されている。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Miniature railroad crossing</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -417,14 +331,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>崩れたビルの模型</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>模型の裏側には「圧」と記載されている。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Miniature of a collapsed building</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -433,14 +339,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>暖炉の模型</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>模型の裏側には「焼」と記載されている。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Miniature fireplace</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -449,14 +347,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プールの模型</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>模型の裏側には「溺」と記載されている。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Miniature swimming pool</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -478,21 +368,6 @@
   </si>
   <si>
     <t>Using this against nearby wanderers in front of the player stuns them, leaving them unable to act for a certain period of time. However, it will generate a loud noise.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>前方近くの彷徨う者に対して使用することで、その者は一定時間ひるんで行動できない。ただし、大きな音が鳴ってしまう。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>かつての親友へ
-小さい頃はいつも近くの△△公園で、一緒に遊んでいたのを覚えていますか？
-「ずっと一緒だよ」
-あの日、公園のベンチでそう言ってくれた言葉を、今でも鮮明に思い出します。
-だけど、季節が過ぎるたびに、君が公園に来られる日は少なくなっていっちゃって……。
-最後に会った時、冷たくなった君は横たわったままピクリとも動かず、いつもの優しい声で僕の名前を呼んでくれることもなかった…。
-君がいなくなってからの日々を耐えて過ごしてきたけど、苦しくてもう限界です。
-だから僕もそっちへ行きます。</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -507,15 +382,150 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>公園に少年の死体</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Body of young boy found in park</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ある親友についてのお話</t>
+    <t>&lt;r="こうえん"&gt;公園&lt;/r&gt;に&lt;r="しょうねん"&gt;少年&lt;/r&gt;の&lt;r="したい"&gt;死体&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="すいみんやく"&gt;睡眠薬&lt;/r&gt;</t>
+    <rPh sb="12" eb="15">
+      <t>スイミンヤク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="おの"&gt;斧&lt;/r&gt;</t>
+    <rPh sb="8" eb="9">
+      <t>オノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スタミナ&lt;r="ぞうきょうざい"&gt;増強剤&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="ふしぎ"&gt;不思議&lt;/r&gt;なコンパス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="びょういん"&gt;病院&lt;/r&gt;のベッドの&lt;r="もけい"&gt;模型&lt;/r&gt;</t>
+    <rPh sb="11" eb="13">
+      <t>ビョウイン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>モケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="ふみきり"&gt;踏切&lt;/r&gt;の&lt;r="もけい"&gt;模型&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="くず"&gt;崩&lt;/r&gt;れたビルの&lt;r="もけい"&gt;模型&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="だんろ"&gt;暖炉&lt;/r&gt;の&lt;r="もけい"&gt;模型&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プールの&lt;r="もけい"&gt;模型&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ある&lt;r="しんゆう"&gt;親友&lt;/r&gt;についてのお&lt;r="はなし"&gt;話&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="そくほう"&gt;速報&lt;/r&gt;！&lt;r="こうえん"&gt;公園&lt;/r&gt;に&lt;r="しょうねん"&gt;少年&lt;/r&gt;の&lt;r="したい"&gt;死体&lt;/r&gt;が！…&lt;r="しよう"&gt;使用&lt;/r&gt;された&lt;r="きょうき"&gt;凶器&lt;/r&gt;は？
+〇&lt;r="がつ"&gt;月&lt;/r&gt;×&lt;r="にち"&gt;日&lt;/r&gt;&lt;r="みめい"&gt;未明&lt;/r&gt;、&lt;r="しない"&gt;市内&lt;/r&gt;の△△&lt;r="こうえん"&gt;公園&lt;/r&gt;&lt;r="ちか"&gt;近&lt;/r&gt;くで、&lt;r="しょうねん"&gt;少年&lt;/r&gt;（&lt;r="すいてい"&gt;推定&lt;/r&gt;&lt;r="ねんれい"&gt;年齢&lt;/r&gt;は12〜14&lt;r="さい"&gt;歳&lt;/r&gt;）が&lt;r="いたい"&gt;遺体&lt;/r&gt;となって&lt;r="はっけん"&gt;発見&lt;/r&gt;された。&lt;r="げんば"&gt;現場&lt;/r&gt;は&lt;r="じもと"&gt;地元&lt;/r&gt;の&lt;r="ひとびと"&gt;人々&lt;/r&gt;に&lt;r="した"&gt;親&lt;/r&gt;しまれる&lt;r="ゆうほどう"&gt;遊歩道&lt;/r&gt;&lt;r="ぞ"&gt;沿&lt;/r&gt;いであり、&lt;r="あさ"&gt;朝&lt;/r&gt;の&lt;r="さんぽちゅう"&gt;散歩中&lt;/r&gt;の&lt;r="つうこうにん"&gt;通行人&lt;/r&gt;によって&lt;r="はっけん"&gt;発見&lt;/r&gt;された。
+&lt;r="いたい"&gt;遺体&lt;/r&gt;には&lt;r="めだ"&gt;目立&lt;/r&gt;った&lt;r="がいしょう"&gt;外傷&lt;/r&gt;がなく、「&lt;r="じけんせい"&gt;事件性&lt;/r&gt;は&lt;r="ふめい"&gt;不明&lt;/r&gt;」とされている。さらに&lt;r="そうさ"&gt;捜査&lt;/r&gt;&lt;r="かんけいしゃ"&gt;関係者&lt;/r&gt;によれば、&lt;r="げんば"&gt;現場&lt;/r&gt;&lt;r="ちか"&gt;近&lt;/r&gt;くから&lt;r="きょうき"&gt;凶器&lt;/r&gt;は&lt;r="はっけん"&gt;発見&lt;/r&gt;されていない&lt;r="もよう"&gt;模様&lt;/r&gt;だ。
+&lt;r="しょうねん"&gt;少年&lt;/r&gt;の&lt;r="みもと"&gt;身元&lt;/r&gt;はいまだ&lt;r="とくてい"&gt;特定&lt;/r&gt;されておらず、&lt;r="けいさつ"&gt;警察&lt;/r&gt;は&lt;r="ちいき"&gt;地域&lt;/r&gt;&lt;r="じゅうみん"&gt;住民&lt;/r&gt;への&lt;r="き"&gt;聞&lt;/r&gt;き&lt;r="こ"&gt;込&lt;/r&gt;みを&lt;r="すす"&gt;進&lt;/r&gt;めている。
+&lt;r="そうさ"&gt;捜査&lt;/r&gt;は&lt;r="なんこう"&gt;難航&lt;/r&gt;としているが、&lt;r="こんご"&gt;今後&lt;/r&gt;の&lt;r="ぞくほう"&gt;続報&lt;/r&gt;が&lt;r="ま"&gt;待&lt;/r&gt;たれる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="しゅうしん"&gt;就寝&lt;/r&gt;の1～2&lt;r="じかんまえ"&gt;時間前&lt;/r&gt;に&lt;r="ふくやく"&gt;服薬&lt;/r&gt;することで&lt;r="ねぶそく"&gt;寝不足&lt;/r&gt;を&lt;r="かいしょう"&gt;解消&lt;/r&gt;できる&lt;r="きょうりょく"&gt;強力&lt;/r&gt;な&lt;r="すいみんやく"&gt;睡眠薬&lt;/r&gt;。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="するど"&gt;鋭&lt;/r&gt;い&lt;r="は"&gt;刃&lt;/r&gt;を&lt;r="も"&gt;持&lt;/r&gt;つ&lt;r="ふる"&gt;古&lt;/r&gt;びたナイフ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="じゅうこう"&gt;重厚&lt;/r&gt;な&lt;r="てつせい"&gt;鉄製&lt;/r&gt;のハンマー。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;r="ふと"&gt;太&lt;/r&gt;く&lt;r="がんじょう"&gt;頑丈&lt;/r&gt;なロープで、&lt;r="はし"&gt;端&lt;/r&gt;がほつれている。 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ある&lt;r="だんせい"&gt;男性&lt;/r&gt;が&lt;r="じたく"&gt;自宅&lt;/r&gt;で&lt;r="さつがい"&gt;殺害&lt;/r&gt;されていた。&lt;r="とうぶ"&gt;頭部&lt;/r&gt;を&lt;r="はげ"&gt;激&lt;/r&gt;しく&lt;r="なぐ"&gt;殴&lt;/r&gt;られた&lt;r="あと"&gt;痕&lt;/r&gt;があり、&lt;r="けいさつ"&gt;警察&lt;/r&gt;は&lt;r="どんき"&gt;鈍器&lt;/r&gt;による&lt;r="はんこう"&gt;犯行&lt;/r&gt;とみて&lt;r="そうさ"&gt;捜査&lt;/r&gt;を&lt;r="かいし"&gt;開始&lt;/r&gt;した。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="み"&gt;見&lt;/r&gt;た&lt;r="め"&gt;目&lt;/r&gt;&lt;r="いじょう"&gt;以上&lt;/r&gt;に&lt;r="は"&gt;刃&lt;/r&gt;こぼれしている&lt;r="おもおも"&gt;重々&lt;/r&gt;しい&lt;r="おの"&gt;斧&lt;/r&gt;。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテム&lt;r="しよう"&gt;使用&lt;/r&gt;：プレイヤーのスタミナ&lt;r="しょうひりょう"&gt;消費量&lt;/r&gt;が&lt;r="いってい"&gt;一定&lt;/r&gt;&lt;r="じかん"&gt;時間&lt;/r&gt;&lt;r="ちい"&gt;小&lt;/r&gt;さくなり、スタミナ&lt;r="かいふくりょう"&gt;回復量&lt;/r&gt;が&lt;r="おお"&gt;大&lt;/r&gt;きくなる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;r="はり"&gt;針&lt;/r&gt;に&lt;r="せいぎょく"&gt;青玉&lt;/r&gt;の&lt;r="かけら"&gt;欠片&lt;/r&gt;が&lt;r="しよう"&gt;使用&lt;/r&gt;されており、&lt;r="つね"&gt;常&lt;/r&gt;に&lt;r="さば"&gt;裁&lt;/r&gt;きの&lt;r="せいぎょく"&gt;青玉&lt;/r&gt;が&lt;r="そんざい"&gt;存在&lt;/r&gt;する&lt;r="ほうこう"&gt;方向&lt;/r&gt;へ&lt;r="さ"&gt;指&lt;/r&gt;し&lt;r="しめ"&gt;示&lt;/r&gt;す。 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="もけい"&gt;模型&lt;/r&gt;の&lt;r="うらがわ"&gt;裏側&lt;/r&gt;には「&lt;r="びょう"&gt;病&lt;/r&gt;」と&lt;r="きさい"&gt;記載&lt;/r&gt;されている。</t>
+    <rPh sb="9" eb="11">
+      <t>モケイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ウラガワ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="もけい"&gt;模型&lt;/r&gt;の&lt;r="うらがわ"&gt;裏側&lt;/r&gt;には「&lt;r="れき"&gt;轢&lt;/r&gt;」と&lt;r="きさい"&gt;記載&lt;/r&gt;されている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="もけい"&gt;模型&lt;/r&gt;の&lt;r="うらがわ"&gt;裏側&lt;/r&gt;には「&lt;r="あつ"&gt;圧&lt;/r&gt;」と&lt;r="きさい"&gt;記載&lt;/r&gt;されている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;r="もけい"&gt;模型&lt;/r&gt;の&lt;r="うらがわ"&gt;裏側&lt;/r&gt;には「&lt;r="しょう"&gt;焼&lt;/r&gt;」と&lt;r="きさい"&gt;記載&lt;/r&gt;されている。 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;r="もけい"&gt;模型&lt;/r&gt;の&lt;r="うらがわ"&gt;裏側&lt;/r&gt;には「&lt;r="でき"&gt;溺&lt;/r&gt;」と&lt;r="きさい"&gt;記載&lt;/r&gt;されている。 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;r="ぜんぽう"&gt;前方&lt;/r&gt;&lt;r="ちか"&gt;近&lt;/r&gt;くの&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;に&lt;r="たい"&gt;対&lt;/r&gt;して&lt;r="しよう"&gt;使用&lt;/r&gt;することで、その&lt;r="もの"&gt;者&lt;/r&gt;は&lt;r="いってい"&gt;一定&lt;/r&gt;&lt;r="じかん"&gt;時間&lt;/r&gt;ひるんで&lt;r="こうどう"&gt;行動&lt;/r&gt;できない。ただし、&lt;r="おお"&gt;大&lt;/r&gt;きな&lt;r="おと"&gt;音&lt;/r&gt;が&lt;r="な"&gt;鳴&lt;/r&gt;ってしまう。 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>かつての&lt;r="しんゆう"&gt;親友&lt;/r&gt;へ 
+&lt;r="ちい"&gt;小&lt;/r&gt;さい&lt;r="ころ"&gt;頃&lt;/r&gt;はいつも&lt;r="ちか"&gt;近&lt;/r&gt;くの△△&lt;r="こうえん"&gt;公園&lt;/r&gt;で、&lt;r="いっしょ"&gt;一緒&lt;/r&gt;に&lt;r="あそ"&gt;遊&lt;/r&gt;んでいたのを&lt;r="おぼ"&gt;覚&lt;/r&gt;えていますか？
+「ずっと&lt;r="いっしょ"&gt;一緒&lt;/r&gt;だよ」
+あの&lt;r="ひ"&gt;日&lt;/r&gt;、&lt;r="こうえん"&gt;公園&lt;/r&gt;のベンチでそう&lt;r="い"&gt;言&lt;/r&gt;ってくれた&lt;r="ことば"&gt;言葉&lt;/r&gt;を、&lt;r="いま"&gt;今&lt;/r&gt;でも&lt;r="せんめい"&gt;鮮明&lt;/r&gt;に&lt;r="おも"&gt;思&lt;/r&gt;い&lt;r="だ"&gt;出&lt;/r&gt;します。
+だけど、&lt;r="きせつ"&gt;季節&lt;/r&gt;が&lt;r="す"&gt;過&lt;/r&gt;ぎるたびに、&lt;r="きみ"&gt;君&lt;/r&gt;が&lt;r="こうえん"&gt;公園&lt;/r&gt;に&lt;r="こ"&gt;来&lt;/r&gt;られる&lt;r="ひ"&gt;日&lt;/r&gt;は&lt;r="すく"&gt;少&lt;/r&gt;なくなっていっちゃって……。
+&lt;r="さいご"&gt;最後&lt;/r&gt;に&lt;r="あ"&gt;会&lt;/r&gt;った&lt;r="とき"&gt;時&lt;/r&gt;、&lt;r="つめ"&gt;冷&lt;/r&gt;たくなった&lt;r="きみ"&gt;君&lt;/r&gt;は&lt;r="よこ"&gt;横&lt;/r&gt;たわったままピクリとも&lt;r="うご"&gt;動&lt;/r&gt;かず、いつもの&lt;r="やさ"&gt;優&lt;/r&gt;しい&lt;r="こえ"&gt;声&lt;/r&gt;で&lt;r="ぼく"&gt;僕&lt;/r&gt;の&lt;r="なまえ"&gt;名前&lt;/r&gt;を&lt;r="よ"&gt;呼&lt;/r&gt;んでくれることもなかった…。
+&lt;r="きみ"&gt;君&lt;/r&gt;がいなくなってからの&lt;r="ひび"&gt;日々&lt;/r&gt;を&lt;r="た"&gt;耐&lt;/r&gt;えて&lt;r="す"&gt;過&lt;/r&gt;ごしてきたけど、&lt;r="くる"&gt;苦&lt;/r&gt;しくてもう&lt;r="げんかい"&gt;限界&lt;/r&gt;です。
+だから&lt;r="ぼく"&gt;僕&lt;/r&gt;もそっちへ&lt;r="い"&gt;行&lt;/r&gt;きます。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -857,7 +867,7 @@
     <col min="6" max="6" width="15.125" customWidth="1"/>
     <col min="7" max="7" width="14.875" customWidth="1"/>
     <col min="8" max="8" width="15.5" customWidth="1"/>
-    <col min="9" max="9" width="26.75" customWidth="1"/>
+    <col min="9" max="9" width="26.75" style="1" customWidth="1"/>
     <col min="10" max="10" width="21.375" customWidth="1"/>
     <col min="11" max="11" width="22.375" customWidth="1"/>
     <col min="12" max="12" width="26.25" customWidth="1"/>
@@ -894,7 +904,7 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -956,14 +966,14 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" t="s">
-        <v>107</v>
+      <c r="I3" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="J3">
         <v>14</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="L3">
         <v>14</v>
@@ -975,22 +985,22 @@
         <v>0</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="P3">
         <v>12</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R3">
         <v>12</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="93.75">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="228" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1012,14 +1022,14 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" t="s">
-        <v>21</v>
+      <c r="I4" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="J4">
         <v>14</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="L4">
         <v>14</v>
@@ -1031,22 +1041,22 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P4">
         <v>14</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="R4">
         <v>14</v>
       </c>
       <c r="S4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="37.5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="92.25" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1068,14 +1078,14 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" t="s">
-        <v>26</v>
+      <c r="I5" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J5">
         <v>14</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="L5">
         <v>14</v>
@@ -1087,22 +1097,22 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="P5">
         <v>14</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="R5">
         <v>14</v>
       </c>
       <c r="S5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="37.5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="56.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1124,14 +1134,14 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" t="s">
-        <v>30</v>
+      <c r="I6" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="J6">
         <v>14</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="L6">
         <v>14</v>
@@ -1143,19 +1153,19 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P6">
         <v>14</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="R6">
         <v>14</v>
       </c>
       <c r="S6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1163,7 +1173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="37.5">
+    <row r="8" spans="1:19" ht="93.75">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1185,14 +1195,14 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" t="s">
-        <v>34</v>
+      <c r="I8" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="J8">
         <v>14</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="L8">
         <v>14</v>
@@ -1204,22 +1214,22 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P8">
         <v>14</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="R8">
         <v>14</v>
       </c>
       <c r="S8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="168.75">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="262.5">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1241,14 +1251,14 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" t="s">
-        <v>38</v>
+      <c r="I9" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="J9">
         <v>14</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="L9">
         <v>14</v>
@@ -1260,22 +1270,22 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="P9">
         <v>14</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="R9">
         <v>14</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="56.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="112.5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1297,14 +1307,14 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" t="s">
-        <v>42</v>
+      <c r="I10" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="J10">
         <v>14</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>14</v>
@@ -1316,22 +1326,22 @@
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="P10">
         <v>14</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="R10">
         <v>14</v>
       </c>
       <c r="S10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="37.5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="56.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1353,14 +1363,14 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11" t="s">
-        <v>30</v>
+      <c r="I11" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="J11">
         <v>14</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="L11">
         <v>14</v>
@@ -1372,22 +1382,22 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P11">
         <v>14</v>
       </c>
       <c r="Q11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R11">
+        <v>14</v>
+      </c>
+      <c r="S11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="R11">
-        <v>14</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="37.5">
+    </row>
+    <row r="12" spans="1:19" ht="93.75">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1410,14 +1420,14 @@
       <c r="H12">
         <v>0</v>
       </c>
-      <c r="I12" t="s">
-        <v>34</v>
+      <c r="I12" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="J12">
         <v>14</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="L12">
         <v>14</v>
@@ -1429,27 +1439,27 @@
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P12">
         <v>14</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="R12">
         <v>14</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="112.5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="225" customHeight="1">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1469,14 +1479,14 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" t="s">
-        <v>47</v>
+      <c r="I13" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="J13">
         <v>14</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="L13">
         <v>14</v>
@@ -1488,22 +1498,22 @@
         <v>60</v>
       </c>
       <c r="O13" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="P13">
         <v>14</v>
       </c>
       <c r="Q13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R13">
+        <v>14</v>
+      </c>
+      <c r="S13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="R13">
-        <v>14</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="112.5">
+    </row>
+    <row r="14" spans="1:19" ht="252" customHeight="1">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1526,14 +1536,14 @@
       <c r="H14" s="1">
         <v>0</v>
       </c>
-      <c r="I14" t="s">
-        <v>51</v>
+      <c r="I14" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="J14" s="1">
         <v>14</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="L14" s="1">
         <v>12</v>
@@ -1545,19 +1555,19 @@
         <v>0</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="P14" s="1">
         <v>14</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="R14" s="1">
         <v>12</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="56.25">
@@ -1602,10 +1612,10 @@
         <v>14</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="56.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="93.75">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1628,14 +1638,14 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" t="s">
-        <v>81</v>
+      <c r="I16" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="J16" s="1">
         <v>14</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="L16" s="1">
         <v>14</v>
@@ -1647,22 +1657,22 @@
         <v>0</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="P16" s="1">
         <v>14</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="R16" s="1">
         <v>14</v>
       </c>
       <c r="S16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="56.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="93.75">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1685,14 +1695,14 @@
       <c r="H17">
         <v>0</v>
       </c>
-      <c r="I17" t="s">
-        <v>83</v>
+      <c r="I17" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="J17" s="1">
         <v>14</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="L17" s="1">
         <v>14</v>
@@ -1704,22 +1714,22 @@
         <v>0</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="P17" s="1">
         <v>14</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="R17" s="1">
         <v>14</v>
       </c>
       <c r="S17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="56.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="93.75">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1741,14 +1751,14 @@
       <c r="H18">
         <v>0</v>
       </c>
-      <c r="I18" t="s">
-        <v>87</v>
+      <c r="I18" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="J18" s="1">
         <v>14</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="L18" s="1">
         <v>14</v>
@@ -1760,22 +1770,22 @@
         <v>0</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="P18" s="1">
         <v>12</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="R18" s="1">
         <v>14</v>
       </c>
       <c r="S18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="56.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="93.75">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1798,14 +1808,14 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="1" t="s">
         <v>91</v>
       </c>
       <c r="J19" s="1">
         <v>14</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="L19" s="1">
         <v>14</v>
@@ -1817,22 +1827,22 @@
         <v>0</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="P19" s="1">
         <v>14</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="R19" s="1">
         <v>14</v>
       </c>
       <c r="S19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="56.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="93.75">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1854,14 +1864,14 @@
       <c r="H20">
         <v>0</v>
       </c>
-      <c r="I20" t="s">
-        <v>95</v>
+      <c r="I20" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="J20" s="1">
         <v>14</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="L20" s="1">
         <v>14</v>
@@ -1873,19 +1883,19 @@
         <v>0</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="P20" s="1">
         <v>12</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="R20" s="1">
         <v>14</v>
       </c>
       <c r="S20" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="257.25" customHeight="1">
@@ -1893,7 +1903,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1913,14 +1923,14 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" t="s">
-        <v>99</v>
+      <c r="I21" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="J21" s="1">
         <v>14</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L21" s="1">
         <v>12</v>
@@ -1932,19 +1942,19 @@
         <v>1</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="P21" s="1">
         <v>14</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="R21" s="1">
         <v>10</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="409.5">
@@ -1969,14 +1979,14 @@
       <c r="H22">
         <v>0</v>
       </c>
-      <c r="I22" t="s">
-        <v>109</v>
+      <c r="I22" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="J22">
         <v>12</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L22">
         <v>14</v>
@@ -1988,19 +1998,19 @@
         <v>0</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="P22">
         <v>12</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="R22">
         <v>12</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -6890,14 +6900,14 @@
       <c r="H996">
         <v>0</v>
       </c>
-      <c r="I996" t="s">
-        <v>56</v>
+      <c r="I996" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="J996">
         <v>14</v>
       </c>
       <c r="K996" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="L996">
         <v>14</v>
@@ -6909,19 +6919,19 @@
         <v>0</v>
       </c>
       <c r="O996" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="P996">
         <v>14</v>
       </c>
       <c r="Q996" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="R996">
         <v>14</v>
       </c>
       <c r="S996" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="997" spans="1:19" ht="93.75">
@@ -6929,7 +6939,7 @@
         <v>995</v>
       </c>
       <c r="B997" s="1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C997">
         <v>0</v>
@@ -6949,14 +6959,14 @@
       <c r="H997">
         <v>0</v>
       </c>
-      <c r="I997" t="s">
-        <v>61</v>
+      <c r="I997" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="J997">
         <v>14</v>
       </c>
       <c r="K997" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="L997">
         <v>14</v>
@@ -6968,19 +6978,19 @@
         <v>0</v>
       </c>
       <c r="O997" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="P997">
         <v>14</v>
       </c>
       <c r="Q997" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="R997">
         <v>14</v>
       </c>
       <c r="S997" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="998" spans="1:19" ht="75">
@@ -7005,14 +7015,14 @@
       <c r="H998">
         <v>0</v>
       </c>
-      <c r="I998" t="s">
-        <v>64</v>
+      <c r="I998" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="J998">
         <v>14</v>
       </c>
       <c r="K998" s="1" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="L998">
         <v>14</v>
@@ -7024,19 +7034,19 @@
         <v>0</v>
       </c>
       <c r="O998" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="P998">
         <v>14</v>
       </c>
       <c r="Q998" s="1" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="R998">
         <v>14</v>
       </c>
       <c r="S998" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="999" spans="1:19" ht="75">
@@ -7061,14 +7071,14 @@
       <c r="H999">
         <v>0</v>
       </c>
-      <c r="I999" t="s">
-        <v>67</v>
+      <c r="I999" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="J999">
         <v>14</v>
       </c>
       <c r="K999" s="1" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="L999">
         <v>14</v>
@@ -7080,19 +7090,19 @@
         <v>0</v>
       </c>
       <c r="O999" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="P999">
         <v>14</v>
       </c>
       <c r="Q999" s="1" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="R999">
         <v>14</v>
       </c>
       <c r="S999" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1000" spans="1:19" ht="75">
@@ -7118,13 +7128,13 @@
         <v>0</v>
       </c>
       <c r="I1000" s="1" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="J1000">
         <v>14</v>
       </c>
       <c r="K1000" s="1" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="L1000">
         <v>14</v>
@@ -7136,19 +7146,19 @@
         <v>0</v>
       </c>
       <c r="O1000" s="1" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="P1000">
         <v>14</v>
       </c>
       <c r="Q1000" s="1" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="R1000">
         <v>14</v>
       </c>
       <c r="S1000" s="1" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1001" spans="1:19">
@@ -7173,14 +7183,14 @@
       <c r="H1001">
         <v>0</v>
       </c>
-      <c r="I1001" t="s">
-        <v>69</v>
+      <c r="I1001" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="J1001">
         <v>14</v>
       </c>
       <c r="K1001" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="L1001">
         <v>14</v>
@@ -7192,19 +7202,19 @@
         <v>0</v>
       </c>
       <c r="O1001" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="P1001">
         <v>14</v>
       </c>
       <c r="Q1001" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="R1001">
         <v>14</v>
       </c>
       <c r="S1001" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1002" spans="1:19">
@@ -7229,14 +7239,14 @@
       <c r="H1002">
         <v>0</v>
       </c>
-      <c r="I1002" t="s">
-        <v>76</v>
+      <c r="I1002" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="J1002">
         <v>0</v>
       </c>
       <c r="K1002" s="1" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="L1002">
         <v>0</v>
@@ -7248,13 +7258,13 @@
         <v>0</v>
       </c>
       <c r="O1002" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="P1002">
         <v>0</v>
       </c>
       <c r="Q1002" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63FE3EB-2F17-4067-8C7D-A6CA71BBFE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8AF563-8703-482C-9DAD-0D7AD2A5DDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -404,14 +404,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>スタミナ&lt;r="ぞうきょうざい"&gt;増強剤&lt;/r&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;r="ふしぎ"&gt;不思議&lt;/r&gt;なコンパス</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>&lt;r="びょういん"&gt;病院&lt;/r&gt;のベッドの&lt;r="もけい"&gt;模型&lt;/r&gt;</t>
     <rPh sb="11" eb="13">
       <t>ビョウイン</t>
@@ -442,90 +434,86 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;r="そくほう"&gt;速報&lt;/r&gt;！&lt;r="こうえん"&gt;公園&lt;/r&gt;に&lt;r="しょうねん"&gt;少年&lt;/r&gt;の&lt;r="したい"&gt;死体&lt;/r&gt;が！…&lt;r="しよう"&gt;使用&lt;/r&gt;された&lt;r="きょうき"&gt;凶器&lt;/r&gt;は？
-〇&lt;r="がつ"&gt;月&lt;/r&gt;×&lt;r="にち"&gt;日&lt;/r&gt;&lt;r="みめい"&gt;未明&lt;/r&gt;、&lt;r="しない"&gt;市内&lt;/r&gt;の△△&lt;r="こうえん"&gt;公園&lt;/r&gt;&lt;r="ちか"&gt;近&lt;/r&gt;くで、&lt;r="しょうねん"&gt;少年&lt;/r&gt;（&lt;r="すいてい"&gt;推定&lt;/r&gt;&lt;r="ねんれい"&gt;年齢&lt;/r&gt;は12〜14&lt;r="さい"&gt;歳&lt;/r&gt;）が&lt;r="いたい"&gt;遺体&lt;/r&gt;となって&lt;r="はっけん"&gt;発見&lt;/r&gt;された。&lt;r="げんば"&gt;現場&lt;/r&gt;は&lt;r="じもと"&gt;地元&lt;/r&gt;の&lt;r="ひとびと"&gt;人々&lt;/r&gt;に&lt;r="した"&gt;親&lt;/r&gt;しまれる&lt;r="ゆうほどう"&gt;遊歩道&lt;/r&gt;&lt;r="ぞ"&gt;沿&lt;/r&gt;いであり、&lt;r="あさ"&gt;朝&lt;/r&gt;の&lt;r="さんぽちゅう"&gt;散歩中&lt;/r&gt;の&lt;r="つうこうにん"&gt;通行人&lt;/r&gt;によって&lt;r="はっけん"&gt;発見&lt;/r&gt;された。
-&lt;r="いたい"&gt;遺体&lt;/r&gt;には&lt;r="めだ"&gt;目立&lt;/r&gt;った&lt;r="がいしょう"&gt;外傷&lt;/r&gt;がなく、「&lt;r="じけんせい"&gt;事件性&lt;/r&gt;は&lt;r="ふめい"&gt;不明&lt;/r&gt;」とされている。さらに&lt;r="そうさ"&gt;捜査&lt;/r&gt;&lt;r="かんけいしゃ"&gt;関係者&lt;/r&gt;によれば、&lt;r="げんば"&gt;現場&lt;/r&gt;&lt;r="ちか"&gt;近&lt;/r&gt;くから&lt;r="きょうき"&gt;凶器&lt;/r&gt;は&lt;r="はっけん"&gt;発見&lt;/r&gt;されていない&lt;r="もよう"&gt;模様&lt;/r&gt;だ。
-&lt;r="しょうねん"&gt;少年&lt;/r&gt;の&lt;r="みもと"&gt;身元&lt;/r&gt;はいまだ&lt;r="とくてい"&gt;特定&lt;/r&gt;されておらず、&lt;r="けいさつ"&gt;警察&lt;/r&gt;は&lt;r="ちいき"&gt;地域&lt;/r&gt;&lt;r="じゅうみん"&gt;住民&lt;/r&gt;への&lt;r="き"&gt;聞&lt;/r&gt;き&lt;r="こ"&gt;込&lt;/r&gt;みを&lt;r="すす"&gt;進&lt;/r&gt;めている。
-&lt;r="そうさ"&gt;捜査&lt;/r&gt;は&lt;r="なんこう"&gt;難航&lt;/r&gt;としているが、&lt;r="こんご"&gt;今後&lt;/r&gt;の&lt;r="ぞくほう"&gt;続報&lt;/r&gt;が&lt;r="ま"&gt;待&lt;/r&gt;たれる。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;r="しゅうしん"&gt;就寝&lt;/r&gt;の1～2&lt;r="じかんまえ"&gt;時間前&lt;/r&gt;に&lt;r="ふくやく"&gt;服薬&lt;/r&gt;することで&lt;r="ねぶそく"&gt;寝不足&lt;/r&gt;を&lt;r="かいしょう"&gt;解消&lt;/r&gt;できる&lt;r="きょうりょく"&gt;強力&lt;/r&gt;な&lt;r="すいみんやく"&gt;睡眠薬&lt;/r&gt;。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;r="するど"&gt;鋭&lt;/r&gt;い&lt;r="は"&gt;刃&lt;/r&gt;を&lt;r="も"&gt;持&lt;/r&gt;つ&lt;r="ふる"&gt;古&lt;/r&gt;びたナイフ。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;r="じゅうこう"&gt;重厚&lt;/r&gt;な&lt;r="てつせい"&gt;鉄製&lt;/r&gt;のハンマー。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;r="ふと"&gt;太&lt;/r&gt;く&lt;r="がんじょう"&gt;頑丈&lt;/r&gt;なロープで、&lt;r="はし"&gt;端&lt;/r&gt;がほつれている。 </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ある&lt;r="だんせい"&gt;男性&lt;/r&gt;が&lt;r="じたく"&gt;自宅&lt;/r&gt;で&lt;r="さつがい"&gt;殺害&lt;/r&gt;されていた。&lt;r="とうぶ"&gt;頭部&lt;/r&gt;を&lt;r="はげ"&gt;激&lt;/r&gt;しく&lt;r="なぐ"&gt;殴&lt;/r&gt;られた&lt;r="あと"&gt;痕&lt;/r&gt;があり、&lt;r="けいさつ"&gt;警察&lt;/r&gt;は&lt;r="どんき"&gt;鈍器&lt;/r&gt;による&lt;r="はんこう"&gt;犯行&lt;/r&gt;とみて&lt;r="そうさ"&gt;捜査&lt;/r&gt;を&lt;r="かいし"&gt;開始&lt;/r&gt;した。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;r="み"&gt;見&lt;/r&gt;た&lt;r="め"&gt;目&lt;/r&gt;&lt;r="いじょう"&gt;以上&lt;/r&gt;に&lt;r="は"&gt;刃&lt;/r&gt;こぼれしている&lt;r="おもおも"&gt;重々&lt;/r&gt;しい&lt;r="おの"&gt;斧&lt;/r&gt;。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アイテム&lt;r="しよう"&gt;使用&lt;/r&gt;：プレイヤーのスタミナ&lt;r="しょうひりょう"&gt;消費量&lt;/r&gt;が&lt;r="いってい"&gt;一定&lt;/r&gt;&lt;r="じかん"&gt;時間&lt;/r&gt;&lt;r="ちい"&gt;小&lt;/r&gt;さくなり、スタミナ&lt;r="かいふくりょう"&gt;回復量&lt;/r&gt;が&lt;r="おお"&gt;大&lt;/r&gt;きくなる。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;r="はり"&gt;針&lt;/r&gt;に&lt;r="せいぎょく"&gt;青玉&lt;/r&gt;の&lt;r="かけら"&gt;欠片&lt;/r&gt;が&lt;r="しよう"&gt;使用&lt;/r&gt;されており、&lt;r="つね"&gt;常&lt;/r&gt;に&lt;r="さば"&gt;裁&lt;/r&gt;きの&lt;r="せいぎょく"&gt;青玉&lt;/r&gt;が&lt;r="そんざい"&gt;存在&lt;/r&gt;する&lt;r="ほうこう"&gt;方向&lt;/r&gt;へ&lt;r="さ"&gt;指&lt;/r&gt;し&lt;r="しめ"&gt;示&lt;/r&gt;す。 </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;r="もけい"&gt;模型&lt;/r&gt;の&lt;r="うらがわ"&gt;裏側&lt;/r&gt;には「&lt;r="びょう"&gt;病&lt;/r&gt;」と&lt;r="きさい"&gt;記載&lt;/r&gt;されている。</t>
-    <rPh sb="9" eb="11">
-      <t>モケイ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ウラガワ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>キサイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;r="もけい"&gt;模型&lt;/r&gt;の&lt;r="うらがわ"&gt;裏側&lt;/r&gt;には「&lt;r="れき"&gt;轢&lt;/r&gt;」と&lt;r="きさい"&gt;記載&lt;/r&gt;されている。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;r="もけい"&gt;模型&lt;/r&gt;の&lt;r="うらがわ"&gt;裏側&lt;/r&gt;には「&lt;r="あつ"&gt;圧&lt;/r&gt;」と&lt;r="きさい"&gt;記載&lt;/r&gt;されている。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;r="もけい"&gt;模型&lt;/r&gt;の&lt;r="うらがわ"&gt;裏側&lt;/r&gt;には「&lt;r="しょう"&gt;焼&lt;/r&gt;」と&lt;r="きさい"&gt;記載&lt;/r&gt;されている。 </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;r="もけい"&gt;模型&lt;/r&gt;の&lt;r="うらがわ"&gt;裏側&lt;/r&gt;には「&lt;r="でき"&gt;溺&lt;/r&gt;」と&lt;r="きさい"&gt;記載&lt;/r&gt;されている。 </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;r="ぜんぽう"&gt;前方&lt;/r&gt;&lt;r="ちか"&gt;近&lt;/r&gt;くの&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;に&lt;r="たい"&gt;対&lt;/r&gt;して&lt;r="しよう"&gt;使用&lt;/r&gt;することで、その&lt;r="もの"&gt;者&lt;/r&gt;は&lt;r="いってい"&gt;一定&lt;/r&gt;&lt;r="じかん"&gt;時間&lt;/r&gt;ひるんで&lt;r="こうどう"&gt;行動&lt;/r&gt;できない。ただし、&lt;r="おお"&gt;大&lt;/r&gt;きな&lt;r="おと"&gt;音&lt;/r&gt;が&lt;r="な"&gt;鳴&lt;/r&gt;ってしまう。 </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>かつての&lt;r="しんゆう"&gt;親友&lt;/r&gt;へ 
-&lt;r="ちい"&gt;小&lt;/r&gt;さい&lt;r="ころ"&gt;頃&lt;/r&gt;はいつも&lt;r="ちか"&gt;近&lt;/r&gt;くの△△&lt;r="こうえん"&gt;公園&lt;/r&gt;で、&lt;r="いっしょ"&gt;一緒&lt;/r&gt;に&lt;r="あそ"&gt;遊&lt;/r&gt;んでいたのを&lt;r="おぼ"&gt;覚&lt;/r&gt;えていますか？
-「ずっと&lt;r="いっしょ"&gt;一緒&lt;/r&gt;だよ」
-あの&lt;r="ひ"&gt;日&lt;/r&gt;、&lt;r="こうえん"&gt;公園&lt;/r&gt;のベンチでそう&lt;r="い"&gt;言&lt;/r&gt;ってくれた&lt;r="ことば"&gt;言葉&lt;/r&gt;を、&lt;r="いま"&gt;今&lt;/r&gt;でも&lt;r="せんめい"&gt;鮮明&lt;/r&gt;に&lt;r="おも"&gt;思&lt;/r&gt;い&lt;r="だ"&gt;出&lt;/r&gt;します。
-だけど、&lt;r="きせつ"&gt;季節&lt;/r&gt;が&lt;r="す"&gt;過&lt;/r&gt;ぎるたびに、&lt;r="きみ"&gt;君&lt;/r&gt;が&lt;r="こうえん"&gt;公園&lt;/r&gt;に&lt;r="こ"&gt;来&lt;/r&gt;られる&lt;r="ひ"&gt;日&lt;/r&gt;は&lt;r="すく"&gt;少&lt;/r&gt;なくなっていっちゃって……。
-&lt;r="さいご"&gt;最後&lt;/r&gt;に&lt;r="あ"&gt;会&lt;/r&gt;った&lt;r="とき"&gt;時&lt;/r&gt;、&lt;r="つめ"&gt;冷&lt;/r&gt;たくなった&lt;r="きみ"&gt;君&lt;/r&gt;は&lt;r="よこ"&gt;横&lt;/r&gt;たわったままピクリとも&lt;r="うご"&gt;動&lt;/r&gt;かず、いつもの&lt;r="やさ"&gt;優&lt;/r&gt;しい&lt;r="こえ"&gt;声&lt;/r&gt;で&lt;r="ぼく"&gt;僕&lt;/r&gt;の&lt;r="なまえ"&gt;名前&lt;/r&gt;を&lt;r="よ"&gt;呼&lt;/r&gt;んでくれることもなかった…。
-&lt;r="きみ"&gt;君&lt;/r&gt;がいなくなってからの&lt;r="ひび"&gt;日々&lt;/r&gt;を&lt;r="た"&gt;耐&lt;/r&gt;えて&lt;r="す"&gt;過&lt;/r&gt;ごしてきたけど、&lt;r="くる"&gt;苦&lt;/r&gt;しくてもう&lt;r="げんかい"&gt;限界&lt;/r&gt;です。
-だから&lt;r="ぼく"&gt;僕&lt;/r&gt;もそっちへ&lt;r="い"&gt;行&lt;/r&gt;きます。</t>
+    <t>不思議なコンパス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>速報！公園に少年の死体が！…使用された凶器は？
+●月×日未明、市内の△△公園近くで、少年（推定年齢は12-14歳）が遺体となって発見された。現場は地元の人々に親しまれる遊歩道沿いであり、朝の散歩中の通行人によって発見された。
+遺体には目立った外傷がなく、「事件性は不明」とされている。さらに捜査関係者によれば、現場近くから凶器は発見されていない模様だ。
+少年の身元はいまだ特定されておらず、警察は地域住民への聞き込みを進めている。
+捜査は難航としているが、今後の続報が待たれる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>就寝の1～2時間前に服薬することで寝不足を解消できる強力な睡眠薬。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鋭い刃を持つ古びたナイフ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重厚な鉄製のハンマー。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">太く頑丈なロープで、端がほつれている。 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ある男性が自宅で殺害されていた。頭部を激しく殴られた痕があり、警察は鈍器による犯行とみて捜査を開始した。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>見た目以上に刃こぼれしている重々しい斧。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スタミナ増強剤</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテム使用：プレイヤーのスタミナ消費量が一定時間小さくなり、スタミナ回復量が大きくなる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">針に青玉の欠片が使用されており、常に裁きの青玉が存在する方向へ指し示す。 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>模型の裏側には「病」と記載されている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>模型の裏側には「轢」と記載されている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>模型の裏側には「圧」と記載されている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>模型の裏側には「焼」と記載されている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>模型の裏側には「溺」と記載されている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">前方近くの彷徨う者に対して使用することで、その者は一定時間ひるんで行動できない。ただし、大きな音が鳴ってしまう。 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>かつての親友へ 
+小さい頃はいつも近くの△△公園で、一緒に遊んでいたのを覚えていますか？
+「ずっと一緒だよ」
+あの日、公園のベンチでそう言ってくれた言葉を、今でも鮮明に思い出します。
+だけど、季節が過ぎるたびに、君が公園に来られる日は少なくなっていっちゃって……。
+最後に会った時、冷たくなった君は横たわったままピクリとも動かず、いつもの優しい声で僕の名前を呼んでくれることもなかった…。
+君がいなくなってからの日々を耐えて過ごしてきたけど、苦しくてもう限界です。
+だから僕もそっちへ行きます。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -973,7 +961,7 @@
         <v>14</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L3">
         <v>14</v>
@@ -1029,7 +1017,7 @@
         <v>14</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L4">
         <v>14</v>
@@ -1085,7 +1073,7 @@
         <v>14</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L5">
         <v>14</v>
@@ -1112,7 +1100,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="56.25">
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1141,7 +1129,7 @@
         <v>14</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L6">
         <v>14</v>
@@ -1173,7 +1161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="93.75">
+    <row r="8" spans="1:19" ht="37.5">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1202,7 +1190,7 @@
         <v>14</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L8">
         <v>14</v>
@@ -1229,7 +1217,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="262.5">
+    <row r="9" spans="1:19" ht="297.75" customHeight="1">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1258,7 +1246,7 @@
         <v>14</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L9">
         <v>14</v>
@@ -1285,7 +1273,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="112.5">
+    <row r="10" spans="1:19" ht="56.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1314,7 +1302,7 @@
         <v>14</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L10">
         <v>14</v>
@@ -1341,7 +1329,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="56.25">
+    <row r="11" spans="1:19" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1370,7 +1358,7 @@
         <v>14</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L11">
         <v>14</v>
@@ -1397,7 +1385,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="93.75">
+    <row r="12" spans="1:19" ht="37.5">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1427,7 +1415,7 @@
         <v>14</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L12">
         <v>14</v>
@@ -1480,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>14</v>
@@ -1537,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J14" s="1">
         <v>14</v>
@@ -1615,7 +1603,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="93.75">
+    <row r="16" spans="1:19" ht="56.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1639,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J16" s="1">
         <v>14</v>
@@ -1672,7 +1660,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="93.75">
+    <row r="17" spans="1:19" ht="56.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1696,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J17" s="1">
         <v>14</v>
@@ -1729,7 +1717,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="93.75">
+    <row r="18" spans="1:19" ht="56.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1752,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J18" s="1">
         <v>14</v>
@@ -1785,7 +1773,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="93.75">
+    <row r="19" spans="1:19" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1809,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J19" s="1">
         <v>14</v>
@@ -1842,7 +1830,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="93.75">
+    <row r="20" spans="1:19" ht="56.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1865,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J20" s="1">
         <v>14</v>
@@ -1980,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J22">
         <v>12</v>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8AF563-8703-482C-9DAD-0D7AD2A5DDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE34FA8-8149-4E22-B9BA-C292AC882D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE34FA8-8149-4E22-B9BA-C292AC882D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02295B08-F913-4D05-A627-00E5D8130B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1477,7 +1477,7 @@
         <v>101</v>
       </c>
       <c r="L13">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M13">
         <v>1</v>
@@ -1495,7 +1495,7 @@
         <v>39</v>
       </c>
       <c r="R13">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>50</v>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02295B08-F913-4D05-A627-00E5D8130B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8679E1-5D97-467F-B071-205E43A8F598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -964,7 +964,7 @@
         <v>93</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -982,7 +982,7 @@
         <v>19</v>
       </c>
       <c r="R3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>21</v>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8679E1-5D97-467F-B071-205E43A8F598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC88FBC1-BDD7-4286-B067-FAA131613AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="159">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -516,12 +516,174 @@
 だから僕もそっちへ行きます。</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>公园惊现少年尸体</t>
+  </si>
+  <si>
+    <t>快讯！公园惊现少年尸体！…凶器究竟为何物？
+●月×日凌晨，市内△△公园附近发现一具少年（推测年龄12-14岁）遗体。案发现场位于当地居民熟悉的步道旁，是一名晨间散步的路人发现的。
+遗体上未见明显外伤，警方称「是否为刑事案件尚不明确」。此外据办案人员透露，现场附近似乎并未发现凶器。
+少年的身份目前仍未查明，警方正在向当地居民展开走访调查。
+案件侦破进展困难，后续报道值得关注。</t>
+  </si>
+  <si>
+    <t>安眠药</t>
+  </si>
+  <si>
+    <t>睡前1～2小时服用即可消除睡眠不足的强效安眠药。</t>
+  </si>
+  <si>
+    <t>小刀</t>
+  </si>
+  <si>
+    <t>带有锋利刀刃的老旧小刀。</t>
+  </si>
+  <si>
+    <t>锤子</t>
+  </si>
+  <si>
+    <t>厚重的铁制锤子。</t>
+  </si>
+  <si>
+    <t>绳子</t>
+  </si>
+  <si>
+    <t>一根粗壮结实、末端已经磨损的绳子。</t>
+  </si>
+  <si>
+    <t>教程</t>
+  </si>
+  <si>
+    <t>一名男子在自家中被杀害。头部有遭受猛烈殴打的痕迹，警方怀疑是钝器行凶，已展开调查。</t>
+  </si>
+  <si>
+    <t>斧头</t>
+  </si>
+  <si>
+    <t>比外表看起来更加缺口累累的沉重斧头。</t>
+  </si>
+  <si>
+    <t>耐力增强剂</t>
+  </si>
+  <si>
+    <t>使用道具：在一定时间内降低玩家的耐力消耗，并提高耐力恢复量。</t>
+  </si>
+  <si>
+    <t>神秘的罗盘</t>
+  </si>
+  <si>
+    <t>指针使用了蓝玉的碎片制成，会一直指向裁决之蓝玉所在的方向。</t>
+  </si>
+  <si>
+    <t>医院病床模型</t>
+  </si>
+  <si>
+    <t>模型背面刻有「病」字。</t>
+  </si>
+  <si>
+    <t>铁路道口模型</t>
+  </si>
+  <si>
+    <t>模型背面刻有「轹」字。</t>
+  </si>
+  <si>
+    <t>倒塌大楼模型</t>
+  </si>
+  <si>
+    <t>模型背面刻有「压」字。</t>
+  </si>
+  <si>
+    <t>壁炉模型</t>
+  </si>
+  <si>
+    <t>模型背面刻有「烧」字。</t>
+  </si>
+  <si>
+    <t>游泳池模型</t>
+  </si>
+  <si>
+    <t>模型背面刻有「溺」字。</t>
+  </si>
+  <si>
+    <t>拉炮</t>
+  </si>
+  <si>
+    <t>对前方附近的徘徊者使用后，可使其在一定时间内畏缩而无法行动。不过会发出很大的声响。</t>
+  </si>
+  <si>
+    <t>关于一位挚友的故事</t>
+  </si>
+  <si>
+    <t>致曾经的挚友：
+还记得小时候，我们总是一起在附近的△△公园玩耍吗？
+「我们会永远在一起哦」
+那天你在公园长椅上说的这句话，我至今仍历历在目。
+可是，随着季节一次次流逝，你能来公园的日子却越来越少……。
+最后一次见面时，早已冰冷的你静静地躺着，一动也不动，也再没能用那如往常般温柔的声音唤我的名字…。
+你离开后的这些日子，我一直强忍着煎熬活到现在，但已经痛苦到了极限。
+所以，我也要到你那边去了。</t>
+  </si>
+  <si>
+    <t>TestUseItem02</t>
+  </si>
+  <si>
+    <t>测试用使用道具02</t>
+  </si>
+  <si>
+    <t>TestUseItem01</t>
+  </si>
+  <si>
+    <t>测试用使用道具01</t>
+  </si>
+  <si>
+    <t>TestMysteryItem02</t>
+  </si>
+  <si>
+    <t>测试用神秘物品02</t>
+  </si>
+  <si>
+    <t>TestMysteryItem01</t>
+  </si>
+  <si>
+    <t>测试用神秘物品01</t>
+  </si>
+  <si>
+    <t>TestDocumentItem01</t>
+  </si>
+  <si>
+    <t>测试用文件道具</t>
+  </si>
+  <si>
+    <t>TestItem01</t>
+  </si>
+  <si>
+    <t>测试用道具</t>
+  </si>
+  <si>
+    <t>DammyItem</t>
+  </si>
+  <si>
+    <t>itemNameChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>itemNameSizeChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>itemDescriptionChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>itemDescriptionSizeChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -535,6 +697,12 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -557,7 +725,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -565,6 +733,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -845,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S1002"/>
+  <dimension ref="A1:W1002"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -865,9 +1037,13 @@
     <col min="16" max="16" width="20.375" customWidth="1"/>
     <col min="17" max="17" width="20.625" customWidth="1"/>
     <col min="18" max="18" width="23.875" customWidth="1"/>
+    <col min="19" max="19" width="24.75" customWidth="1"/>
+    <col min="20" max="20" width="24.875" customWidth="1"/>
+    <col min="21" max="21" width="26.375" customWidth="1"/>
+    <col min="22" max="22" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -923,16 +1099,28 @@
         <v>17</v>
       </c>
       <c r="S1" t="s">
+        <v>155</v>
+      </c>
+      <c r="T1" t="s">
+        <v>156</v>
+      </c>
+      <c r="U1" t="s">
+        <v>157</v>
+      </c>
+      <c r="V1" t="s">
+        <v>158</v>
+      </c>
+      <c r="W1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:23">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:19" ht="409.5">
+    <row r="3" spans="1:23" ht="409.6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -984,11 +1172,23 @@
       <c r="R3">
         <v>11</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="S3" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="T3" s="4">
+        <v>14</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="V3" s="4">
+        <v>13</v>
+      </c>
+      <c r="W3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="228" customHeight="1">
+    <row r="4" spans="1:23" ht="228" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1040,11 +1240,23 @@
       <c r="R4">
         <v>14</v>
       </c>
-      <c r="S4" t="s">
+      <c r="S4" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="T4" s="4">
+        <v>14</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="V4" s="4">
+        <v>14</v>
+      </c>
+      <c r="W4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="92.25" customHeight="1">
+    <row r="5" spans="1:23" ht="92.25" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1096,11 +1308,23 @@
       <c r="R5">
         <v>14</v>
       </c>
-      <c r="S5" t="s">
+      <c r="S5" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="T5" s="4">
+        <v>14</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="V5" s="4">
+        <v>14</v>
+      </c>
+      <c r="W5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:23" ht="34.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1152,16 +1376,28 @@
       <c r="R6">
         <v>14</v>
       </c>
-      <c r="S6" t="s">
+      <c r="S6" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="T6" s="4">
+        <v>14</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="V6" s="4">
+        <v>14</v>
+      </c>
+      <c r="W6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:23">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="37.5">
+    <row r="8" spans="1:23" ht="84">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1213,11 +1449,23 @@
       <c r="R8">
         <v>14</v>
       </c>
-      <c r="S8" t="s">
+      <c r="S8" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="T8" s="4">
+        <v>14</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="V8" s="4">
+        <v>14</v>
+      </c>
+      <c r="W8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="297.75" customHeight="1">
+    <row r="9" spans="1:23" ht="297.75" customHeight="1">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1269,11 +1517,23 @@
       <c r="R9">
         <v>14</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="S9" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="T9" s="4">
+        <v>14</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="V9" s="4">
+        <v>14</v>
+      </c>
+      <c r="W9" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="56.25">
+    <row r="10" spans="1:23" ht="84">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1325,11 +1585,23 @@
       <c r="R10">
         <v>14</v>
       </c>
-      <c r="S10" t="s">
+      <c r="S10" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="T10" s="4">
+        <v>14</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="V10" s="4">
+        <v>14</v>
+      </c>
+      <c r="W10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="37.5">
+    <row r="11" spans="1:23" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1381,11 +1653,23 @@
       <c r="R11">
         <v>14</v>
       </c>
-      <c r="S11" s="1" t="s">
+      <c r="S11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="T11" s="4">
+        <v>14</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="V11" s="4">
+        <v>14</v>
+      </c>
+      <c r="W11" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="37.5">
+    <row r="12" spans="1:23" ht="84">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1438,11 +1722,23 @@
       <c r="R12">
         <v>14</v>
       </c>
-      <c r="S12" s="1" t="s">
+      <c r="S12" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="T12" s="4">
+        <v>14</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="V12" s="4">
+        <v>14</v>
+      </c>
+      <c r="W12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="225" customHeight="1">
+    <row r="13" spans="1:23" ht="225" customHeight="1">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1497,11 +1793,23 @@
       <c r="R13">
         <v>10</v>
       </c>
-      <c r="S13" s="1" t="s">
+      <c r="S13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="T13" s="4">
+        <v>14</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="V13" s="4">
+        <v>12</v>
+      </c>
+      <c r="W13" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="252" customHeight="1">
+    <row r="14" spans="1:23" ht="252" customHeight="1">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1554,11 +1862,23 @@
       <c r="R14" s="1">
         <v>12</v>
       </c>
-      <c r="S14" s="1" t="s">
+      <c r="S14" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="T14" s="4">
+        <v>14</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="V14" s="4">
+        <v>12</v>
+      </c>
+      <c r="W14" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="56.25">
+    <row r="15" spans="1:23" ht="56.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1599,11 +1919,11 @@
       <c r="R15" s="1">
         <v>14</v>
       </c>
-      <c r="S15" s="1" t="s">
+      <c r="W15" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="56.25">
+    <row r="16" spans="1:23" ht="67.5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1656,11 +1976,23 @@
       <c r="R16" s="1">
         <v>14</v>
       </c>
-      <c r="S16" t="s">
+      <c r="S16" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="T16" s="4">
+        <v>14</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="V16" s="4">
+        <v>14</v>
+      </c>
+      <c r="W16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="56.25">
+    <row r="17" spans="1:23" ht="67.5">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1713,11 +2045,23 @@
       <c r="R17" s="1">
         <v>14</v>
       </c>
-      <c r="S17" t="s">
+      <c r="S17" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="T17" s="4">
+        <v>14</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="V17" s="4">
+        <v>14</v>
+      </c>
+      <c r="W17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="56.25">
+    <row r="18" spans="1:23" ht="67.5">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1769,11 +2113,23 @@
       <c r="R18" s="1">
         <v>14</v>
       </c>
-      <c r="S18" t="s">
+      <c r="S18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="T18" s="4">
+        <v>14</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="V18" s="4">
+        <v>14</v>
+      </c>
+      <c r="W18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="56.25">
+    <row r="19" spans="1:23" ht="67.5">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1826,11 +2182,23 @@
       <c r="R19" s="1">
         <v>14</v>
       </c>
-      <c r="S19" t="s">
+      <c r="S19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="T19" s="4">
+        <v>14</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="V19" s="4">
+        <v>14</v>
+      </c>
+      <c r="W19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="56.25">
+    <row r="20" spans="1:23" ht="67.5">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1882,11 +2250,23 @@
       <c r="R20" s="1">
         <v>14</v>
       </c>
-      <c r="S20" t="s">
+      <c r="S20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="T20" s="4">
+        <v>14</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="V20" s="4">
+        <v>14</v>
+      </c>
+      <c r="W20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="257.25" customHeight="1">
+    <row r="21" spans="1:23" ht="257.25" customHeight="1">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1941,11 +2321,23 @@
       <c r="R21" s="1">
         <v>10</v>
       </c>
-      <c r="S21" s="1" t="s">
+      <c r="S21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="T21" s="4">
+        <v>14</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="V21" s="4">
+        <v>12</v>
+      </c>
+      <c r="W21" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="409.5">
+    <row r="22" spans="1:23" ht="409.6">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1997,56 +2389,68 @@
       <c r="R22">
         <v>12</v>
       </c>
-      <c r="S22" s="1" t="s">
+      <c r="S22" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="T22" s="4">
+        <v>12</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="V22" s="4">
+        <v>14</v>
+      </c>
+      <c r="W22" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:23">
       <c r="A23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:23">
       <c r="A24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:23">
       <c r="A25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:23">
       <c r="A26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:23">
       <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:23">
       <c r="A28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:23">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:23">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:23">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:23">
       <c r="A32">
         <v>30</v>
       </c>
@@ -6851,22 +7255,22 @@
         <v>990</v>
       </c>
     </row>
-    <row r="993" spans="1:19">
+    <row r="993" spans="1:23">
       <c r="A993">
         <v>991</v>
       </c>
     </row>
-    <row r="994" spans="1:19">
+    <row r="994" spans="1:23">
       <c r="A994">
         <v>992</v>
       </c>
     </row>
-    <row r="995" spans="1:19">
+    <row r="995" spans="1:23">
       <c r="A995">
         <v>993</v>
       </c>
     </row>
-    <row r="996" spans="1:19">
+    <row r="996" spans="1:23" ht="34.5">
       <c r="A996">
         <v>994</v>
       </c>
@@ -6918,11 +7322,23 @@
       <c r="R996">
         <v>14</v>
       </c>
-      <c r="S996" t="s">
+      <c r="S996" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="T996" s="4">
+        <v>14</v>
+      </c>
+      <c r="U996" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="V996" s="4">
+        <v>14</v>
+      </c>
+      <c r="W996" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="997" spans="1:19" ht="93.75">
+    <row r="997" spans="1:23" ht="93.75">
       <c r="A997">
         <v>995</v>
       </c>
@@ -6977,11 +7393,23 @@
       <c r="R997">
         <v>14</v>
       </c>
-      <c r="S997" s="1" t="s">
+      <c r="S997" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="T997" s="4">
+        <v>14</v>
+      </c>
+      <c r="U997" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="V997" s="4">
+        <v>14</v>
+      </c>
+      <c r="W997" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="998" spans="1:19" ht="75">
+    <row r="998" spans="1:23" ht="75">
       <c r="A998">
         <v>996</v>
       </c>
@@ -7033,11 +7461,23 @@
       <c r="R998">
         <v>14</v>
       </c>
-      <c r="S998" s="1" t="s">
+      <c r="S998" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="T998" s="4">
+        <v>14</v>
+      </c>
+      <c r="U998" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="V998" s="4">
+        <v>14</v>
+      </c>
+      <c r="W998" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="999" spans="1:19" ht="75">
+    <row r="999" spans="1:23" ht="75">
       <c r="A999">
         <v>997</v>
       </c>
@@ -7089,11 +7529,23 @@
       <c r="R999">
         <v>14</v>
       </c>
-      <c r="S999" s="1" t="s">
+      <c r="S999" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="T999" s="4">
+        <v>14</v>
+      </c>
+      <c r="U999" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="V999" s="4">
+        <v>14</v>
+      </c>
+      <c r="W999" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="1000" spans="1:19" ht="75">
+    <row r="1000" spans="1:23" ht="75">
       <c r="A1000">
         <v>998</v>
       </c>
@@ -7145,11 +7597,23 @@
       <c r="R1000">
         <v>14</v>
       </c>
-      <c r="S1000" s="1" t="s">
+      <c r="S1000" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="T1000" s="4">
+        <v>14</v>
+      </c>
+      <c r="U1000" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="V1000" s="4">
+        <v>14</v>
+      </c>
+      <c r="W1000" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="1001" spans="1:19">
+    <row r="1001" spans="1:23" ht="34.5">
       <c r="A1001">
         <v>999</v>
       </c>
@@ -7201,11 +7665,23 @@
       <c r="R1001">
         <v>14</v>
       </c>
-      <c r="S1001" t="s">
+      <c r="S1001" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="T1001" s="4">
+        <v>14</v>
+      </c>
+      <c r="U1001" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="V1001" s="4">
+        <v>14</v>
+      </c>
+      <c r="W1001" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="1002" spans="1:19">
+    <row r="1002" spans="1:23" ht="34.5">
       <c r="A1002">
         <v>1000</v>
       </c>
@@ -7253,6 +7729,18 @@
       </c>
       <c r="Q1002" t="s">
         <v>62</v>
+      </c>
+      <c r="S1002" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="T1002" s="4">
+        <v>0</v>
+      </c>
+      <c r="U1002" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="V1002" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC88FBC1-BDD7-4286-B067-FAA131613AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B74A43-001A-4694-9C1A-C51FBFD1E219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="195">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -678,12 +678,135 @@
     <t>itemDescriptionSizeChinese01</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>公園驚現少年屍體</t>
+  </si>
+  <si>
+    <t>快訊！公園驚現少年屍體！…兇器究竟為何物？
+●月×日凌晨，市內△△公園附近發現一具少年（推測年齡12-14歲）遺體。案發現場位於當地居民熟悉的步道旁，是一名晨間散步的路人發現的。
+遺體上未見明顯外傷，警方稱「是否為刑事案件尚不明確」。此外據辦案人員透露，現場附近似乎並未發現兇器。
+少年的身份目前仍未查明，警方正在向當地居民展開走訪調查。
+案件偵破進展困難，後續報道值得關注。</t>
+  </si>
+  <si>
+    <t>安眠藥</t>
+  </si>
+  <si>
+    <t>睡前1～2小時服用即可消除睡眠不足的強效安眠藥。</t>
+  </si>
+  <si>
+    <t>帶有鋒利刀刃的老舊小刀。</t>
+  </si>
+  <si>
+    <t>錘子</t>
+  </si>
+  <si>
+    <t>厚重的鐵製錘子。</t>
+  </si>
+  <si>
+    <t>繩子</t>
+  </si>
+  <si>
+    <t>一根粗壯結實、末端已經磨損的繩子。</t>
+  </si>
+  <si>
+    <t>一名男子在自家中被殺害。頭部有遭受猛烈毆打的痕跡，警方懷疑是鈍器行兇，已展開調查。</t>
+  </si>
+  <si>
+    <t>斧頭</t>
+  </si>
+  <si>
+    <t>比外表看起來更加缺口累累的沉重斧頭。</t>
+  </si>
+  <si>
+    <t>耐力增強劑</t>
+  </si>
+  <si>
+    <t>使用道具：在一定時間內降低玩家的耐力消耗，並提高耐力恢復量。</t>
+  </si>
+  <si>
+    <t>神秘的羅盤</t>
+  </si>
+  <si>
+    <t>指標使用了藍玉的碎片製成，會一直指向裁決之藍玉所在的方向。</t>
+  </si>
+  <si>
+    <t>醫院病床模型</t>
+  </si>
+  <si>
+    <t>鐵路道口模型</t>
+  </si>
+  <si>
+    <t>模型背面刻有「轢」字。</t>
+  </si>
+  <si>
+    <t>倒塌大樓模型</t>
+  </si>
+  <si>
+    <t>模型背面刻有「壓」字。</t>
+  </si>
+  <si>
+    <t>壁爐模型</t>
+  </si>
+  <si>
+    <t>模型背面刻有「燒」字。</t>
+  </si>
+  <si>
+    <t>對前方附近的徘徊者使用後，可使其在一定時間內畏縮而無法行動。不過會發出很大的聲響。</t>
+  </si>
+  <si>
+    <t>關於一位摯友的故事</t>
+  </si>
+  <si>
+    <t>致曾經的摯友：
+還記得小時候，我們總是一起在附近的△△公園玩耍嗎？
+「我們會永遠在一起哦」
+那天你在公園長椅上說的這句話，我至今仍歷歷在目。
+可是，隨著季節一次次流逝，你能來公園的日子卻越來越少……。
+最後一次見面時，早已冰冷的你靜靜地躺著，一動也不動，也再沒能用那如往常般溫柔的聲音喚我的名字…。
+你離開後的這些日子，我一直強忍著煎熬活到現在，但已經痛苦到了極限。
+所以，我也要到你那邊去了。</t>
+  </si>
+  <si>
+    <t>測試用使用道具02</t>
+  </si>
+  <si>
+    <t>測試用使用道具01</t>
+  </si>
+  <si>
+    <t>測試用神秘物品02</t>
+  </si>
+  <si>
+    <t>測試用神秘物品01</t>
+  </si>
+  <si>
+    <t>測試用檔案道具</t>
+  </si>
+  <si>
+    <t>測試用道具</t>
+  </si>
+  <si>
+    <t>itemNameChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>itemNameSizeChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>itemDescriptionChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>itemDescriptionSizeChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -703,6 +826,12 @@
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -725,7 +854,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -737,6 +866,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1017,7 +1150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W1002"/>
+  <dimension ref="A1:AA1002"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -1041,9 +1174,13 @@
     <col min="20" max="20" width="24.875" customWidth="1"/>
     <col min="21" max="21" width="26.375" customWidth="1"/>
     <col min="22" max="22" width="32" customWidth="1"/>
+    <col min="23" max="23" width="19" customWidth="1"/>
+    <col min="24" max="24" width="22.5" customWidth="1"/>
+    <col min="25" max="25" width="23.625" customWidth="1"/>
+    <col min="26" max="26" width="28.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1111,16 +1248,28 @@
         <v>158</v>
       </c>
       <c r="W1" t="s">
+        <v>191</v>
+      </c>
+      <c r="X1" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>194</v>
+      </c>
+      <c r="AA1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:23" ht="409.6">
+    <row r="3" spans="1:27" ht="409.6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1184,11 +1333,23 @@
       <c r="V3" s="4">
         <v>13</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="W3" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="X3" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z3" s="6">
+        <v>13</v>
+      </c>
+      <c r="AA3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="228" customHeight="1">
+    <row r="4" spans="1:27" ht="228" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1252,11 +1413,23 @@
       <c r="V4" s="4">
         <v>14</v>
       </c>
-      <c r="W4" t="s">
+      <c r="W4" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="X4" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z4" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="92.25" customHeight="1">
+    <row r="5" spans="1:27" ht="92.25" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1320,11 +1493,23 @@
       <c r="V5" s="4">
         <v>14</v>
       </c>
-      <c r="W5" t="s">
+      <c r="W5" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="X5" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z5" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="34.5">
+    <row r="6" spans="1:27" ht="32.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1388,16 +1573,28 @@
       <c r="V6" s="4">
         <v>14</v>
       </c>
-      <c r="W6" t="s">
+      <c r="W6" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="X6" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="84">
+    <row r="8" spans="1:27" ht="77.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1461,11 +1658,23 @@
       <c r="V8" s="4">
         <v>14</v>
       </c>
-      <c r="W8" t="s">
+      <c r="W8" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="X8" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y8" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="Z8" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="297.75" customHeight="1">
+    <row r="9" spans="1:27" ht="297.75" customHeight="1">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1529,11 +1738,23 @@
       <c r="V9" s="4">
         <v>14</v>
       </c>
-      <c r="W9" s="1" t="s">
+      <c r="W9" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="X9" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y9" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z9" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA9" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="84">
+    <row r="10" spans="1:27" ht="77.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1597,11 +1818,23 @@
       <c r="V10" s="4">
         <v>14</v>
       </c>
-      <c r="W10" t="s">
+      <c r="W10" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="X10" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y10" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z10" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="37.5">
+    <row r="11" spans="1:27" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1665,11 +1898,23 @@
       <c r="V11" s="4">
         <v>14</v>
       </c>
-      <c r="W11" s="1" t="s">
+      <c r="W11" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="X11" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y11" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA11" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="84">
+    <row r="12" spans="1:27" ht="77.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1734,11 +1979,23 @@
       <c r="V12" s="4">
         <v>14</v>
       </c>
-      <c r="W12" s="1" t="s">
+      <c r="W12" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="X12" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y12" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="Z12" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="225" customHeight="1">
+    <row r="13" spans="1:27" ht="225" customHeight="1">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1805,11 +2062,23 @@
       <c r="V13" s="4">
         <v>12</v>
       </c>
-      <c r="W13" s="1" t="s">
+      <c r="W13" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="X13" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y13" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>12</v>
+      </c>
+      <c r="AA13" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="252" customHeight="1">
+    <row r="14" spans="1:27" ht="252" customHeight="1">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1874,11 +2143,23 @@
       <c r="V14" s="4">
         <v>12</v>
       </c>
-      <c r="W14" s="1" t="s">
+      <c r="W14" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="X14" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y14" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z14" s="6">
+        <v>12</v>
+      </c>
+      <c r="AA14" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="56.25">
+    <row r="15" spans="1:27" ht="56.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1919,11 +2200,11 @@
       <c r="R15" s="1">
         <v>14</v>
       </c>
-      <c r="W15" s="1" t="s">
+      <c r="AA15" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="67.5">
+    <row r="16" spans="1:27" ht="62.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1988,11 +2269,23 @@
       <c r="V16" s="4">
         <v>14</v>
       </c>
-      <c r="W16" t="s">
+      <c r="W16" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="X16" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y16" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z16" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="67.5">
+    <row r="17" spans="1:27" ht="62.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2057,11 +2350,23 @@
       <c r="V17" s="4">
         <v>14</v>
       </c>
-      <c r="W17" t="s">
+      <c r="W17" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="X17" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y17" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z17" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="67.5">
+    <row r="18" spans="1:27" ht="62.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2125,11 +2430,23 @@
       <c r="V18" s="4">
         <v>14</v>
       </c>
-      <c r="W18" t="s">
+      <c r="W18" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="X18" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y18" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="Z18" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="67.5">
+    <row r="19" spans="1:27" ht="62.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2194,11 +2511,23 @@
       <c r="V19" s="4">
         <v>14</v>
       </c>
-      <c r="W19" t="s">
+      <c r="W19" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="X19" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y19" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z19" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="67.5">
+    <row r="20" spans="1:27" ht="62.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2262,11 +2591,23 @@
       <c r="V20" s="4">
         <v>14</v>
       </c>
-      <c r="W20" t="s">
+      <c r="W20" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="X20" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y20" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z20" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="257.25" customHeight="1">
+    <row r="21" spans="1:27" ht="257.25" customHeight="1">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2333,11 +2674,23 @@
       <c r="V21" s="4">
         <v>12</v>
       </c>
-      <c r="W21" s="1" t="s">
+      <c r="W21" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="X21" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y21" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z21" s="6">
+        <v>12</v>
+      </c>
+      <c r="AA21" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="409.6">
+    <row r="22" spans="1:27" ht="409.6">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2401,56 +2754,68 @@
       <c r="V22" s="4">
         <v>14</v>
       </c>
-      <c r="W22" s="1" t="s">
+      <c r="W22" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="X22" s="6">
+        <v>12</v>
+      </c>
+      <c r="Y22" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z22" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA22" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:27">
       <c r="A23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:27">
       <c r="A24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:27">
       <c r="A25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:27">
       <c r="A26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:27">
       <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:27">
       <c r="A28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:27">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:27">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:27">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:27">
       <c r="A32">
         <v>30</v>
       </c>
@@ -7255,22 +7620,22 @@
         <v>990</v>
       </c>
     </row>
-    <row r="993" spans="1:23">
+    <row r="993" spans="1:27">
       <c r="A993">
         <v>991</v>
       </c>
     </row>
-    <row r="994" spans="1:23">
+    <row r="994" spans="1:27">
       <c r="A994">
         <v>992</v>
       </c>
     </row>
-    <row r="995" spans="1:23">
+    <row r="995" spans="1:27">
       <c r="A995">
         <v>993</v>
       </c>
     </row>
-    <row r="996" spans="1:23" ht="34.5">
+    <row r="996" spans="1:27" ht="32.25">
       <c r="A996">
         <v>994</v>
       </c>
@@ -7334,11 +7699,23 @@
       <c r="V996" s="4">
         <v>14</v>
       </c>
-      <c r="W996" t="s">
+      <c r="W996" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="X996" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y996" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z996" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA996" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="997" spans="1:23" ht="93.75">
+    <row r="997" spans="1:27" ht="93.75">
       <c r="A997">
         <v>995</v>
       </c>
@@ -7405,11 +7782,23 @@
       <c r="V997" s="4">
         <v>14</v>
       </c>
-      <c r="W997" s="1" t="s">
+      <c r="W997" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="X997" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y997" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="Z997" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA997" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="998" spans="1:23" ht="75">
+    <row r="998" spans="1:27" ht="75">
       <c r="A998">
         <v>996</v>
       </c>
@@ -7473,11 +7862,23 @@
       <c r="V998" s="4">
         <v>14</v>
       </c>
-      <c r="W998" s="1" t="s">
+      <c r="W998" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="X998" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y998" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z998" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA998" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="999" spans="1:23" ht="75">
+    <row r="999" spans="1:27" ht="75">
       <c r="A999">
         <v>997</v>
       </c>
@@ -7541,11 +7942,23 @@
       <c r="V999" s="4">
         <v>14</v>
       </c>
-      <c r="W999" s="1" t="s">
+      <c r="W999" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="X999" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y999" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z999" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA999" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="1000" spans="1:23" ht="75">
+    <row r="1000" spans="1:27" ht="75">
       <c r="A1000">
         <v>998</v>
       </c>
@@ -7609,11 +8022,23 @@
       <c r="V1000" s="4">
         <v>14</v>
       </c>
-      <c r="W1000" s="1" t="s">
+      <c r="W1000" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="X1000" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y1000" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="Z1000" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA1000" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="1001" spans="1:23" ht="34.5">
+    <row r="1001" spans="1:27" ht="32.25">
       <c r="A1001">
         <v>999</v>
       </c>
@@ -7677,11 +8102,23 @@
       <c r="V1001" s="4">
         <v>14</v>
       </c>
-      <c r="W1001" t="s">
+      <c r="W1001" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="X1001" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y1001" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="Z1001" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA1001" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="1002" spans="1:23" ht="34.5">
+    <row r="1002" spans="1:27" ht="32.25">
       <c r="A1002">
         <v>1000</v>
       </c>
@@ -7740,6 +8177,18 @@
         <v>154</v>
       </c>
       <c r="V1002" s="4">
+        <v>0</v>
+      </c>
+      <c r="W1002" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="X1002" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y1002" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z1002" s="6">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B74A43-001A-4694-9C1A-C51FBFD1E219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38229D59-945E-459D-AEA5-BBD8E1F8DD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="237">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -800,6 +800,143 @@
   <si>
     <t>itemDescriptionSizeChinese02</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>itemNameSpanish</t>
+  </si>
+  <si>
+    <t>itemNameSizeSpanish</t>
+  </si>
+  <si>
+    <t>itemDescriptionSpanish</t>
+  </si>
+  <si>
+    <t>itemDescriptionSizeSpanish</t>
+  </si>
+  <si>
+    <t>Cadáver de un niño en el parque</t>
+  </si>
+  <si>
+    <t>¡Última hora! ¡Han hallado el cadáver de un niño en un parque! ¿Cuál fue el arma homicida?
+En la madrugada del [mes] [día], se encontró el cuerpo sin vida de un niño (de entre 12 y 14 años, según las estimaciones) cerca del parque △△, en la ciudad. El lugar de los hechos se encuentra junto a un sendero muy frecuentado por los vecinos, y fue un transeúnte que paseaba por la mañana quien descubrió el cadáver.
+El cuerpo no presentaba heridas visibles, por lo que las autoridades afirman que «aún no está claro si se trata de un crimen». Además, según los investigadores, no se ha hallado ningún arma cerca del lugar.
+La identidad del niño sigue sin determinarse, y la policía continúa interrogando a los vecinos de la zona.
+La investigación avanza con dificultad, pero se esperan nuevas novedades próximamente.</t>
+  </si>
+  <si>
+    <t>Pastillas para dormir</t>
+  </si>
+  <si>
+    <t>Un potente somnífero que alivia la falta de sueño si se toma entre 1 y 2 horas antes de acostarse.</t>
+  </si>
+  <si>
+    <t>Cuchillo</t>
+  </si>
+  <si>
+    <t>Un cuchillo viejo con una hoja afilada.</t>
+  </si>
+  <si>
+    <t>Martillo</t>
+  </si>
+  <si>
+    <t>Un pesado martillo de hierro.</t>
+  </si>
+  <si>
+    <t>Cuerda</t>
+  </si>
+  <si>
+    <t>Una cuerda gruesa y resistente con los extremos deshilachados.</t>
+  </si>
+  <si>
+    <t>Tutorial</t>
+  </si>
+  <si>
+    <t>Un hombre fue asesinado en su propia casa. Presentaba fuertes golpes en la cabeza, por lo que la policía sospecha que se usó un objeto contundente y ha iniciado la investigación.</t>
+  </si>
+  <si>
+    <t>Hacha</t>
+  </si>
+  <si>
+    <t>Un hacha pesada, más mellada de lo que aparenta.</t>
+  </si>
+  <si>
+    <t>Potenciador de resistencia</t>
+  </si>
+  <si>
+    <t>Al usarlo: durante un tiempo, reduce el consumo de resistencia del jugador y aumenta su recuperación.</t>
+  </si>
+  <si>
+    <t>Brújula misteriosa</t>
+  </si>
+  <si>
+    <t>Su aguja está hecha con un fragmento de la Esfera Azul, por lo que siempre señala la dirección donde se encuentra una Esfera Azul del Juicio.</t>
+  </si>
+  <si>
+    <t>Miniatura de cama de hospital</t>
+  </si>
+  <si>
+    <t>En la parte trasera de la miniatura está grabado el carácter «enfermedad».</t>
+  </si>
+  <si>
+    <t>Miniatura de paso a nivel</t>
+  </si>
+  <si>
+    <t>En la parte trasera de la miniatura está grabado el carácter «atropello».</t>
+  </si>
+  <si>
+    <t>Miniatura de un edificio derrumbado</t>
+  </si>
+  <si>
+    <t>En la parte trasera de la miniatura está grabado el carácter «aplastamiento».</t>
+  </si>
+  <si>
+    <t>Miniatura de chimenea</t>
+  </si>
+  <si>
+    <t>En la parte trasera de la miniatura está grabado el carácter «quemadura».</t>
+  </si>
+  <si>
+    <t>Miniatura de piscina</t>
+  </si>
+  <si>
+    <t>En la parte trasera de la miniatura está grabado el carácter «ahogamiento».</t>
+  </si>
+  <si>
+    <t>Petardo</t>
+  </si>
+  <si>
+    <t>Al usarlo contra un Errante cercano, este se queda aturdido y no puede actuar durante un tiempo. Sin embargo, produce un ruido muy fuerte.</t>
+  </si>
+  <si>
+    <t>Una historia sobre un buen amigo</t>
+  </si>
+  <si>
+    <t>Para mi querido amigo:
+¿Recuerdas cuando de pequeños siempre jugábamos juntos en el parque △△ cercano?
+«Estaremos juntos para siempre»
+Todavía recuerdo con total claridad esas palabras que me dijiste aquel día, sentado en el banco del parque.
+Pero, a medida que pasaban las estaciones, los días en que podías venir al parque se hicieron cada vez menos frecuentes...
+La última vez que nos vimos, estabas tendido, frío, sin moverte lo más mínimo, y ya no volviste a llamarme por mi nombre con aquella voz tan dulce de siempre...
+He soportado los días desde que te fuiste, pero el dolor ha llegado a su límite.
+Así que yo también voy a reunirme contigo.</t>
+  </si>
+  <si>
+    <t>Objeto de uso de prueba 02</t>
+  </si>
+  <si>
+    <t>Objeto de uso de prueba 01</t>
+  </si>
+  <si>
+    <t>Objeto Misterioso de prueba 02</t>
+  </si>
+  <si>
+    <t>Objeto Misterioso de prueba 01</t>
+  </si>
+  <si>
+    <t>Documento de prueba</t>
+  </si>
+  <si>
+    <t>Objeto de prueba</t>
   </si>
 </sst>
 </file>
@@ -1150,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA1002"/>
+  <dimension ref="A1:AE1002"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -1178,9 +1315,13 @@
     <col min="24" max="24" width="22.5" customWidth="1"/>
     <col min="25" max="25" width="23.625" customWidth="1"/>
     <col min="26" max="26" width="28.375" customWidth="1"/>
+    <col min="27" max="27" width="21" customWidth="1"/>
+    <col min="28" max="28" width="23.125" customWidth="1"/>
+    <col min="29" max="29" width="24.875" customWidth="1"/>
+    <col min="30" max="30" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1260,16 +1401,28 @@
         <v>194</v>
       </c>
       <c r="AA1" t="s">
+        <v>195</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>196</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>197</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AE1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:31">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:27" ht="409.6">
+    <row r="3" spans="1:31" ht="409.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1346,10 +1499,22 @@
         <v>13</v>
       </c>
       <c r="AA3" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="AB3">
+        <v>12</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AD3">
+        <v>11</v>
+      </c>
+      <c r="AE3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="228" customHeight="1">
+    <row r="4" spans="1:31" ht="228" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1426,10 +1591,22 @@
         <v>14</v>
       </c>
       <c r="AA4" t="s">
+        <v>201</v>
+      </c>
+      <c r="AB4">
+        <v>14</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="AD4">
+        <v>14</v>
+      </c>
+      <c r="AE4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="92.25" customHeight="1">
+    <row r="5" spans="1:31" ht="92.25" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1506,10 +1683,22 @@
         <v>14</v>
       </c>
       <c r="AA5" t="s">
+        <v>203</v>
+      </c>
+      <c r="AB5">
+        <v>14</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="AD5">
+        <v>14</v>
+      </c>
+      <c r="AE5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="32.25">
+    <row r="6" spans="1:31" ht="75">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1586,15 +1775,27 @@
         <v>14</v>
       </c>
       <c r="AA6" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB6">
+        <v>14</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="AD6">
+        <v>14</v>
+      </c>
+      <c r="AE6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:31">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="77.25">
+    <row r="8" spans="1:31" ht="150">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1671,10 +1872,22 @@
         <v>14</v>
       </c>
       <c r="AA8" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB8">
+        <v>14</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="AD8">
+        <v>14</v>
+      </c>
+      <c r="AE8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="297.75" customHeight="1">
+    <row r="9" spans="1:31" ht="297.75" customHeight="1">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1751,10 +1964,22 @@
         <v>14</v>
       </c>
       <c r="AA9" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB9">
+        <v>14</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="AD9">
+        <v>14</v>
+      </c>
+      <c r="AE9" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="77.25">
+    <row r="10" spans="1:31" ht="112.5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1831,10 +2056,22 @@
         <v>14</v>
       </c>
       <c r="AA10" t="s">
+        <v>211</v>
+      </c>
+      <c r="AB10">
+        <v>14</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD10">
+        <v>14</v>
+      </c>
+      <c r="AE10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="37.5">
+    <row r="11" spans="1:31" ht="75">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1910,11 +2147,23 @@
       <c r="Z11" s="6">
         <v>14</v>
       </c>
-      <c r="AA11" s="1" t="s">
+      <c r="AA11" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB11">
+        <v>14</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="AD11">
+        <v>14</v>
+      </c>
+      <c r="AE11" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="77.25">
+    <row r="12" spans="1:31" ht="150">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1991,11 +2240,23 @@
       <c r="Z12" s="6">
         <v>14</v>
       </c>
-      <c r="AA12" s="1" t="s">
+      <c r="AA12" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB12">
+        <v>14</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="AD12">
+        <v>14</v>
+      </c>
+      <c r="AE12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="225" customHeight="1">
+    <row r="13" spans="1:31" ht="225" customHeight="1">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2074,11 +2335,23 @@
       <c r="Z13" s="6">
         <v>12</v>
       </c>
-      <c r="AA13" s="1" t="s">
+      <c r="AA13" t="s">
+        <v>213</v>
+      </c>
+      <c r="AB13">
+        <v>14</v>
+      </c>
+      <c r="AC13" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="AD13">
+        <v>10</v>
+      </c>
+      <c r="AE13" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="252" customHeight="1">
+    <row r="14" spans="1:31" ht="252" customHeight="1">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2156,10 +2429,22 @@
         <v>12</v>
       </c>
       <c r="AA14" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB14">
+        <v>14</v>
+      </c>
+      <c r="AC14" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="AD14">
+        <v>12</v>
+      </c>
+      <c r="AE14" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="56.25">
+    <row r="15" spans="1:31" ht="56.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2200,11 +2485,11 @@
       <c r="R15" s="1">
         <v>14</v>
       </c>
-      <c r="AA15" s="1" t="s">
+      <c r="AE15" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="62.25">
+    <row r="16" spans="1:31" ht="206.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2281,11 +2566,23 @@
       <c r="Z16" s="6">
         <v>14</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="AA16" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="AB16">
+        <v>14</v>
+      </c>
+      <c r="AC16" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="AD16">
+        <v>14</v>
+      </c>
+      <c r="AE16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="62.25">
+    <row r="17" spans="1:31" ht="206.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2362,11 +2659,23 @@
       <c r="Z17" s="6">
         <v>14</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="AA17" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB17">
+        <v>14</v>
+      </c>
+      <c r="AC17" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="AD17">
+        <v>14</v>
+      </c>
+      <c r="AE17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="62.25">
+    <row r="18" spans="1:31" ht="206.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2442,11 +2751,23 @@
       <c r="Z18" s="6">
         <v>14</v>
       </c>
-      <c r="AA18" t="s">
+      <c r="AA18" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB18">
+        <v>12</v>
+      </c>
+      <c r="AC18" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="AD18">
+        <v>14</v>
+      </c>
+      <c r="AE18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="62.25">
+    <row r="19" spans="1:31" ht="206.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2523,11 +2844,23 @@
       <c r="Z19" s="6">
         <v>14</v>
       </c>
-      <c r="AA19" t="s">
+      <c r="AA19" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB19">
+        <v>14</v>
+      </c>
+      <c r="AC19" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="AD19">
+        <v>14</v>
+      </c>
+      <c r="AE19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="62.25">
+    <row r="20" spans="1:31" ht="206.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2603,11 +2936,23 @@
       <c r="Z20" s="6">
         <v>14</v>
       </c>
-      <c r="AA20" t="s">
+      <c r="AA20" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="AB20">
+        <v>12</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD20">
+        <v>14</v>
+      </c>
+      <c r="AE20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="257.25" customHeight="1">
+    <row r="21" spans="1:31" ht="257.25" customHeight="1">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2687,10 +3032,22 @@
         <v>12</v>
       </c>
       <c r="AA21" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="AB21">
+        <v>14</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="AD21">
+        <v>10</v>
+      </c>
+      <c r="AE21" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="409.6">
+    <row r="22" spans="1:31" ht="409.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2767,55 +3124,67 @@
         <v>14</v>
       </c>
       <c r="AA22" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB22">
+        <v>12</v>
+      </c>
+      <c r="AC22" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="AD22">
+        <v>12</v>
+      </c>
+      <c r="AE22" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:31">
       <c r="A23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:31">
       <c r="A24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:31">
       <c r="A25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:31">
       <c r="A26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:31">
       <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:31">
       <c r="A28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:31">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:31">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:31">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:31">
       <c r="A32">
         <v>30</v>
       </c>
@@ -7620,22 +7989,22 @@
         <v>990</v>
       </c>
     </row>
-    <row r="993" spans="1:27">
+    <row r="993" spans="1:31">
       <c r="A993">
         <v>991</v>
       </c>
     </row>
-    <row r="994" spans="1:27">
+    <row r="994" spans="1:31">
       <c r="A994">
         <v>992</v>
       </c>
     </row>
-    <row r="995" spans="1:27">
+    <row r="995" spans="1:31">
       <c r="A995">
         <v>993</v>
       </c>
     </row>
-    <row r="996" spans="1:27" ht="32.25">
+    <row r="996" spans="1:31">
       <c r="A996">
         <v>994</v>
       </c>
@@ -7712,10 +8081,22 @@
         <v>14</v>
       </c>
       <c r="AA996" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB996">
+        <v>14</v>
+      </c>
+      <c r="AC996" t="s">
+        <v>231</v>
+      </c>
+      <c r="AD996">
+        <v>14</v>
+      </c>
+      <c r="AE996" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="997" spans="1:27" ht="93.75">
+    <row r="997" spans="1:31" ht="93.75">
       <c r="A997">
         <v>995</v>
       </c>
@@ -7794,11 +8175,23 @@
       <c r="Z997" s="6">
         <v>14</v>
       </c>
-      <c r="AA997" s="1" t="s">
+      <c r="AA997" t="s">
+        <v>144</v>
+      </c>
+      <c r="AB997">
+        <v>14</v>
+      </c>
+      <c r="AC997" t="s">
+        <v>232</v>
+      </c>
+      <c r="AD997">
+        <v>14</v>
+      </c>
+      <c r="AE997" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="998" spans="1:27" ht="75">
+    <row r="998" spans="1:31" ht="93.75">
       <c r="A998">
         <v>996</v>
       </c>
@@ -7874,11 +8267,23 @@
       <c r="Z998" s="6">
         <v>14</v>
       </c>
-      <c r="AA998" s="1" t="s">
+      <c r="AA998" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB998">
+        <v>14</v>
+      </c>
+      <c r="AC998" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="AD998">
+        <v>14</v>
+      </c>
+      <c r="AE998" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="999" spans="1:27" ht="75">
+    <row r="999" spans="1:31" ht="93.75">
       <c r="A999">
         <v>997</v>
       </c>
@@ -7954,11 +8359,23 @@
       <c r="Z999" s="6">
         <v>14</v>
       </c>
-      <c r="AA999" s="1" t="s">
+      <c r="AA999" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB999">
+        <v>14</v>
+      </c>
+      <c r="AC999" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="AD999">
+        <v>14</v>
+      </c>
+      <c r="AE999" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="1000" spans="1:27" ht="75">
+    <row r="1000" spans="1:31" ht="75">
       <c r="A1000">
         <v>998</v>
       </c>
@@ -8035,10 +8452,22 @@
         <v>14</v>
       </c>
       <c r="AA1000" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AB1000">
+        <v>14</v>
+      </c>
+      <c r="AC1000" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AD1000">
+        <v>14</v>
+      </c>
+      <c r="AE1000" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="1001" spans="1:27" ht="32.25">
+    <row r="1001" spans="1:31">
       <c r="A1001">
         <v>999</v>
       </c>
@@ -8115,10 +8544,22 @@
         <v>14</v>
       </c>
       <c r="AA1001" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB1001">
+        <v>14</v>
+      </c>
+      <c r="AC1001" t="s">
+        <v>236</v>
+      </c>
+      <c r="AD1001">
+        <v>14</v>
+      </c>
+      <c r="AE1001" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="1002" spans="1:27" ht="32.25">
+    <row r="1002" spans="1:31">
       <c r="A1002">
         <v>1000</v>
       </c>
@@ -8190,6 +8631,15 @@
       </c>
       <c r="Z1002" s="6">
         <v>0</v>
+      </c>
+      <c r="AA1002" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB1002">
+        <v>0</v>
+      </c>
+      <c r="AC1002" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38229D59-945E-459D-AEA5-BBD8E1F8DD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D5AF72-87D9-49C7-A190-72BED2D01AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="276">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -937,6 +937,134 @@
   </si>
   <si>
     <t>Objeto de prueba</t>
+  </si>
+  <si>
+    <t>itemNamePortuguese</t>
+  </si>
+  <si>
+    <t>itemNameSizePortuguese</t>
+  </si>
+  <si>
+    <t>itemDescriptionPortuguese</t>
+  </si>
+  <si>
+    <t>itemDescriptionSizePortuguese</t>
+  </si>
+  <si>
+    <t>Corpo de um garoto encontrado no parque</t>
+  </si>
+  <si>
+    <t>Última hora! Corpo de um garoto é encontrado em um parque! Qual foi a arma do crime?
+Na madrugada de [mês] [dia], o corpo sem vida de um garoto (com idade estimada entre 12 e 14 anos) foi encontrado perto do parque △△, na cidade. O local fica ao lado de uma trilha muito frequentada pelos moradores da região, e o corpo foi descoberto por um transeunte durante uma caminhada matinal.
+O corpo não apresentava ferimentos visíveis, e as autoridades afirmam que «ainda não está claro se houve crime». Além disso, segundo os investigadores, nenhuma arma foi encontrada nas proximidades do local.
+A identidade do garoto ainda não foi determinada, e a polícia está conduzindo buscas junto aos moradores da região.
+A investigação está avançando com dificuldade, mas novas atualizações são aguardadas.</t>
+  </si>
+  <si>
+    <t>Comprimidos para dormir</t>
+  </si>
+  <si>
+    <t>Um forte sonífero que alivia a privação de sono quando tomado de 1 a 2 horas antes de dormir.</t>
+  </si>
+  <si>
+    <t>Faca</t>
+  </si>
+  <si>
+    <t>Uma faca antiga com uma lâmina afiada.</t>
+  </si>
+  <si>
+    <t>Martelo</t>
+  </si>
+  <si>
+    <t>Um martelo pesado de ferro.</t>
+  </si>
+  <si>
+    <t>Corda</t>
+  </si>
+  <si>
+    <t>Uma corda grossa e resistente, com as pontas desfiadas.</t>
+  </si>
+  <si>
+    <t>Um homem foi encontrado assassinado em sua própria casa. Havia sinais de golpes violentos na cabeça, e a polícia iniciou uma investigação suspeitando do uso de um objeto contundente.</t>
+  </si>
+  <si>
+    <t>Machado</t>
+  </si>
+  <si>
+    <t>Um machado pesado, com mais rachaduras do que aparenta.</t>
+  </si>
+  <si>
+    <t>Reforço de resistência</t>
+  </si>
+  <si>
+    <t>Ao usar: reduz o consumo de resistência do jogador por um determinado tempo e aumenta a taxa de recuperação de resistência.</t>
+  </si>
+  <si>
+    <t>Bússola misteriosa</t>
+  </si>
+  <si>
+    <t>A agulha é feita com um fragmento da Esfera Azul; ela sempre aponta na direção onde existe uma Esfera Azul do Julgamento.</t>
+  </si>
+  <si>
+    <t>Nas costas da miniatura está gravado o caractere «Doença».</t>
+  </si>
+  <si>
+    <t>Miniatura de passagem de nível</t>
+  </si>
+  <si>
+    <t>Nas costas da miniatura está gravado o caractere «Atropelamento».</t>
+  </si>
+  <si>
+    <t>Miniatura de prédio desmoronado</t>
+  </si>
+  <si>
+    <t>Nas costas da miniatura está gravado o caractere «Esmagamento».</t>
+  </si>
+  <si>
+    <t>Miniatura de lareira</t>
+  </si>
+  <si>
+    <t>Nas costas da miniatura está gravado o caractere «Queimadura».</t>
+  </si>
+  <si>
+    <t>Nas costas da miniatura está gravado o caractere «Afogamento».</t>
+  </si>
+  <si>
+    <t>Bombinha</t>
+  </si>
+  <si>
+    <t>Ao usar contra um Errante próximo à frente, ele fica atordoado e incapaz de agir por um determinado tempo. No entanto, isso gera um barulho muito alto.</t>
+  </si>
+  <si>
+    <t>Uma história sobre um bom amigo</t>
+  </si>
+  <si>
+    <t>Para o meu antigo melhor amigo,
+Você se lembra de que, quando éramos pequenos, sempre brincávamos juntos no parque △△ ali perto?
+«Vamos ficar juntos para sempre»
+Ainda me lembro claramente dessas palavras que você me disse naquele dia, no banco do parque.
+Mas, à medida que as estações passavam, os dias em que você podia vir ao parque foram ficando cada vez mais raros...
+Da última vez que nos vimos, você estava deitado, frio, sem se mexer nem um pouco, e nem chamou meu nome com aquela voz gentil de sempre...
+Eu aguentei firme os dias desde que você se foi, mas a dor já chegou ao limite.
+Por isso, eu também vou para aí.</t>
+  </si>
+  <si>
+    <t>Item de uso de teste 02</t>
+  </si>
+  <si>
+    <t>Item de uso de teste 01</t>
+  </si>
+  <si>
+    <t>Item Misterioso de teste 02</t>
+  </si>
+  <si>
+    <t>Item Misterioso de teste 01</t>
+  </si>
+  <si>
+    <t>Item de documento de teste</t>
+  </si>
+  <si>
+    <t>Item de teste</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE1002"/>
+  <dimension ref="A1:AI1002"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -1319,9 +1447,13 @@
     <col min="28" max="28" width="23.125" customWidth="1"/>
     <col min="29" max="29" width="24.875" customWidth="1"/>
     <col min="30" max="30" width="26" customWidth="1"/>
+    <col min="31" max="31" width="31.875" customWidth="1"/>
+    <col min="32" max="32" width="28.5" customWidth="1"/>
+    <col min="33" max="33" width="28.25" customWidth="1"/>
+    <col min="34" max="34" width="31.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1413,16 +1545,28 @@
         <v>198</v>
       </c>
       <c r="AE1" t="s">
+        <v>237</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>238</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>239</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>240</v>
+      </c>
+      <c r="AI1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:35">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:31" ht="409.5">
+    <row r="3" spans="1:35" ht="409.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1511,10 +1655,22 @@
         <v>11</v>
       </c>
       <c r="AE3" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="AF3">
+        <v>12</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="AH3">
+        <v>11</v>
+      </c>
+      <c r="AI3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="228" customHeight="1">
+    <row r="4" spans="1:35" ht="228" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1603,10 +1759,22 @@
         <v>14</v>
       </c>
       <c r="AE4" t="s">
+        <v>243</v>
+      </c>
+      <c r="AF4">
+        <v>14</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="AH4">
+        <v>14</v>
+      </c>
+      <c r="AI4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="92.25" customHeight="1">
+    <row r="5" spans="1:35" ht="92.25" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1695,10 +1863,22 @@
         <v>14</v>
       </c>
       <c r="AE5" t="s">
+        <v>245</v>
+      </c>
+      <c r="AF5">
+        <v>14</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="AH5">
+        <v>14</v>
+      </c>
+      <c r="AI5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="75">
+    <row r="6" spans="1:35" ht="75">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1787,15 +1967,27 @@
         <v>14</v>
       </c>
       <c r="AE6" t="s">
+        <v>247</v>
+      </c>
+      <c r="AF6">
+        <v>14</v>
+      </c>
+      <c r="AG6" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="AH6">
+        <v>14</v>
+      </c>
+      <c r="AI6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:35">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="150">
+    <row r="8" spans="1:35" ht="150">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1884,10 +2076,22 @@
         <v>14</v>
       </c>
       <c r="AE8" t="s">
+        <v>249</v>
+      </c>
+      <c r="AF8">
+        <v>14</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AH8">
+        <v>14</v>
+      </c>
+      <c r="AI8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="297.75" customHeight="1">
+    <row r="9" spans="1:35" ht="297.75" customHeight="1">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1976,10 +2180,22 @@
         <v>14</v>
       </c>
       <c r="AE9" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="AF9">
+        <v>14</v>
+      </c>
+      <c r="AG9" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="AH9">
+        <v>14</v>
+      </c>
+      <c r="AI9" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="112.5">
+    <row r="10" spans="1:35" ht="131.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2068,10 +2284,22 @@
         <v>14</v>
       </c>
       <c r="AE10" t="s">
+        <v>252</v>
+      </c>
+      <c r="AF10">
+        <v>14</v>
+      </c>
+      <c r="AG10" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="AH10">
+        <v>14</v>
+      </c>
+      <c r="AI10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="75">
+    <row r="11" spans="1:35" ht="75">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2159,11 +2387,23 @@
       <c r="AD11">
         <v>14</v>
       </c>
-      <c r="AE11" s="1" t="s">
+      <c r="AE11" t="s">
+        <v>247</v>
+      </c>
+      <c r="AF11">
+        <v>14</v>
+      </c>
+      <c r="AG11" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="AH11">
+        <v>14</v>
+      </c>
+      <c r="AI11" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="150">
+    <row r="12" spans="1:35" ht="150">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2252,11 +2492,23 @@
       <c r="AD12">
         <v>14</v>
       </c>
-      <c r="AE12" s="1" t="s">
+      <c r="AE12" t="s">
+        <v>249</v>
+      </c>
+      <c r="AF12">
+        <v>14</v>
+      </c>
+      <c r="AG12" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AH12">
+        <v>14</v>
+      </c>
+      <c r="AI12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="225" customHeight="1">
+    <row r="13" spans="1:35" ht="225" customHeight="1">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2347,11 +2599,23 @@
       <c r="AD13">
         <v>10</v>
       </c>
-      <c r="AE13" s="1" t="s">
+      <c r="AE13" t="s">
+        <v>254</v>
+      </c>
+      <c r="AF13">
+        <v>14</v>
+      </c>
+      <c r="AG13" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="AH13">
+        <v>10</v>
+      </c>
+      <c r="AI13" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="252" customHeight="1">
+    <row r="14" spans="1:35" ht="252" customHeight="1">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2441,10 +2705,22 @@
         <v>12</v>
       </c>
       <c r="AE14" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AF14">
+        <v>14</v>
+      </c>
+      <c r="AG14" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="AH14">
+        <v>12</v>
+      </c>
+      <c r="AI14" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="56.25">
+    <row r="15" spans="1:35" ht="56.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2485,11 +2761,11 @@
       <c r="R15" s="1">
         <v>14</v>
       </c>
-      <c r="AE15" s="1" t="s">
+      <c r="AI15" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="206.25">
+    <row r="16" spans="1:35" ht="150">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2578,11 +2854,23 @@
       <c r="AD16">
         <v>14</v>
       </c>
-      <c r="AE16" t="s">
+      <c r="AE16" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="AF16">
+        <v>14</v>
+      </c>
+      <c r="AG16" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AH16">
+        <v>14</v>
+      </c>
+      <c r="AI16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="206.25">
+    <row r="17" spans="1:35" ht="168.75">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2671,11 +2959,23 @@
       <c r="AD17">
         <v>14</v>
       </c>
-      <c r="AE17" t="s">
+      <c r="AE17" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="AF17">
+        <v>14</v>
+      </c>
+      <c r="AG17" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AH17">
+        <v>14</v>
+      </c>
+      <c r="AI17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="206.25">
+    <row r="18" spans="1:35" ht="168.75">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2763,11 +3063,23 @@
       <c r="AD18">
         <v>14</v>
       </c>
-      <c r="AE18" t="s">
+      <c r="AE18" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="AF18">
+        <v>12</v>
+      </c>
+      <c r="AG18" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="AH18">
+        <v>14</v>
+      </c>
+      <c r="AI18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="206.25">
+    <row r="19" spans="1:35" ht="168.75">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2856,11 +3168,23 @@
       <c r="AD19">
         <v>14</v>
       </c>
-      <c r="AE19" t="s">
+      <c r="AE19" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="AF19">
+        <v>14</v>
+      </c>
+      <c r="AG19" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="AH19">
+        <v>14</v>
+      </c>
+      <c r="AI19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="206.25">
+    <row r="20" spans="1:35" ht="168.75">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2948,11 +3272,23 @@
       <c r="AD20">
         <v>14</v>
       </c>
-      <c r="AE20" t="s">
+      <c r="AE20" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="AF20">
+        <v>12</v>
+      </c>
+      <c r="AG20" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="AH20">
+        <v>14</v>
+      </c>
+      <c r="AI20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="257.25" customHeight="1">
+    <row r="21" spans="1:35" ht="257.25" customHeight="1">
       <c r="A21">
         <v>19</v>
       </c>
@@ -3044,10 +3380,22 @@
         <v>10</v>
       </c>
       <c r="AE21" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="AF21">
+        <v>14</v>
+      </c>
+      <c r="AG21" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="AH21">
+        <v>10</v>
+      </c>
+      <c r="AI21" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="409.5">
+    <row r="22" spans="1:35" ht="409.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -3136,55 +3484,67 @@
         <v>12</v>
       </c>
       <c r="AE22" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="AF22">
+        <v>12</v>
+      </c>
+      <c r="AG22" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="AH22">
+        <v>12</v>
+      </c>
+      <c r="AI22" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:31">
+    <row r="23" spans="1:35">
       <c r="A23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:31">
+    <row r="24" spans="1:35">
       <c r="A24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:31">
+    <row r="25" spans="1:35">
       <c r="A25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:31">
+    <row r="26" spans="1:35">
       <c r="A26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:31">
+    <row r="27" spans="1:35">
       <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:31">
+    <row r="28" spans="1:35">
       <c r="A28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:31">
+    <row r="29" spans="1:35">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:31">
+    <row r="30" spans="1:35">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:31">
+    <row r="31" spans="1:35">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:31">
+    <row r="32" spans="1:35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -7989,22 +8349,22 @@
         <v>990</v>
       </c>
     </row>
-    <row r="993" spans="1:31">
+    <row r="993" spans="1:35">
       <c r="A993">
         <v>991</v>
       </c>
     </row>
-    <row r="994" spans="1:31">
+    <row r="994" spans="1:35">
       <c r="A994">
         <v>992</v>
       </c>
     </row>
-    <row r="995" spans="1:31">
+    <row r="995" spans="1:35">
       <c r="A995">
         <v>993</v>
       </c>
     </row>
-    <row r="996" spans="1:31">
+    <row r="996" spans="1:35">
       <c r="A996">
         <v>994</v>
       </c>
@@ -8093,10 +8453,22 @@
         <v>14</v>
       </c>
       <c r="AE996" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF996">
+        <v>14</v>
+      </c>
+      <c r="AG996" t="s">
+        <v>270</v>
+      </c>
+      <c r="AH996">
+        <v>14</v>
+      </c>
+      <c r="AI996" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="997" spans="1:31" ht="93.75">
+    <row r="997" spans="1:35" ht="93.75">
       <c r="A997">
         <v>995</v>
       </c>
@@ -8187,11 +8559,23 @@
       <c r="AD997">
         <v>14</v>
       </c>
-      <c r="AE997" s="1" t="s">
+      <c r="AE997" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF997">
+        <v>14</v>
+      </c>
+      <c r="AG997" t="s">
+        <v>271</v>
+      </c>
+      <c r="AH997">
+        <v>14</v>
+      </c>
+      <c r="AI997" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="998" spans="1:31" ht="93.75">
+    <row r="998" spans="1:35" ht="75">
       <c r="A998">
         <v>996</v>
       </c>
@@ -8279,11 +8663,23 @@
       <c r="AD998">
         <v>14</v>
       </c>
-      <c r="AE998" s="1" t="s">
+      <c r="AE998" t="s">
+        <v>146</v>
+      </c>
+      <c r="AF998">
+        <v>14</v>
+      </c>
+      <c r="AG998" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="AH998">
+        <v>14</v>
+      </c>
+      <c r="AI998" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="999" spans="1:31" ht="93.75">
+    <row r="999" spans="1:35" ht="75">
       <c r="A999">
         <v>997</v>
       </c>
@@ -8371,11 +8767,23 @@
       <c r="AD999">
         <v>14</v>
       </c>
-      <c r="AE999" s="1" t="s">
+      <c r="AE999" t="s">
+        <v>148</v>
+      </c>
+      <c r="AF999">
+        <v>14</v>
+      </c>
+      <c r="AG999" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="AH999">
+        <v>14</v>
+      </c>
+      <c r="AI999" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="1000" spans="1:31" ht="75">
+    <row r="1000" spans="1:35" ht="75">
       <c r="A1000">
         <v>998</v>
       </c>
@@ -8464,10 +8872,22 @@
         <v>14</v>
       </c>
       <c r="AE1000" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AF1000">
+        <v>14</v>
+      </c>
+      <c r="AG1000" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="AH1000">
+        <v>14</v>
+      </c>
+      <c r="AI1000" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="1001" spans="1:31">
+    <row r="1001" spans="1:35">
       <c r="A1001">
         <v>999</v>
       </c>
@@ -8556,10 +8976,22 @@
         <v>14</v>
       </c>
       <c r="AE1001" t="s">
+        <v>152</v>
+      </c>
+      <c r="AF1001">
+        <v>14</v>
+      </c>
+      <c r="AG1001" t="s">
+        <v>275</v>
+      </c>
+      <c r="AH1001">
+        <v>14</v>
+      </c>
+      <c r="AI1001" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="1002" spans="1:31">
+    <row r="1002" spans="1:35">
       <c r="A1002">
         <v>1000</v>
       </c>
@@ -8639,6 +9071,15 @@
         <v>0</v>
       </c>
       <c r="AC1002" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE1002" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF1002">
+        <v>0</v>
+      </c>
+      <c r="AG1002" t="s">
         <v>154</v>
       </c>
     </row>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D5AF72-87D9-49C7-A190-72BED2D01AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2F1D83-695D-43F7-A0BD-DB1D39087019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="349">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -517,9 +517,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>公园惊现少年尸体</t>
-  </si>
-  <si>
     <t>快讯！公园惊现少年尸体！…凶器究竟为何物？
 ●月×日凌晨，市内△△公园附近发现一具少年（推测年龄12-14岁）遗体。案发现场位于当地居民熟悉的步道旁，是一名晨间散步的路人发现的。
 遗体上未见明显外伤，警方称「是否为刑事案件尚不明确」。此外据办案人员透露，现场附近似乎并未发现凶器。
@@ -679,9 +676,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>公園驚現少年屍體</t>
-  </si>
-  <si>
     <t>快訊！公園驚現少年屍體！…兇器究竟為何物？
 ●月×日凌晨，市內△△公園附近發現一具少年（推測年齡12-14歲）遺體。案發現場位於當地居民熟悉的步道旁，是一名晨間散步的路人發現的。
 遺體上未見明顯外傷，警方稱「是否為刑事案件尚不明確」。此外據辦案人員透露，現場附近似乎並未發現兇器。
@@ -814,9 +808,6 @@
     <t>itemDescriptionSizeSpanish</t>
   </si>
   <si>
-    <t>Cadáver de un niño en el parque</t>
-  </si>
-  <si>
     <t>¡Última hora! ¡Han hallado el cadáver de un niño en un parque! ¿Cuál fue el arma homicida?
 En la madrugada del [mes] [día], se encontró el cuerpo sin vida de un niño (de entre 12 y 14 años, según las estimaciones) cerca del parque △△, en la ciudad. El lugar de los hechos se encuentra junto a un sendero muy frecuentado por los vecinos, y fue un transeúnte que paseaba por la mañana quien descubrió el cadáver.
 El cuerpo no presentaba heridas visibles, por lo que las autoridades afirman que «aún no está claro si se trata de un crimen». Además, según los investigadores, no se ha hallado ningún arma cerca del lugar.
@@ -951,9 +942,6 @@
     <t>itemDescriptionSizePortuguese</t>
   </si>
   <si>
-    <t>Corpo de um garoto encontrado no parque</t>
-  </si>
-  <si>
     <t>Última hora! Corpo de um garoto é encontrado em um parque! Qual foi a arma do crime?
 Na madrugada de [mês] [dia], o corpo sem vida de um garoto (com idade estimada entre 12 e 14 anos) foi encontrado perto do parque △△, na cidade. O local fica ao lado de uma trilha muito frequentada pelos moradores da região, e o corpo foi descoberto por um transeunte durante uma caminhada matinal.
 O corpo não apresentava ferimentos visíveis, e as autoridades afirmam que «ainda não está claro se houve crime». Além disso, segundo os investigadores, nenhuma arma foi encontrada nas proximidades do local.
@@ -1066,12 +1054,410 @@
   <si>
     <t>Item de teste</t>
   </si>
+  <si>
+    <t>&lt;r="ぞくほう"&gt;続報&lt;/r&gt;！　&lt;r="こうえん"&gt; 公園&lt;/r&gt;に&lt;r="しょうねん"&gt; 少年&lt;/r&gt;の&lt;r="したい"&gt;死体&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>△△公園で発見された少年の遺体について、警察は周辺の聞き込みを進めている。
+少年の通っていた学校で関わりのある7人の生徒から聞き込みをした。少年の学校の持ち物について聞き込んだ結果、警察はこれらの証言の中から何人か嘘をついている可能性があると踏んでいる。
+A：木工加工の授業で新品のスプレーを木材に少しだけ使用した。
+B：長年使い込んだ結果、教科書が限界を迎えてボロボロになっている。
+C：上履きに針を入れている様子を見たことがある。
+D：Aと同意見。
+E：ノートは新品のため、特に使用されていない。
+F：Bと同意見。Cは嘘を言っている。
+G：Cと同意見。Aは嘘を言っている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Follow-up! Body of young boy found in park</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Police are conducting neighborhood inquiries regarding the body of a young boy found in △△ Park.
+Investigators questioned seven students who had interactions with him at school. Based on their statements regarding the boy’s school supplies, police suspect that several of them may be lying.
+A: He used a tiny bit of a brand-new spray paint on some wood during woodworking class.
+B: His textbook was falling apart at the seams after years of heavy use.
+C: I saw someone putting needles into his indoor shoes once.
+D: I agree with A.
+E: His notebook is brand new and barely used.
+F: I agree with B. C is lying.
+G: I agree with C. A is lying.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>公园惊现少年尸体</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>续报！公园惊现少年尸体</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>关于在△△公园发现的少年遗体，警方正在周边展开走访调查。
+警方对少年就读学校中与之有所交集的7名学生进行了问讯。在调查少年的随身物品时，警方根据以下证词推断，其中可能有人在说谎。
+A：他在木工课上，把全新的喷漆在木材上稍微用了一点。
+B：因为用了很久，他的教科书已经破旧不堪，快要报废了。
+C：我曾看到有人把针放进他的室内鞋里。
+D：我和A的看法一致。
+E：他的笔记本是全新的，基本没有使用过的痕迹。
+F：我和B的看法一致。C在说谎。
+G：我和C的看法一致。A在说谎。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>公園驚現少年屍體</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>續報！公園驚現少年屍體</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>關於在△△公園發現的少年遺體，警方正在周邊展開詢問。
+警方對少年就讀學校裡與他有關的7名學生進行了詢問。在詢問了少年的學校用品後，警方認為這些證詞中有幾人可能在說謊。
+A：在木工課上，只用了一點點新的噴漆噴在木材上。
+B：教科書因長年使用已經破舊不堪，到了極限。
+C：曾經看到他把針放進室內鞋裡。
+D：與A意見相同。
+E：筆記本是全新的，幾乎沒有使用過。
+F：與B意見相同。C在說謊。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cadáver de un niño en el parque</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>¡Última hora! Cadáver de un niño en el parque</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La policía está llevando a cabo investigaciones en la zona tras el hallazgo del cuerpo de un joven en el parque </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>△△</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+Se tomó declaración a siete estudiantes de la escuela del joven que tenían relación con él. Tras interrogarlos sobre las pertenencias escolares de la víctima, la policía sospecha que algunos de ellos podrían estar mintiendo.
+A: Usó solo un poco de un aerosol nuevo sobre la madera durante la clase de carpintería.
+B: Tras años de uso continuado, su libro de texto estaba en las últimas, totalmente destrozado.
+C: Una vez vi cómo le metían agujas en las zapatillas de interior.
+D: Estoy de acuerdo con A.
+E: Su cuaderno es completamente nuevo, apenas se ha usado.
+F: Estoy de acuerdo con B. C está mintiendo.
+G: Estoy de acuerdo con C. A está mintiendo.</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Corpo de um garoto encontrado no parque</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Atualização! Corpo de um garoto encontrado no parque</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A polícia está fazendo investigações na região após o corpo de um jovem ter sido encontrado no Parque </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>△△</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+Foram interrogados sete alunos da escola da vítima que tinham relação com ela. Com base nos depoimentos sobre os pertences escolares do jovem, a polícia suspeita que alguns deles possam estar mentindo.
+A: Ele usou só um pouquinho de um spray novinho na madeira durante a aula de marcenaria.
+B: De tanto usar ao longo dos anos, o livro didático dele estava caindo aos pedaços, no limite.
+C: Já vi colocarem agulhas dentro da sapatilha de uso interno dele.
+D: Concordo com o A.
+E: O caderno dele é novinho em folha, praticamente sem uso.
+F: Concordo com o B. O C está mentindo.
+G: Concordo com o C. O A está mentindo.</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="うわば"&gt;上履&lt;/r&gt;き</t>
+    <rPh sb="9" eb="11">
+      <t>ウワバ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>よく見ると針が仕掛けられている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Indoor Shoes</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Look closely, and you’ll notice needles rigged inside.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>室内鞋</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仔细观察会发现里面藏了针。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>室內鞋</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仔細觀察會發現裡面藏了針。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Zapatillas de interior</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Si miras de cerca, verás que hay agujas escondidas en su interior.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sapatilha de uso interno</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Olhando de perto, dá para notar que há agulhas escondidas nela.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教科書</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>とても自然とは思えない程ボロボロになっている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Textbook</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>It's shredded to a degree that feels completely unnatural.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教科书</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>破旧得极其不自然。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>破舊得極其不自然。</t>
+  </si>
+  <si>
+    <t>Libro de texto</t>
+  </si>
+  <si>
+    <t>Está tan destrozado que resulta completamente antinatural.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Livro didático</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Está caindo aos pedaços a ponto de parecer totalmente não natural.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="きょうかしょ"&gt;教科書&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="よご"&gt;汚&lt;/r&gt;れた&lt;r="かたほう"&gt;片方&lt;/r&gt;のシューズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スプレーで色を塗りつぶされており、かなり汚されている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A Dirty Shoe</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Covered in spray paint and heavily soiled.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>破旧的单只鞋子</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被喷漆涂满了颜色，脏得不成样子。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>破舊的單隻鞋子</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被噴漆塗滿了顏色，臟得不成樣子。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Zapatilla sucia</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Está completamente cubierta de pintura en aerosol y extremadamente sucia.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pé de sapato sujo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Foi completamente coberto por tinta spray e está extremamente sujo.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スプレー&lt;r="かん"&gt;缶&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>塗料用スプレー。中身はほぼ残っていない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Spray Can</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A can of spray paint. It’s almost completely empty.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>喷漆罐</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>涂料用的喷漆罐。里面的内容物几乎没剩多少。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>噴漆罐</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>塗料用的噴漆罐。裡面的內容物幾乎沒剩多少。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bote de aerosol</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pintura en aerosol. Apenas le queda contenido.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Lata de spray</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tinta em spray. O conteúdo está quase no fim.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="しんぴん"&gt;新品&lt;/r&gt;のノート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>よくみると一部のページ同士がのりで貼り付けられている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Brand-New Notebook</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A closer look reveals that some of the pages are glued together.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全新的笔记本</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仔细观察会发现，有几页被胶水粘在了一起。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全新的筆記本</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仔細觀察會發現，有幾頁被膠水黏在一塊了。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cuaderno nuevo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mirándolo detenidamente, se nota que algunas páginas están pegadas con pegamento.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Caderno novinho em folha</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Olhando bem, percebe-se que algumas páginas foram coladas umas nas outras.</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1098,6 +1484,19 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1119,7 +1518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1135,6 +1534,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1509,52 +1912,52 @@
         <v>17</v>
       </c>
       <c r="S1" t="s">
+        <v>154</v>
+      </c>
+      <c r="T1" t="s">
         <v>155</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>156</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>157</v>
       </c>
-      <c r="V1" t="s">
-        <v>158</v>
-      </c>
       <c r="W1" t="s">
+        <v>189</v>
+      </c>
+      <c r="X1" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y1" t="s">
         <v>191</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>192</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>193</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>194</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>195</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>196</v>
       </c>
-      <c r="AC1" t="s">
-        <v>197</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>198</v>
-      </c>
       <c r="AE1" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>236</v>
+      </c>
+      <c r="AH1" t="s">
         <v>237</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>238</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>239</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>240</v>
       </c>
       <c r="AI1" t="s">
         <v>18</v>
@@ -1619,49 +2022,49 @@
         <v>11</v>
       </c>
       <c r="S3" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="T3" s="4">
+        <v>14</v>
+      </c>
+      <c r="U3" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="T3" s="4">
-        <v>14</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="V3" s="4">
         <v>13</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>159</v>
+        <v>279</v>
       </c>
       <c r="X3" s="6">
         <v>14</v>
       </c>
       <c r="Y3" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Z3" s="6">
         <v>13</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>199</v>
+        <v>283</v>
       </c>
       <c r="AB3">
         <v>12</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AD3">
         <v>11</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>241</v>
+        <v>286</v>
       </c>
       <c r="AF3">
         <v>12</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AH3">
         <v>11</v>
@@ -1723,49 +2126,49 @@
         <v>14</v>
       </c>
       <c r="S4" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="T4" s="4">
+        <v>14</v>
+      </c>
+      <c r="U4" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="T4" s="4">
-        <v>14</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="V4" s="4">
         <v>14</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="X4" s="6">
         <v>14</v>
       </c>
       <c r="Y4" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Z4" s="6">
         <v>14</v>
       </c>
       <c r="AA4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AB4">
         <v>14</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AD4">
         <v>14</v>
       </c>
       <c r="AE4" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AF4">
         <v>14</v>
       </c>
       <c r="AG4" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AH4">
         <v>14</v>
@@ -1827,49 +2230,49 @@
         <v>14</v>
       </c>
       <c r="S5" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="T5" s="4">
+        <v>14</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="T5" s="4">
-        <v>14</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="V5" s="4">
         <v>14</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="X5" s="6">
         <v>14</v>
       </c>
       <c r="Y5" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="Z5" s="6">
         <v>14</v>
       </c>
       <c r="AA5" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AB5">
         <v>14</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AD5">
         <v>14</v>
       </c>
       <c r="AE5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="AF5">
         <v>14</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AH5">
         <v>14</v>
@@ -1878,7 +2281,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="75">
+    <row r="6" spans="1:35" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1931,49 +2334,49 @@
         <v>14</v>
       </c>
       <c r="S6" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="T6" s="4">
+        <v>14</v>
+      </c>
+      <c r="U6" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="T6" s="4">
-        <v>14</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="V6" s="4">
         <v>14</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="X6" s="6">
         <v>14</v>
       </c>
       <c r="Y6" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Z6" s="6">
         <v>14</v>
       </c>
       <c r="AA6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AB6">
         <v>14</v>
       </c>
       <c r="AC6" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AD6">
         <v>14</v>
       </c>
       <c r="AE6" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AF6">
         <v>14</v>
       </c>
       <c r="AG6" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AH6">
         <v>14</v>
@@ -1987,7 +2390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="150">
+    <row r="8" spans="1:35" ht="56.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2040,49 +2443,49 @@
         <v>14</v>
       </c>
       <c r="S8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="T8" s="4">
+        <v>14</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="T8" s="4">
-        <v>14</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="V8" s="4">
         <v>14</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="X8" s="6">
         <v>14</v>
       </c>
       <c r="Y8" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Z8" s="6">
         <v>14</v>
       </c>
       <c r="AA8" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AB8">
         <v>14</v>
       </c>
       <c r="AC8" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AD8">
         <v>14</v>
       </c>
       <c r="AE8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AF8">
         <v>14</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AH8">
         <v>14</v>
@@ -2144,49 +2547,49 @@
         <v>14</v>
       </c>
       <c r="S9" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="T9" s="4">
+        <v>14</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="T9" s="4">
-        <v>14</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="V9" s="4">
         <v>14</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X9" s="6">
         <v>14</v>
       </c>
       <c r="Y9" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Z9" s="6">
         <v>14</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AB9">
         <v>14</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AD9">
         <v>14</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AF9">
         <v>14</v>
       </c>
       <c r="AG9" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="AH9">
         <v>14</v>
@@ -2195,7 +2598,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="131.25">
+    <row r="10" spans="1:35" ht="56.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2248,49 +2651,49 @@
         <v>14</v>
       </c>
       <c r="S10" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="T10" s="4">
+        <v>14</v>
+      </c>
+      <c r="U10" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="T10" s="4">
-        <v>14</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="V10" s="4">
         <v>14</v>
       </c>
       <c r="W10" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="X10" s="6">
         <v>14</v>
       </c>
       <c r="Y10" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Z10" s="6">
         <v>14</v>
       </c>
       <c r="AA10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AB10">
         <v>14</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AD10">
         <v>14</v>
       </c>
       <c r="AE10" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AF10">
         <v>14</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="AH10">
         <v>14</v>
@@ -2299,7 +2702,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="75">
+    <row r="11" spans="1:35" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2352,49 +2755,49 @@
         <v>14</v>
       </c>
       <c r="S11" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="T11" s="4">
+        <v>14</v>
+      </c>
+      <c r="U11" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="T11" s="4">
-        <v>14</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="V11" s="4">
         <v>14</v>
       </c>
       <c r="W11" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="X11" s="6">
         <v>14</v>
       </c>
       <c r="Y11" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Z11" s="6">
         <v>14</v>
       </c>
       <c r="AA11" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AB11">
         <v>14</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AD11">
         <v>14</v>
       </c>
       <c r="AE11" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AF11">
         <v>14</v>
       </c>
       <c r="AG11" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AH11">
         <v>14</v>
@@ -2403,7 +2806,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="150">
+    <row r="12" spans="1:35" ht="56.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2457,49 +2860,49 @@
         <v>14</v>
       </c>
       <c r="S12" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="T12" s="4">
+        <v>14</v>
+      </c>
+      <c r="U12" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="T12" s="4">
-        <v>14</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="V12" s="4">
         <v>14</v>
       </c>
       <c r="W12" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="X12" s="6">
         <v>14</v>
       </c>
       <c r="Y12" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Z12" s="6">
         <v>14</v>
       </c>
       <c r="AA12" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AB12">
         <v>14</v>
       </c>
       <c r="AC12" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AD12">
         <v>14</v>
       </c>
       <c r="AE12" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AF12">
         <v>14</v>
       </c>
       <c r="AG12" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AH12">
         <v>14</v>
@@ -2564,49 +2967,49 @@
         <v>10</v>
       </c>
       <c r="S13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="T13" s="4">
+        <v>14</v>
+      </c>
+      <c r="U13" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="T13" s="4">
-        <v>14</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="V13" s="4">
         <v>12</v>
       </c>
       <c r="W13" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="X13" s="6">
         <v>14</v>
       </c>
       <c r="Y13" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Z13" s="6">
         <v>12</v>
       </c>
       <c r="AA13" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AB13">
         <v>14</v>
       </c>
       <c r="AC13" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AD13">
         <v>10</v>
       </c>
       <c r="AE13" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="AF13">
         <v>14</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="AH13">
         <v>10</v>
@@ -2669,49 +3072,49 @@
         <v>12</v>
       </c>
       <c r="S14" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="T14" s="4">
+        <v>14</v>
+      </c>
+      <c r="U14" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="T14" s="4">
-        <v>14</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="V14" s="4">
         <v>12</v>
       </c>
       <c r="W14" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="X14" s="6">
         <v>14</v>
       </c>
       <c r="Y14" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Z14" s="6">
         <v>12</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB14">
         <v>14</v>
       </c>
       <c r="AC14" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AD14">
         <v>12</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AF14">
         <v>14</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AH14">
         <v>12</v>
@@ -2765,7 +3168,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="150">
+    <row r="16" spans="1:35" ht="56.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2819,49 +3222,49 @@
         <v>14</v>
       </c>
       <c r="S16" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="T16" s="4">
+        <v>14</v>
+      </c>
+      <c r="U16" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="T16" s="4">
-        <v>14</v>
-      </c>
-      <c r="U16" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="V16" s="4">
         <v>14</v>
       </c>
       <c r="W16" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="X16" s="6">
         <v>14</v>
       </c>
       <c r="Y16" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Z16" s="6">
         <v>14</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AB16">
         <v>14</v>
       </c>
       <c r="AC16" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AD16">
         <v>14</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AF16">
         <v>14</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AH16">
         <v>14</v>
@@ -2870,7 +3273,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="168.75">
+    <row r="17" spans="1:35" ht="56.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2924,49 +3327,49 @@
         <v>14</v>
       </c>
       <c r="S17" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="T17" s="4">
+        <v>14</v>
+      </c>
+      <c r="U17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="T17" s="4">
-        <v>14</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="V17" s="4">
         <v>14</v>
       </c>
       <c r="W17" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X17" s="6">
         <v>14</v>
       </c>
       <c r="Y17" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="Z17" s="6">
         <v>14</v>
       </c>
       <c r="AA17" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AB17">
         <v>14</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AD17">
         <v>14</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AF17">
         <v>14</v>
       </c>
       <c r="AG17" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AH17">
         <v>14</v>
@@ -2975,7 +3378,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="168.75">
+    <row r="18" spans="1:35" ht="56.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3028,49 +3431,49 @@
         <v>14</v>
       </c>
       <c r="S18" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="T18" s="4">
+        <v>14</v>
+      </c>
+      <c r="U18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="T18" s="4">
-        <v>14</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="V18" s="4">
         <v>14</v>
       </c>
       <c r="W18" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="X18" s="6">
         <v>14</v>
       </c>
       <c r="Y18" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Z18" s="6">
         <v>14</v>
       </c>
       <c r="AA18" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AB18">
         <v>12</v>
       </c>
       <c r="AC18" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AD18">
         <v>14</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AF18">
         <v>12</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AH18">
         <v>14</v>
@@ -3079,7 +3482,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="168.75">
+    <row r="19" spans="1:35" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3133,49 +3536,49 @@
         <v>14</v>
       </c>
       <c r="S19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="T19" s="4">
+        <v>14</v>
+      </c>
+      <c r="U19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="T19" s="4">
-        <v>14</v>
-      </c>
-      <c r="U19" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="V19" s="4">
         <v>14</v>
       </c>
       <c r="W19" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="X19" s="6">
         <v>14</v>
       </c>
       <c r="Y19" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Z19" s="6">
         <v>14</v>
       </c>
       <c r="AA19" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AB19">
         <v>14</v>
       </c>
       <c r="AC19" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AD19">
         <v>14</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AF19">
         <v>14</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AH19">
         <v>14</v>
@@ -3184,7 +3587,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="168.75">
+    <row r="20" spans="1:35" ht="56.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -3237,49 +3640,49 @@
         <v>14</v>
       </c>
       <c r="S20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="T20" s="4">
+        <v>14</v>
+      </c>
+      <c r="U20" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="T20" s="4">
-        <v>14</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="V20" s="4">
         <v>14</v>
       </c>
       <c r="W20" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="X20" s="6">
+        <v>14</v>
+      </c>
+      <c r="Y20" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="X20" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y20" s="5" t="s">
-        <v>137</v>
-      </c>
       <c r="Z20" s="6">
         <v>14</v>
       </c>
       <c r="AA20" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AB20">
         <v>12</v>
       </c>
       <c r="AC20" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AD20">
         <v>14</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AF20">
         <v>12</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="AH20">
         <v>14</v>
@@ -3344,49 +3747,49 @@
         <v>10</v>
       </c>
       <c r="S21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="T21" s="4">
+        <v>14</v>
+      </c>
+      <c r="U21" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="T21" s="4">
-        <v>14</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="V21" s="4">
         <v>12</v>
       </c>
       <c r="W21" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="X21" s="6">
         <v>14</v>
       </c>
       <c r="Y21" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Z21" s="6">
         <v>12</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AB21">
         <v>14</v>
       </c>
       <c r="AC21" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AD21">
         <v>10</v>
       </c>
       <c r="AE21" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AF21">
         <v>14</v>
       </c>
       <c r="AG21" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AH21">
         <v>10</v>
@@ -3448,49 +3851,49 @@
         <v>12</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T22" s="4">
         <v>12</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="V22" s="4">
         <v>14</v>
       </c>
       <c r="W22" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="X22" s="6">
         <v>12</v>
       </c>
       <c r="Y22" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Z22" s="6">
         <v>14</v>
       </c>
       <c r="AA22" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AB22">
         <v>12</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AD22">
         <v>12</v>
       </c>
       <c r="AE22" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AF22">
         <v>12</v>
       </c>
       <c r="AG22" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AH22">
         <v>12</v>
@@ -3499,34 +3902,628 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:35">
+    <row r="23" spans="1:35" ht="409.5">
       <c r="A23">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="1:35">
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="J23" s="1">
+        <v>12</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="L23">
+        <v>14</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="P23" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="R23">
+        <v>12</v>
+      </c>
+      <c r="S23" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="T23" s="4">
+        <v>12</v>
+      </c>
+      <c r="U23" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="V23" s="4">
+        <v>14</v>
+      </c>
+      <c r="W23" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="X23" s="4">
+        <v>12</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="Z23" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA23" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="AB23">
+        <v>12</v>
+      </c>
+      <c r="AC23" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="AD23">
+        <v>12</v>
+      </c>
+      <c r="AE23" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="AF23">
+        <v>12</v>
+      </c>
+      <c r="AG23" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="AH23">
+        <v>12</v>
+      </c>
+      <c r="AI23" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="24" spans="1:35" ht="56.25">
       <c r="A24">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:35">
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J24" s="1">
+        <v>14</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="L24">
+        <v>14</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="P24" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="R24" s="1">
+        <v>14</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="T24" s="1">
+        <v>14</v>
+      </c>
+      <c r="U24" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="V24" s="1">
+        <v>14</v>
+      </c>
+      <c r="W24" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="X24" s="1">
+        <v>14</v>
+      </c>
+      <c r="Y24" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA24" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="AB24">
+        <v>12</v>
+      </c>
+      <c r="AC24" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD24" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE24" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="AF24">
+        <v>12</v>
+      </c>
+      <c r="AG24" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="AH24" s="6">
+        <v>14</v>
+      </c>
+      <c r="AI24" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" ht="56.25">
       <c r="A25">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:35">
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="J25" s="1">
+        <v>14</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="L25">
+        <v>14</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="P25" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="R25" s="1">
+        <v>14</v>
+      </c>
+      <c r="S25" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="T25" s="1">
+        <v>14</v>
+      </c>
+      <c r="U25" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="V25" s="1">
+        <v>14</v>
+      </c>
+      <c r="W25" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="X25" s="1">
+        <v>14</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>307</v>
+      </c>
+      <c r="Z25" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>308</v>
+      </c>
+      <c r="AB25">
+        <v>12</v>
+      </c>
+      <c r="AC25" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="AD25" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE25" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="AF25">
+        <v>12</v>
+      </c>
+      <c r="AG25" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="AH25" s="6">
+        <v>14</v>
+      </c>
+      <c r="AI25" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" ht="75">
       <c r="A26">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:35">
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="J26" s="1">
+        <v>14</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="L26">
+        <v>14</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="P26" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="R26" s="1">
+        <v>14</v>
+      </c>
+      <c r="S26" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="T26" s="1">
+        <v>14</v>
+      </c>
+      <c r="U26" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="V26" s="1">
+        <v>14</v>
+      </c>
+      <c r="W26" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="X26" s="1">
+        <v>14</v>
+      </c>
+      <c r="Y26" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="Z26" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA26" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="AB26">
+        <v>12</v>
+      </c>
+      <c r="AC26" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="AD26" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE26" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="AF26">
+        <v>12</v>
+      </c>
+      <c r="AG26" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="AH26" s="6">
+        <v>14</v>
+      </c>
+      <c r="AI26" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" ht="56.25">
       <c r="A27">
         <v>25</v>
       </c>
-    </row>
-    <row r="28" spans="1:35">
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="J27" s="1">
+        <v>14</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L27">
+        <v>14</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="P27" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="R27" s="1">
+        <v>14</v>
+      </c>
+      <c r="S27" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="T27" s="1">
+        <v>14</v>
+      </c>
+      <c r="U27" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="V27" s="1">
+        <v>14</v>
+      </c>
+      <c r="W27" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="X27" s="1">
+        <v>14</v>
+      </c>
+      <c r="Y27" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z27" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA27" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="AB27">
+        <v>12</v>
+      </c>
+      <c r="AC27" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="AD27" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE27" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="AF27">
+        <v>12</v>
+      </c>
+      <c r="AG27" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="AH27" s="6">
+        <v>14</v>
+      </c>
+      <c r="AI27" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="28" spans="1:35" ht="75">
       <c r="A28">
         <v>26</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="J28" s="1">
+        <v>14</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="L28">
+        <v>14</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="P28" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="R28" s="1">
+        <v>14</v>
+      </c>
+      <c r="S28" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="T28" s="1">
+        <v>14</v>
+      </c>
+      <c r="U28" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="V28" s="1">
+        <v>14</v>
+      </c>
+      <c r="W28" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X28" s="1">
+        <v>14</v>
+      </c>
+      <c r="Y28" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA28" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="AB28">
+        <v>12</v>
+      </c>
+      <c r="AC28" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="AD28" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE28" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="AF28">
+        <v>12</v>
+      </c>
+      <c r="AG28" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="AH28" s="6">
+        <v>14</v>
+      </c>
+      <c r="AI28" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -8417,49 +9414,49 @@
         <v>14</v>
       </c>
       <c r="S996" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="T996" s="4">
+        <v>14</v>
+      </c>
+      <c r="U996" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="T996" s="4">
-        <v>14</v>
-      </c>
-      <c r="U996" s="4" t="s">
-        <v>143</v>
-      </c>
       <c r="V996" s="4">
         <v>14</v>
       </c>
       <c r="W996" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="X996" s="6">
         <v>14</v>
       </c>
       <c r="Y996" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="Z996" s="6">
         <v>14</v>
       </c>
       <c r="AA996" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AB996">
         <v>14</v>
       </c>
       <c r="AC996" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AD996">
         <v>14</v>
       </c>
       <c r="AE996" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AF996">
         <v>14</v>
       </c>
       <c r="AG996" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AH996">
         <v>14</v>
@@ -8524,49 +9521,49 @@
         <v>14</v>
       </c>
       <c r="S997" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="T997" s="4">
+        <v>14</v>
+      </c>
+      <c r="U997" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="T997" s="4">
-        <v>14</v>
-      </c>
-      <c r="U997" s="4" t="s">
-        <v>145</v>
-      </c>
       <c r="V997" s="4">
         <v>14</v>
       </c>
       <c r="W997" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="X997" s="6">
         <v>14</v>
       </c>
       <c r="Y997" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Z997" s="6">
         <v>14</v>
       </c>
       <c r="AA997" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AB997">
         <v>14</v>
       </c>
       <c r="AC997" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AD997">
         <v>14</v>
       </c>
       <c r="AE997" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF997">
         <v>14</v>
       </c>
       <c r="AG997" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AH997">
         <v>14</v>
@@ -8628,49 +9625,49 @@
         <v>14</v>
       </c>
       <c r="S998" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="T998" s="4">
+        <v>14</v>
+      </c>
+      <c r="U998" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="T998" s="4">
-        <v>14</v>
-      </c>
-      <c r="U998" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="V998" s="4">
         <v>14</v>
       </c>
       <c r="W998" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X998" s="6">
         <v>14</v>
       </c>
       <c r="Y998" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="Z998" s="6">
         <v>14</v>
       </c>
       <c r="AA998" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AB998">
         <v>14</v>
       </c>
       <c r="AC998" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AD998">
         <v>14</v>
       </c>
       <c r="AE998" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AF998">
         <v>14</v>
       </c>
       <c r="AG998" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AH998">
         <v>14</v>
@@ -8732,49 +9729,49 @@
         <v>14</v>
       </c>
       <c r="S999" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="T999" s="4">
+        <v>14</v>
+      </c>
+      <c r="U999" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="T999" s="4">
-        <v>14</v>
-      </c>
-      <c r="U999" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="V999" s="4">
         <v>14</v>
       </c>
       <c r="W999" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="X999" s="6">
         <v>14</v>
       </c>
       <c r="Y999" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="Z999" s="6">
         <v>14</v>
       </c>
       <c r="AA999" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AB999">
         <v>14</v>
       </c>
       <c r="AC999" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AD999">
         <v>14</v>
       </c>
       <c r="AE999" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AF999">
         <v>14</v>
       </c>
       <c r="AG999" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AH999">
         <v>14</v>
@@ -8836,49 +9833,49 @@
         <v>14</v>
       </c>
       <c r="S1000" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="T1000" s="4">
+        <v>14</v>
+      </c>
+      <c r="U1000" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="T1000" s="4">
-        <v>14</v>
-      </c>
-      <c r="U1000" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="V1000" s="4">
         <v>14</v>
       </c>
       <c r="W1000" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="X1000" s="6">
         <v>14</v>
       </c>
       <c r="Y1000" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="Z1000" s="6">
         <v>14</v>
       </c>
       <c r="AA1000" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AB1000">
         <v>14</v>
       </c>
       <c r="AC1000" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AD1000">
         <v>14</v>
       </c>
       <c r="AE1000" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AF1000">
         <v>14</v>
       </c>
       <c r="AG1000" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="AH1000">
         <v>14</v>
@@ -8940,49 +9937,49 @@
         <v>14</v>
       </c>
       <c r="S1001" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="T1001" s="4">
+        <v>14</v>
+      </c>
+      <c r="U1001" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="T1001" s="4">
-        <v>14</v>
-      </c>
-      <c r="U1001" s="4" t="s">
-        <v>153</v>
-      </c>
       <c r="V1001" s="4">
         <v>14</v>
       </c>
       <c r="W1001" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="X1001" s="6">
         <v>14</v>
       </c>
       <c r="Y1001" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="Z1001" s="6">
         <v>14</v>
       </c>
       <c r="AA1001" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AB1001">
         <v>14</v>
       </c>
       <c r="AC1001" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AD1001">
         <v>14</v>
       </c>
       <c r="AE1001" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AF1001">
         <v>14</v>
       </c>
       <c r="AG1001" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AH1001">
         <v>14</v>
@@ -9047,7 +10044,7 @@
         <v>0</v>
       </c>
       <c r="U1002" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V1002" s="4">
         <v>0</v>
@@ -9059,7 +10056,7 @@
         <v>0</v>
       </c>
       <c r="Y1002" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Z1002" s="6">
         <v>0</v>
@@ -9071,7 +10068,7 @@
         <v>0</v>
       </c>
       <c r="AC1002" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AE1002" t="s">
         <v>62</v>
@@ -9080,7 +10077,7 @@
         <v>0</v>
       </c>
       <c r="AG1002" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2F1D83-695D-43F7-A0BD-DB1D39087019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0926A480-B0E3-40D1-8D49-DD55AD8E77BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3933,8 +3933,8 @@
       <c r="K23" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="L23">
-        <v>14</v>
+      <c r="L23" s="4">
+        <v>12</v>
       </c>
       <c r="M23">
         <v>1</v>
@@ -3964,7 +3964,7 @@
         <v>278</v>
       </c>
       <c r="V23" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W23" s="5" t="s">
         <v>280</v>
@@ -3975,8 +3975,8 @@
       <c r="Y23" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="Z23" s="6">
-        <v>14</v>
+      <c r="Z23" s="4">
+        <v>12</v>
       </c>
       <c r="AA23" s="1" t="s">
         <v>284</v>
@@ -3988,7 +3988,7 @@
         <v>285</v>
       </c>
       <c r="AD23">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE23" s="1" t="s">
         <v>287</v>
@@ -4000,7 +4000,7 @@
         <v>288</v>
       </c>
       <c r="AH23">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI23" s="1" t="s">
         <v>282</v>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0926A480-B0E3-40D1-8D49-DD55AD8E77BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3615968-93DC-40C6-B705-8ADD3F5FA494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="350">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -1450,6 +1450,10 @@
   </si>
   <si>
     <t>Olhando bem, percebe-se que algumas páginas foram coladas umas nas outras.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>enemyInformationMessageId</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1818,7 +1822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1002"/>
+  <dimension ref="A1:AJ1002"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -1828,35 +1832,36 @@
     <col min="6" max="6" width="15.125" customWidth="1"/>
     <col min="7" max="7" width="14.875" customWidth="1"/>
     <col min="8" max="8" width="15.5" customWidth="1"/>
-    <col min="9" max="9" width="26.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21.375" customWidth="1"/>
-    <col min="11" max="11" width="22.375" customWidth="1"/>
-    <col min="12" max="12" width="26.25" customWidth="1"/>
-    <col min="13" max="13" width="9.625" customWidth="1"/>
-    <col min="14" max="14" width="14.875" customWidth="1"/>
-    <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="20.375" customWidth="1"/>
-    <col min="17" max="17" width="20.625" customWidth="1"/>
-    <col min="18" max="18" width="23.875" customWidth="1"/>
-    <col min="19" max="19" width="24.75" customWidth="1"/>
-    <col min="20" max="20" width="24.875" customWidth="1"/>
-    <col min="21" max="21" width="26.375" customWidth="1"/>
-    <col min="22" max="22" width="32" customWidth="1"/>
-    <col min="23" max="23" width="19" customWidth="1"/>
-    <col min="24" max="24" width="22.5" customWidth="1"/>
-    <col min="25" max="25" width="23.625" customWidth="1"/>
-    <col min="26" max="26" width="28.375" customWidth="1"/>
-    <col min="27" max="27" width="21" customWidth="1"/>
-    <col min="28" max="28" width="23.125" customWidth="1"/>
-    <col min="29" max="29" width="24.875" customWidth="1"/>
-    <col min="30" max="30" width="26" customWidth="1"/>
-    <col min="31" max="31" width="31.875" customWidth="1"/>
-    <col min="32" max="32" width="28.5" customWidth="1"/>
-    <col min="33" max="33" width="28.25" customWidth="1"/>
-    <col min="34" max="34" width="31.375" customWidth="1"/>
+    <col min="9" max="9" width="27.625" customWidth="1"/>
+    <col min="10" max="10" width="26.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="21.375" customWidth="1"/>
+    <col min="12" max="12" width="22.375" customWidth="1"/>
+    <col min="13" max="13" width="26.25" customWidth="1"/>
+    <col min="14" max="14" width="9.625" customWidth="1"/>
+    <col min="15" max="15" width="14.875" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
+    <col min="17" max="17" width="20.375" customWidth="1"/>
+    <col min="18" max="18" width="20.625" customWidth="1"/>
+    <col min="19" max="19" width="23.875" customWidth="1"/>
+    <col min="20" max="20" width="24.75" customWidth="1"/>
+    <col min="21" max="21" width="24.875" customWidth="1"/>
+    <col min="22" max="22" width="26.375" customWidth="1"/>
+    <col min="23" max="23" width="32" customWidth="1"/>
+    <col min="24" max="24" width="19" customWidth="1"/>
+    <col min="25" max="25" width="22.5" customWidth="1"/>
+    <col min="26" max="26" width="23.625" customWidth="1"/>
+    <col min="27" max="27" width="28.375" customWidth="1"/>
+    <col min="28" max="28" width="21" customWidth="1"/>
+    <col min="29" max="29" width="23.125" customWidth="1"/>
+    <col min="30" max="30" width="24.875" customWidth="1"/>
+    <col min="31" max="31" width="26" customWidth="1"/>
+    <col min="32" max="32" width="31.875" customWidth="1"/>
+    <col min="33" max="33" width="28.5" customWidth="1"/>
+    <col min="34" max="34" width="28.25" customWidth="1"/>
+    <col min="35" max="35" width="31.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:36">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1881,95 +1886,98 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
+        <v>349</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
       <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>154</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>155</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>156</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>157</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>189</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>190</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>191</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>192</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>193</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>194</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>195</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>196</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>234</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>235</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>236</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>237</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:36">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:35" ht="409.5">
+    <row r="3" spans="1:36" ht="409.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1991,89 +1999,92 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3">
+        <v>99999</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J3">
-        <v>14</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3">
+        <v>14</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>13</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>1</v>
       </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" s="1" t="s">
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>12</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>11</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="T3" s="4">
-        <v>14</v>
-      </c>
-      <c r="U3" s="3" t="s">
+      <c r="U3" s="4">
+        <v>14</v>
+      </c>
+      <c r="V3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="V3" s="4">
+      <c r="W3" s="4">
         <v>13</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="X3" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="X3" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Y3" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z3" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="Z3" s="6">
+      <c r="AA3" s="6">
         <v>13</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="AB3">
+      <c r="AC3">
         <v>12</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AD3" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AD3">
+      <c r="AE3">
         <v>11</v>
       </c>
-      <c r="AE3" s="1" t="s">
+      <c r="AF3" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="AF3">
+      <c r="AG3">
         <v>12</v>
       </c>
-      <c r="AG3" s="1" t="s">
+      <c r="AH3" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="AH3">
+      <c r="AI3">
         <v>11</v>
       </c>
-      <c r="AI3" s="1" t="s">
+      <c r="AJ3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="228" customHeight="1">
+    <row r="4" spans="1:36" ht="228" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2095,89 +2106,92 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4">
+        <v>99999</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J4">
-        <v>14</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4">
+        <v>14</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="L4">
-        <v>14</v>
-      </c>
       <c r="M4">
+        <v>14</v>
+      </c>
+      <c r="N4">
         <v>1</v>
       </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4" t="s">
         <v>20</v>
       </c>
-      <c r="P4">
-        <v>14</v>
-      </c>
-      <c r="Q4" s="1" t="s">
+      <c r="Q4">
+        <v>14</v>
+      </c>
+      <c r="R4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="R4">
-        <v>14</v>
-      </c>
-      <c r="S4" s="3" t="s">
+      <c r="S4">
+        <v>14</v>
+      </c>
+      <c r="T4" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="T4" s="4">
-        <v>14</v>
-      </c>
-      <c r="U4" s="3" t="s">
+      <c r="U4" s="4">
+        <v>14</v>
+      </c>
+      <c r="V4" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="V4" s="4">
-        <v>14</v>
-      </c>
-      <c r="W4" s="5" t="s">
+      <c r="W4" s="4">
+        <v>14</v>
+      </c>
+      <c r="X4" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="X4" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Y4" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z4" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="Z4" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA4" t="s">
+      <c r="AA4" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB4" t="s">
         <v>198</v>
       </c>
-      <c r="AB4">
-        <v>14</v>
-      </c>
-      <c r="AC4" s="1" t="s">
+      <c r="AC4">
+        <v>14</v>
+      </c>
+      <c r="AD4" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AD4">
-        <v>14</v>
-      </c>
-      <c r="AE4" t="s">
+      <c r="AE4">
+        <v>14</v>
+      </c>
+      <c r="AF4" t="s">
         <v>239</v>
       </c>
-      <c r="AF4">
-        <v>14</v>
-      </c>
-      <c r="AG4" s="1" t="s">
+      <c r="AG4">
+        <v>14</v>
+      </c>
+      <c r="AH4" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="AH4">
-        <v>14</v>
-      </c>
-      <c r="AI4" t="s">
+      <c r="AI4">
+        <v>14</v>
+      </c>
+      <c r="AJ4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="92.25" customHeight="1">
+    <row r="5" spans="1:36" ht="92.25" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2199,89 +2213,92 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5">
+        <v>99999</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J5">
-        <v>14</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5">
+        <v>14</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="L5">
-        <v>14</v>
-      </c>
       <c r="M5">
+        <v>14</v>
+      </c>
+      <c r="N5">
         <v>1</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5" t="s">
         <v>24</v>
       </c>
-      <c r="P5">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="1" t="s">
+      <c r="Q5">
+        <v>14</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="R5">
-        <v>14</v>
-      </c>
-      <c r="S5" s="3" t="s">
+      <c r="S5">
+        <v>14</v>
+      </c>
+      <c r="T5" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="T5" s="4">
-        <v>14</v>
-      </c>
-      <c r="U5" s="3" t="s">
+      <c r="U5" s="4">
+        <v>14</v>
+      </c>
+      <c r="V5" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="V5" s="4">
-        <v>14</v>
-      </c>
-      <c r="W5" s="5" t="s">
+      <c r="W5" s="4">
+        <v>14</v>
+      </c>
+      <c r="X5" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="X5" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y5" s="5" t="s">
+      <c r="Y5" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z5" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="Z5" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA5" t="s">
+      <c r="AA5" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB5" t="s">
         <v>200</v>
       </c>
-      <c r="AB5">
-        <v>14</v>
-      </c>
-      <c r="AC5" s="1" t="s">
+      <c r="AC5">
+        <v>14</v>
+      </c>
+      <c r="AD5" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="AD5">
-        <v>14</v>
-      </c>
-      <c r="AE5" t="s">
+      <c r="AE5">
+        <v>14</v>
+      </c>
+      <c r="AF5" t="s">
         <v>241</v>
       </c>
-      <c r="AF5">
-        <v>14</v>
-      </c>
-      <c r="AG5" s="1" t="s">
+      <c r="AG5">
+        <v>14</v>
+      </c>
+      <c r="AH5" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="AH5">
-        <v>14</v>
-      </c>
-      <c r="AI5" t="s">
+      <c r="AI5">
+        <v>14</v>
+      </c>
+      <c r="AJ5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="37.5">
+    <row r="6" spans="1:36" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2303,94 +2320,97 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6">
+        <v>99999</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J6">
-        <v>14</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6">
+        <v>14</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="L6">
-        <v>14</v>
-      </c>
       <c r="M6">
+        <v>14</v>
+      </c>
+      <c r="N6">
         <v>1</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6" t="s">
         <v>27</v>
       </c>
-      <c r="P6">
-        <v>14</v>
-      </c>
-      <c r="Q6" s="1" t="s">
+      <c r="Q6">
+        <v>14</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="R6">
-        <v>14</v>
-      </c>
-      <c r="S6" s="3" t="s">
+      <c r="S6">
+        <v>14</v>
+      </c>
+      <c r="T6" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="T6" s="4">
-        <v>14</v>
-      </c>
-      <c r="U6" s="3" t="s">
+      <c r="U6" s="4">
+        <v>14</v>
+      </c>
+      <c r="V6" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="V6" s="4">
-        <v>14</v>
-      </c>
-      <c r="W6" s="5" t="s">
+      <c r="W6" s="4">
+        <v>14</v>
+      </c>
+      <c r="X6" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="X6" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y6" s="5" t="s">
+      <c r="Y6" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z6" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="Z6" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA6" t="s">
+      <c r="AA6" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB6" t="s">
         <v>202</v>
       </c>
-      <c r="AB6">
-        <v>14</v>
-      </c>
-      <c r="AC6" s="1" t="s">
+      <c r="AC6">
+        <v>14</v>
+      </c>
+      <c r="AD6" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="AD6">
-        <v>14</v>
-      </c>
-      <c r="AE6" t="s">
+      <c r="AE6">
+        <v>14</v>
+      </c>
+      <c r="AF6" t="s">
         <v>243</v>
       </c>
-      <c r="AF6">
-        <v>14</v>
-      </c>
-      <c r="AG6" s="1" t="s">
+      <c r="AG6">
+        <v>14</v>
+      </c>
+      <c r="AH6" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="AH6">
-        <v>14</v>
-      </c>
-      <c r="AI6" t="s">
+      <c r="AI6">
+        <v>14</v>
+      </c>
+      <c r="AJ6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:36">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="56.25">
+    <row r="8" spans="1:36" ht="56.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2412,89 +2432,92 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8">
+        <v>99999</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J8">
-        <v>14</v>
-      </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8">
+        <v>14</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="L8">
-        <v>14</v>
-      </c>
       <c r="M8">
+        <v>14</v>
+      </c>
+      <c r="N8">
         <v>1</v>
       </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8" t="s">
         <v>30</v>
       </c>
-      <c r="P8">
-        <v>14</v>
-      </c>
-      <c r="Q8" s="1" t="s">
+      <c r="Q8">
+        <v>14</v>
+      </c>
+      <c r="R8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R8">
-        <v>14</v>
-      </c>
-      <c r="S8" s="3" t="s">
+      <c r="S8">
+        <v>14</v>
+      </c>
+      <c r="T8" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="T8" s="4">
-        <v>14</v>
-      </c>
-      <c r="U8" s="3" t="s">
+      <c r="U8" s="4">
+        <v>14</v>
+      </c>
+      <c r="V8" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="V8" s="4">
-        <v>14</v>
-      </c>
-      <c r="W8" s="5" t="s">
+      <c r="W8" s="4">
+        <v>14</v>
+      </c>
+      <c r="X8" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="X8" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y8" s="5" t="s">
+      <c r="Y8" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z8" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="Z8" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA8" t="s">
+      <c r="AA8" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB8" t="s">
         <v>204</v>
       </c>
-      <c r="AB8">
-        <v>14</v>
-      </c>
-      <c r="AC8" s="1" t="s">
+      <c r="AC8">
+        <v>14</v>
+      </c>
+      <c r="AD8" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="AD8">
-        <v>14</v>
-      </c>
-      <c r="AE8" t="s">
+      <c r="AE8">
+        <v>14</v>
+      </c>
+      <c r="AF8" t="s">
         <v>245</v>
       </c>
-      <c r="AF8">
-        <v>14</v>
-      </c>
-      <c r="AG8" s="1" t="s">
+      <c r="AG8">
+        <v>14</v>
+      </c>
+      <c r="AH8" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="AH8">
-        <v>14</v>
-      </c>
-      <c r="AI8" t="s">
+      <c r="AI8">
+        <v>14</v>
+      </c>
+      <c r="AJ8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="297.75" customHeight="1">
+    <row r="9" spans="1:36" ht="297.75" customHeight="1">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2516,89 +2539,92 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9">
+        <v>99999</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J9">
-        <v>14</v>
-      </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9">
+        <v>14</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="L9">
-        <v>14</v>
-      </c>
       <c r="M9">
+        <v>14</v>
+      </c>
+      <c r="N9">
         <v>1</v>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" s="1" t="s">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P9">
-        <v>14</v>
-      </c>
-      <c r="Q9" s="1" t="s">
+      <c r="Q9">
+        <v>14</v>
+      </c>
+      <c r="R9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R9">
-        <v>14</v>
-      </c>
-      <c r="S9" s="3" t="s">
+      <c r="S9">
+        <v>14</v>
+      </c>
+      <c r="T9" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="T9" s="4">
-        <v>14</v>
-      </c>
-      <c r="U9" s="3" t="s">
+      <c r="U9" s="4">
+        <v>14</v>
+      </c>
+      <c r="V9" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="V9" s="4">
-        <v>14</v>
-      </c>
-      <c r="W9" s="5" t="s">
+      <c r="W9" s="4">
+        <v>14</v>
+      </c>
+      <c r="X9" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="X9" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y9" s="5" t="s">
+      <c r="Y9" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z9" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="Z9" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA9" s="1" t="s">
+      <c r="AA9" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB9" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="AB9">
-        <v>14</v>
-      </c>
-      <c r="AC9" s="1" t="s">
+      <c r="AC9">
+        <v>14</v>
+      </c>
+      <c r="AD9" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="AD9">
-        <v>14</v>
-      </c>
-      <c r="AE9" s="1" t="s">
+      <c r="AE9">
+        <v>14</v>
+      </c>
+      <c r="AF9" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="AF9">
-        <v>14</v>
-      </c>
-      <c r="AG9" s="1" t="s">
+      <c r="AG9">
+        <v>14</v>
+      </c>
+      <c r="AH9" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="AH9">
-        <v>14</v>
-      </c>
-      <c r="AI9" s="1" t="s">
+      <c r="AI9">
+        <v>14</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="56.25">
+    <row r="10" spans="1:36" ht="56.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2620,89 +2646,92 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10">
+        <v>99999</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J10">
-        <v>14</v>
-      </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10">
+        <v>14</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="L10">
-        <v>14</v>
-      </c>
       <c r="M10">
+        <v>14</v>
+      </c>
+      <c r="N10">
         <v>1</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10" t="s">
         <v>35</v>
       </c>
-      <c r="P10">
-        <v>14</v>
-      </c>
-      <c r="Q10" s="1" t="s">
+      <c r="Q10">
+        <v>14</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="R10">
-        <v>14</v>
-      </c>
-      <c r="S10" s="3" t="s">
+      <c r="S10">
+        <v>14</v>
+      </c>
+      <c r="T10" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="T10" s="4">
-        <v>14</v>
-      </c>
-      <c r="U10" s="3" t="s">
+      <c r="U10" s="4">
+        <v>14</v>
+      </c>
+      <c r="V10" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="V10" s="4">
-        <v>14</v>
-      </c>
-      <c r="W10" s="5" t="s">
+      <c r="W10" s="4">
+        <v>14</v>
+      </c>
+      <c r="X10" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="X10" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y10" s="5" t="s">
+      <c r="Y10" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z10" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="Z10" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA10" t="s">
+      <c r="AA10" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB10" t="s">
         <v>208</v>
       </c>
-      <c r="AB10">
-        <v>14</v>
-      </c>
-      <c r="AC10" s="1" t="s">
+      <c r="AC10">
+        <v>14</v>
+      </c>
+      <c r="AD10" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="AD10">
-        <v>14</v>
-      </c>
-      <c r="AE10" t="s">
+      <c r="AE10">
+        <v>14</v>
+      </c>
+      <c r="AF10" t="s">
         <v>248</v>
       </c>
-      <c r="AF10">
-        <v>14</v>
-      </c>
-      <c r="AG10" s="1" t="s">
+      <c r="AG10">
+        <v>14</v>
+      </c>
+      <c r="AH10" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="AH10">
-        <v>14</v>
-      </c>
-      <c r="AI10" t="s">
+      <c r="AI10">
+        <v>14</v>
+      </c>
+      <c r="AJ10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="37.5">
+    <row r="11" spans="1:36" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2724,89 +2753,92 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11">
+        <v>99999</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J11">
-        <v>14</v>
-      </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11">
+        <v>14</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="L11">
-        <v>14</v>
-      </c>
       <c r="M11">
+        <v>14</v>
+      </c>
+      <c r="N11">
         <v>1</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11" t="s">
         <v>27</v>
       </c>
-      <c r="P11">
-        <v>14</v>
-      </c>
-      <c r="Q11" s="1" t="s">
+      <c r="Q11">
+        <v>14</v>
+      </c>
+      <c r="R11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="R11">
-        <v>14</v>
-      </c>
-      <c r="S11" s="3" t="s">
+      <c r="S11">
+        <v>14</v>
+      </c>
+      <c r="T11" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="T11" s="4">
-        <v>14</v>
-      </c>
-      <c r="U11" s="3" t="s">
+      <c r="U11" s="4">
+        <v>14</v>
+      </c>
+      <c r="V11" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="V11" s="4">
-        <v>14</v>
-      </c>
-      <c r="W11" s="5" t="s">
+      <c r="W11" s="4">
+        <v>14</v>
+      </c>
+      <c r="X11" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="X11" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y11" s="5" t="s">
+      <c r="Y11" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z11" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="Z11" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA11" t="s">
+      <c r="AA11" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB11" t="s">
         <v>202</v>
       </c>
-      <c r="AB11">
-        <v>14</v>
-      </c>
-      <c r="AC11" s="1" t="s">
+      <c r="AC11">
+        <v>14</v>
+      </c>
+      <c r="AD11" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="AD11">
-        <v>14</v>
-      </c>
-      <c r="AE11" t="s">
+      <c r="AE11">
+        <v>14</v>
+      </c>
+      <c r="AF11" t="s">
         <v>243</v>
       </c>
-      <c r="AF11">
-        <v>14</v>
-      </c>
-      <c r="AG11" s="1" t="s">
+      <c r="AG11">
+        <v>14</v>
+      </c>
+      <c r="AH11" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="AH11">
-        <v>14</v>
-      </c>
-      <c r="AI11" s="1" t="s">
+      <c r="AI11">
+        <v>14</v>
+      </c>
+      <c r="AJ11" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="56.25">
+    <row r="12" spans="1:36" ht="56.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2829,89 +2861,92 @@
       <c r="H12">
         <v>0</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12">
+        <v>99999</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J12">
-        <v>14</v>
-      </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12">
+        <v>14</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="L12">
-        <v>14</v>
-      </c>
       <c r="M12">
+        <v>14</v>
+      </c>
+      <c r="N12">
         <v>1</v>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12" t="s">
         <v>30</v>
       </c>
-      <c r="P12">
-        <v>14</v>
-      </c>
-      <c r="Q12" s="1" t="s">
+      <c r="Q12">
+        <v>14</v>
+      </c>
+      <c r="R12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R12">
-        <v>14</v>
-      </c>
-      <c r="S12" s="3" t="s">
+      <c r="S12">
+        <v>14</v>
+      </c>
+      <c r="T12" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="T12" s="4">
-        <v>14</v>
-      </c>
-      <c r="U12" s="3" t="s">
+      <c r="U12" s="4">
+        <v>14</v>
+      </c>
+      <c r="V12" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="V12" s="4">
-        <v>14</v>
-      </c>
-      <c r="W12" s="5" t="s">
+      <c r="W12" s="4">
+        <v>14</v>
+      </c>
+      <c r="X12" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="X12" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y12" s="5" t="s">
+      <c r="Y12" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z12" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="Z12" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA12" t="s">
+      <c r="AA12" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB12" t="s">
         <v>204</v>
       </c>
-      <c r="AB12">
-        <v>14</v>
-      </c>
-      <c r="AC12" s="1" t="s">
+      <c r="AC12">
+        <v>14</v>
+      </c>
+      <c r="AD12" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="AD12">
-        <v>14</v>
-      </c>
-      <c r="AE12" t="s">
+      <c r="AE12">
+        <v>14</v>
+      </c>
+      <c r="AF12" t="s">
         <v>245</v>
       </c>
-      <c r="AF12">
-        <v>14</v>
-      </c>
-      <c r="AG12" s="1" t="s">
+      <c r="AG12">
+        <v>14</v>
+      </c>
+      <c r="AH12" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="AH12">
-        <v>14</v>
-      </c>
-      <c r="AI12" s="1" t="s">
+      <c r="AI12">
+        <v>14</v>
+      </c>
+      <c r="AJ12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="225" customHeight="1">
+    <row r="13" spans="1:36" ht="225" customHeight="1">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2936,89 +2971,92 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13">
+        <v>99999</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="J13">
-        <v>14</v>
-      </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13">
+        <v>14</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>12</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>1</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>60</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>38</v>
       </c>
-      <c r="P13">
-        <v>14</v>
-      </c>
-      <c r="Q13" s="1" t="s">
+      <c r="Q13">
+        <v>14</v>
+      </c>
+      <c r="R13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>10</v>
       </c>
-      <c r="S13" s="3" t="s">
+      <c r="T13" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="T13" s="4">
-        <v>14</v>
-      </c>
-      <c r="U13" s="3" t="s">
+      <c r="U13" s="4">
+        <v>14</v>
+      </c>
+      <c r="V13" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="V13" s="4">
+      <c r="W13" s="4">
         <v>12</v>
       </c>
-      <c r="W13" s="5" t="s">
+      <c r="X13" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="X13" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y13" s="5" t="s">
+      <c r="Y13" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z13" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="Z13" s="6">
+      <c r="AA13" s="6">
         <v>12</v>
       </c>
-      <c r="AA13" t="s">
+      <c r="AB13" t="s">
         <v>210</v>
       </c>
-      <c r="AB13">
-        <v>14</v>
-      </c>
-      <c r="AC13" s="1" t="s">
+      <c r="AC13">
+        <v>14</v>
+      </c>
+      <c r="AD13" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="AD13">
+      <c r="AE13">
         <v>10</v>
       </c>
-      <c r="AE13" t="s">
+      <c r="AF13" t="s">
         <v>250</v>
       </c>
-      <c r="AF13">
-        <v>14</v>
-      </c>
-      <c r="AG13" s="1" t="s">
+      <c r="AG13">
+        <v>14</v>
+      </c>
+      <c r="AH13" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="AH13">
+      <c r="AI13">
         <v>10</v>
       </c>
-      <c r="AI13" s="1" t="s">
+      <c r="AJ13" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="252" customHeight="1">
+    <row r="14" spans="1:36" ht="252" customHeight="1">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3041,89 +3079,92 @@
       <c r="H14" s="1">
         <v>0</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14">
+        <v>99999</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="J14" s="1">
-        <v>14</v>
-      </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" s="1">
+        <v>14</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="L14" s="1">
+      <c r="M14" s="1">
         <v>12</v>
       </c>
-      <c r="M14" s="1">
+      <c r="N14" s="1">
         <v>1</v>
       </c>
-      <c r="N14" s="1">
-        <v>0</v>
-      </c>
-      <c r="O14" s="1" t="s">
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P14" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q14" s="1" t="s">
+      <c r="Q14" s="1">
+        <v>14</v>
+      </c>
+      <c r="R14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="R14" s="1">
+      <c r="S14" s="1">
         <v>12</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="T14" s="4">
-        <v>14</v>
-      </c>
-      <c r="U14" s="3" t="s">
+      <c r="U14" s="4">
+        <v>14</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="V14" s="4">
+      <c r="W14" s="4">
         <v>12</v>
       </c>
-      <c r="W14" s="5" t="s">
+      <c r="X14" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="X14" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y14" s="5" t="s">
+      <c r="Y14" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z14" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="Z14" s="6">
+      <c r="AA14" s="6">
         <v>12</v>
       </c>
-      <c r="AA14" s="1" t="s">
+      <c r="AB14" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="AB14">
-        <v>14</v>
-      </c>
-      <c r="AC14" s="1" t="s">
+      <c r="AC14">
+        <v>14</v>
+      </c>
+      <c r="AD14" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="AD14">
+      <c r="AE14">
         <v>12</v>
       </c>
-      <c r="AE14" s="1" t="s">
+      <c r="AF14" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="AF14">
-        <v>14</v>
-      </c>
-      <c r="AG14" s="1" t="s">
+      <c r="AG14">
+        <v>14</v>
+      </c>
+      <c r="AH14" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="AH14">
+      <c r="AI14">
         <v>12</v>
       </c>
-      <c r="AI14" s="1" t="s">
+      <c r="AJ14" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="56.25">
+    <row r="15" spans="1:36" ht="56.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3146,29 +3187,32 @@
       <c r="H15" s="1">
         <v>0</v>
       </c>
-      <c r="J15" s="1">
-        <v>14</v>
-      </c>
-      <c r="L15" s="1">
-        <v>14</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1">
-        <v>0</v>
-      </c>
-      <c r="P15" s="1">
-        <v>14</v>
-      </c>
-      <c r="R15" s="1">
-        <v>14</v>
-      </c>
-      <c r="AI15" s="1" t="s">
+      <c r="I15">
+        <v>99999</v>
+      </c>
+      <c r="K15" s="1">
+        <v>14</v>
+      </c>
+      <c r="M15" s="1">
+        <v>14</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>14</v>
+      </c>
+      <c r="S15" s="1">
+        <v>14</v>
+      </c>
+      <c r="AJ15" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="56.25">
+    <row r="16" spans="1:36" ht="56.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3191,89 +3235,92 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16">
+        <v>99999</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="J16" s="1">
-        <v>14</v>
-      </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="1">
+        <v>14</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="L16" s="1">
-        <v>14</v>
-      </c>
-      <c r="M16">
+      <c r="M16" s="1">
+        <v>14</v>
+      </c>
+      <c r="N16">
         <v>1</v>
       </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" s="1" t="s">
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="P16" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q16" s="1" t="s">
+      <c r="Q16" s="1">
+        <v>14</v>
+      </c>
+      <c r="R16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="R16" s="1">
-        <v>14</v>
-      </c>
-      <c r="S16" s="3" t="s">
+      <c r="S16" s="1">
+        <v>14</v>
+      </c>
+      <c r="T16" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="T16" s="4">
-        <v>14</v>
-      </c>
-      <c r="U16" s="3" t="s">
+      <c r="U16" s="4">
+        <v>14</v>
+      </c>
+      <c r="V16" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="V16" s="4">
-        <v>14</v>
-      </c>
-      <c r="W16" s="5" t="s">
+      <c r="W16" s="4">
+        <v>14</v>
+      </c>
+      <c r="X16" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="X16" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y16" s="5" t="s">
+      <c r="Y16" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z16" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="Z16" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA16" s="1" t="s">
+      <c r="AA16" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB16" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="AB16">
-        <v>14</v>
-      </c>
-      <c r="AC16" s="1" t="s">
+      <c r="AC16">
+        <v>14</v>
+      </c>
+      <c r="AD16" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="AD16">
-        <v>14</v>
-      </c>
-      <c r="AE16" s="1" t="s">
+      <c r="AE16">
+        <v>14</v>
+      </c>
+      <c r="AF16" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="AF16">
-        <v>14</v>
-      </c>
-      <c r="AG16" s="1" t="s">
+      <c r="AG16">
+        <v>14</v>
+      </c>
+      <c r="AH16" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="AH16">
-        <v>14</v>
-      </c>
-      <c r="AI16" t="s">
+      <c r="AI16">
+        <v>14</v>
+      </c>
+      <c r="AJ16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="56.25">
+    <row r="17" spans="1:36" ht="56.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -3296,89 +3343,92 @@
       <c r="H17">
         <v>0</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17">
+        <v>99999</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J17" s="1">
-        <v>14</v>
-      </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" s="1">
+        <v>14</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L17" s="1">
-        <v>14</v>
-      </c>
-      <c r="M17">
+      <c r="M17" s="1">
+        <v>14</v>
+      </c>
+      <c r="N17">
         <v>1</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" s="1" t="s">
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="P17" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q17" s="1" t="s">
+      <c r="Q17" s="1">
+        <v>14</v>
+      </c>
+      <c r="R17" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="R17" s="1">
-        <v>14</v>
-      </c>
-      <c r="S17" s="3" t="s">
+      <c r="S17" s="1">
+        <v>14</v>
+      </c>
+      <c r="T17" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="T17" s="4">
-        <v>14</v>
-      </c>
-      <c r="U17" s="3" t="s">
+      <c r="U17" s="4">
+        <v>14</v>
+      </c>
+      <c r="V17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="V17" s="4">
-        <v>14</v>
-      </c>
-      <c r="W17" s="5" t="s">
+      <c r="W17" s="4">
+        <v>14</v>
+      </c>
+      <c r="X17" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="X17" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y17" s="5" t="s">
+      <c r="Y17" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z17" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="Z17" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA17" s="1" t="s">
+      <c r="AA17" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB17" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="AB17">
-        <v>14</v>
-      </c>
-      <c r="AC17" s="1" t="s">
+      <c r="AC17">
+        <v>14</v>
+      </c>
+      <c r="AD17" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="AD17">
-        <v>14</v>
-      </c>
-      <c r="AE17" s="1" t="s">
+      <c r="AE17">
+        <v>14</v>
+      </c>
+      <c r="AF17" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="AF17">
-        <v>14</v>
-      </c>
-      <c r="AG17" s="1" t="s">
+      <c r="AG17">
+        <v>14</v>
+      </c>
+      <c r="AH17" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="AH17">
-        <v>14</v>
-      </c>
-      <c r="AI17" t="s">
+      <c r="AI17">
+        <v>14</v>
+      </c>
+      <c r="AJ17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="56.25">
+    <row r="18" spans="1:36" ht="56.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3400,89 +3450,92 @@
       <c r="H18">
         <v>0</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18">
+        <v>99999</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="J18" s="1">
-        <v>14</v>
-      </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" s="1">
+        <v>14</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="L18" s="1">
-        <v>14</v>
-      </c>
-      <c r="M18">
+      <c r="M18" s="1">
+        <v>14</v>
+      </c>
+      <c r="N18">
         <v>1</v>
       </c>
-      <c r="N18" s="1">
-        <v>0</v>
-      </c>
-      <c r="O18" s="1" t="s">
+      <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="P18" s="1">
+      <c r="Q18" s="1">
         <v>12</v>
       </c>
-      <c r="Q18" s="1" t="s">
+      <c r="R18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="R18" s="1">
-        <v>14</v>
-      </c>
-      <c r="S18" s="3" t="s">
+      <c r="S18" s="1">
+        <v>14</v>
+      </c>
+      <c r="T18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="T18" s="4">
-        <v>14</v>
-      </c>
-      <c r="U18" s="3" t="s">
+      <c r="U18" s="4">
+        <v>14</v>
+      </c>
+      <c r="V18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="V18" s="4">
-        <v>14</v>
-      </c>
-      <c r="W18" s="5" t="s">
+      <c r="W18" s="4">
+        <v>14</v>
+      </c>
+      <c r="X18" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="X18" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y18" s="5" t="s">
+      <c r="Y18" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z18" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="Z18" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA18" s="1" t="s">
+      <c r="AA18" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB18" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="AB18">
+      <c r="AC18">
         <v>12</v>
       </c>
-      <c r="AC18" s="1" t="s">
+      <c r="AD18" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="AD18">
-        <v>14</v>
-      </c>
-      <c r="AE18" s="1" t="s">
+      <c r="AE18">
+        <v>14</v>
+      </c>
+      <c r="AF18" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="AF18">
+      <c r="AG18">
         <v>12</v>
       </c>
-      <c r="AG18" s="1" t="s">
+      <c r="AH18" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AH18">
-        <v>14</v>
-      </c>
-      <c r="AI18" t="s">
+      <c r="AI18">
+        <v>14</v>
+      </c>
+      <c r="AJ18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="56.25">
+    <row r="19" spans="1:36" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3505,89 +3558,92 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19">
+        <v>99999</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J19" s="1">
-        <v>14</v>
-      </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" s="1">
+        <v>14</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="L19" s="1">
-        <v>14</v>
-      </c>
-      <c r="M19">
+      <c r="M19" s="1">
+        <v>14</v>
+      </c>
+      <c r="N19">
         <v>1</v>
       </c>
-      <c r="N19" s="1">
-        <v>0</v>
-      </c>
-      <c r="O19" s="1" t="s">
+      <c r="O19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P19" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q19" s="1" t="s">
+      <c r="Q19" s="1">
+        <v>14</v>
+      </c>
+      <c r="R19" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="R19" s="1">
-        <v>14</v>
-      </c>
-      <c r="S19" s="3" t="s">
+      <c r="S19" s="1">
+        <v>14</v>
+      </c>
+      <c r="T19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="T19" s="4">
-        <v>14</v>
-      </c>
-      <c r="U19" s="3" t="s">
+      <c r="U19" s="4">
+        <v>14</v>
+      </c>
+      <c r="V19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="V19" s="4">
-        <v>14</v>
-      </c>
-      <c r="W19" s="5" t="s">
+      <c r="W19" s="4">
+        <v>14</v>
+      </c>
+      <c r="X19" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="X19" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y19" s="5" t="s">
+      <c r="Y19" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z19" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="Z19" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA19" s="1" t="s">
+      <c r="AA19" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB19" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="AB19">
-        <v>14</v>
-      </c>
-      <c r="AC19" s="1" t="s">
+      <c r="AC19">
+        <v>14</v>
+      </c>
+      <c r="AD19" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="AD19">
-        <v>14</v>
-      </c>
-      <c r="AE19" s="1" t="s">
+      <c r="AE19">
+        <v>14</v>
+      </c>
+      <c r="AF19" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="AF19">
-        <v>14</v>
-      </c>
-      <c r="AG19" s="1" t="s">
+      <c r="AG19">
+        <v>14</v>
+      </c>
+      <c r="AH19" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="AH19">
-        <v>14</v>
-      </c>
-      <c r="AI19" t="s">
+      <c r="AI19">
+        <v>14</v>
+      </c>
+      <c r="AJ19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="56.25">
+    <row r="20" spans="1:36" ht="56.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -3609,89 +3665,92 @@
       <c r="H20">
         <v>0</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20">
+        <v>99999</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J20" s="1">
-        <v>14</v>
-      </c>
-      <c r="K20" s="1" t="s">
+      <c r="K20" s="1">
+        <v>14</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="L20" s="1">
-        <v>14</v>
-      </c>
-      <c r="M20">
+      <c r="M20" s="1">
+        <v>14</v>
+      </c>
+      <c r="N20">
         <v>1</v>
       </c>
-      <c r="N20" s="1">
-        <v>0</v>
-      </c>
-      <c r="O20" s="1" t="s">
+      <c r="O20" s="1">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="P20" s="1">
+      <c r="Q20" s="1">
         <v>12</v>
       </c>
-      <c r="Q20" s="1" t="s">
+      <c r="R20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="R20" s="1">
-        <v>14</v>
-      </c>
-      <c r="S20" s="3" t="s">
+      <c r="S20" s="1">
+        <v>14</v>
+      </c>
+      <c r="T20" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="T20" s="4">
-        <v>14</v>
-      </c>
-      <c r="U20" s="3" t="s">
+      <c r="U20" s="4">
+        <v>14</v>
+      </c>
+      <c r="V20" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="V20" s="4">
-        <v>14</v>
-      </c>
-      <c r="W20" s="5" t="s">
+      <c r="W20" s="4">
+        <v>14</v>
+      </c>
+      <c r="X20" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="X20" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y20" s="5" t="s">
+      <c r="Y20" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z20" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="Z20" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA20" s="1" t="s">
+      <c r="AA20" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB20" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="AB20">
+      <c r="AC20">
         <v>12</v>
       </c>
-      <c r="AC20" s="1" t="s">
+      <c r="AD20" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="AD20">
-        <v>14</v>
-      </c>
-      <c r="AE20" s="1" t="s">
+      <c r="AE20">
+        <v>14</v>
+      </c>
+      <c r="AF20" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="AF20">
+      <c r="AG20">
         <v>12</v>
       </c>
-      <c r="AG20" s="1" t="s">
+      <c r="AH20" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="AH20">
-        <v>14</v>
-      </c>
-      <c r="AI20" t="s">
+      <c r="AI20">
+        <v>14</v>
+      </c>
+      <c r="AJ20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="257.25" customHeight="1">
+    <row r="21" spans="1:36" ht="257.25" customHeight="1">
       <c r="A21">
         <v>19</v>
       </c>
@@ -3716,89 +3775,92 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21">
+        <v>99999</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="J21" s="1">
-        <v>14</v>
-      </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" s="1">
+        <v>14</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="L21" s="1">
+      <c r="M21" s="1">
         <v>12</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>1</v>
       </c>
-      <c r="N21" s="1">
+      <c r="O21" s="1">
         <v>1</v>
       </c>
-      <c r="O21" s="1" t="s">
+      <c r="P21" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="P21" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q21" s="1" t="s">
+      <c r="Q21" s="1">
+        <v>14</v>
+      </c>
+      <c r="R21" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="R21" s="1">
+      <c r="S21" s="1">
         <v>10</v>
       </c>
-      <c r="S21" s="3" t="s">
+      <c r="T21" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="T21" s="4">
-        <v>14</v>
-      </c>
-      <c r="U21" s="3" t="s">
+      <c r="U21" s="4">
+        <v>14</v>
+      </c>
+      <c r="V21" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="V21" s="4">
+      <c r="W21" s="4">
         <v>12</v>
       </c>
-      <c r="W21" s="5" t="s">
+      <c r="X21" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="X21" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y21" s="5" t="s">
+      <c r="Y21" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z21" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="Z21" s="6">
+      <c r="AA21" s="6">
         <v>12</v>
       </c>
-      <c r="AA21" s="1" t="s">
+      <c r="AB21" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="AB21">
-        <v>14</v>
-      </c>
-      <c r="AC21" s="1" t="s">
+      <c r="AC21">
+        <v>14</v>
+      </c>
+      <c r="AD21" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="AD21">
+      <c r="AE21">
         <v>10</v>
       </c>
-      <c r="AE21" s="1" t="s">
+      <c r="AF21" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="AF21">
-        <v>14</v>
-      </c>
-      <c r="AG21" s="1" t="s">
+      <c r="AG21">
+        <v>14</v>
+      </c>
+      <c r="AH21" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="AH21">
+      <c r="AI21">
         <v>10</v>
       </c>
-      <c r="AI21" s="1" t="s">
+      <c r="AJ21" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="409.5">
+    <row r="22" spans="1:36" ht="409.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -3820,89 +3882,92 @@
       <c r="H22">
         <v>0</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22">
+        <v>99999</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>12</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L22">
-        <v>14</v>
-      </c>
       <c r="M22">
+        <v>14</v>
+      </c>
+      <c r="N22">
         <v>1</v>
       </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" s="1" t="s">
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>12</v>
       </c>
-      <c r="Q22" s="1" t="s">
+      <c r="R22" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <v>12</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="T22" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="T22" s="4">
+      <c r="U22" s="4">
         <v>12</v>
       </c>
-      <c r="U22" s="3" t="s">
+      <c r="V22" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="V22" s="4">
-        <v>14</v>
-      </c>
-      <c r="W22" s="5" t="s">
+      <c r="W22" s="4">
+        <v>14</v>
+      </c>
+      <c r="X22" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="X22" s="6">
+      <c r="Y22" s="6">
         <v>12</v>
       </c>
-      <c r="Y22" s="5" t="s">
+      <c r="Z22" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="Z22" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA22" s="1" t="s">
+      <c r="AA22" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB22" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="AB22">
+      <c r="AC22">
         <v>12</v>
       </c>
-      <c r="AC22" s="1" t="s">
+      <c r="AD22" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="AD22">
+      <c r="AE22">
         <v>12</v>
       </c>
-      <c r="AE22" s="1" t="s">
+      <c r="AF22" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="AF22">
+      <c r="AG22">
         <v>12</v>
       </c>
-      <c r="AG22" s="1" t="s">
+      <c r="AH22" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="AH22">
+      <c r="AI22">
         <v>12</v>
       </c>
-      <c r="AI22" s="1" t="s">
+      <c r="AJ22" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="409.5">
+    <row r="23" spans="1:36" ht="409.5">
       <c r="A23">
         <v>21</v>
       </c>
@@ -3924,89 +3989,92 @@
       <c r="H23">
         <v>0</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23">
+        <v>99999</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="J23" s="1">
+      <c r="K23" s="1">
         <v>12</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="L23" s="4">
+      <c r="M23" s="4">
         <v>12</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>1</v>
       </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23" s="1" t="s">
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="P23" s="1">
+      <c r="Q23" s="1">
         <v>12</v>
       </c>
-      <c r="Q23" s="1" t="s">
+      <c r="R23" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>12</v>
       </c>
-      <c r="S23" s="7" t="s">
+      <c r="T23" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="T23" s="4">
+      <c r="U23" s="4">
         <v>12</v>
       </c>
-      <c r="U23" s="8" t="s">
+      <c r="V23" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="V23" s="4">
+      <c r="W23" s="4">
         <v>12</v>
       </c>
-      <c r="W23" s="5" t="s">
+      <c r="X23" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="X23" s="4">
+      <c r="Y23" s="4">
         <v>12</v>
       </c>
-      <c r="Y23" s="1" t="s">
+      <c r="Z23" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="Z23" s="4">
+      <c r="AA23" s="4">
         <v>12</v>
       </c>
-      <c r="AA23" s="1" t="s">
+      <c r="AB23" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="AB23">
+      <c r="AC23">
         <v>12</v>
       </c>
-      <c r="AC23" s="1" t="s">
+      <c r="AD23" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="AD23">
+      <c r="AE23">
         <v>10</v>
       </c>
-      <c r="AE23" s="1" t="s">
+      <c r="AF23" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="AF23">
+      <c r="AG23">
         <v>12</v>
       </c>
-      <c r="AG23" s="1" t="s">
+      <c r="AH23" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="AH23">
+      <c r="AI23">
         <v>10</v>
       </c>
-      <c r="AI23" s="1" t="s">
+      <c r="AJ23" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="56.25">
+    <row r="24" spans="1:36" ht="56.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -4028,89 +4096,92 @@
       <c r="H24">
         <v>0</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24">
+        <v>99999</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="J24" s="1">
-        <v>14</v>
-      </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" s="1">
+        <v>14</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="L24">
-        <v>14</v>
-      </c>
       <c r="M24">
+        <v>14</v>
+      </c>
+      <c r="N24">
         <v>1</v>
       </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24" s="1" t="s">
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="P24" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q24" s="1" t="s">
+      <c r="Q24" s="1">
+        <v>14</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="R24" s="1">
-        <v>14</v>
-      </c>
-      <c r="S24" s="3" t="s">
+      <c r="S24" s="1">
+        <v>14</v>
+      </c>
+      <c r="T24" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="T24" s="1">
-        <v>14</v>
-      </c>
-      <c r="U24" s="7" t="s">
+      <c r="U24" s="1">
+        <v>14</v>
+      </c>
+      <c r="V24" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="V24" s="1">
-        <v>14</v>
-      </c>
-      <c r="W24" s="5" t="s">
+      <c r="W24" s="1">
+        <v>14</v>
+      </c>
+      <c r="X24" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="X24" s="1">
-        <v>14</v>
-      </c>
-      <c r="Y24" s="5" t="s">
+      <c r="Y24" s="1">
+        <v>14</v>
+      </c>
+      <c r="Z24" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="Z24" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA24" s="1" t="s">
+      <c r="AA24" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB24" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="AB24">
+      <c r="AC24">
         <v>12</v>
       </c>
-      <c r="AC24" s="1" t="s">
+      <c r="AD24" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="AD24" s="6">
-        <v>14</v>
-      </c>
-      <c r="AE24" s="1" t="s">
+      <c r="AE24" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF24" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="AF24">
+      <c r="AG24">
         <v>12</v>
       </c>
-      <c r="AG24" s="1" t="s">
+      <c r="AH24" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="AH24" s="6">
-        <v>14</v>
-      </c>
-      <c r="AI24" s="1" t="s">
+      <c r="AI24" s="6">
+        <v>14</v>
+      </c>
+      <c r="AJ24" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="56.25">
+    <row r="25" spans="1:36" ht="56.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -4132,89 +4203,92 @@
       <c r="H25">
         <v>0</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25">
+        <v>99999</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="J25" s="1">
-        <v>14</v>
-      </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" s="1">
+        <v>14</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="L25">
-        <v>14</v>
-      </c>
       <c r="M25">
+        <v>14</v>
+      </c>
+      <c r="N25">
         <v>1</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25" s="1" t="s">
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="P25" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q25" s="1" t="s">
+      <c r="Q25" s="1">
+        <v>14</v>
+      </c>
+      <c r="R25" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="R25" s="1">
-        <v>14</v>
-      </c>
-      <c r="S25" s="7" t="s">
+      <c r="S25" s="1">
+        <v>14</v>
+      </c>
+      <c r="T25" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="T25" s="1">
-        <v>14</v>
-      </c>
-      <c r="U25" s="3" t="s">
+      <c r="U25" s="1">
+        <v>14</v>
+      </c>
+      <c r="V25" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="V25" s="1">
-        <v>14</v>
-      </c>
-      <c r="W25" s="5" t="s">
+      <c r="W25" s="1">
+        <v>14</v>
+      </c>
+      <c r="X25" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="X25" s="1">
-        <v>14</v>
-      </c>
-      <c r="Y25" t="s">
+      <c r="Y25" s="1">
+        <v>14</v>
+      </c>
+      <c r="Z25" t="s">
         <v>307</v>
       </c>
-      <c r="Z25" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA25" t="s">
+      <c r="AA25" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB25" t="s">
         <v>308</v>
       </c>
-      <c r="AB25">
+      <c r="AC25">
         <v>12</v>
       </c>
-      <c r="AC25" s="1" t="s">
+      <c r="AD25" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="AD25" s="6">
-        <v>14</v>
-      </c>
-      <c r="AE25" s="1" t="s">
+      <c r="AE25" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF25" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="AF25">
+      <c r="AG25">
         <v>12</v>
       </c>
-      <c r="AG25" s="1" t="s">
+      <c r="AH25" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="AH25" s="6">
-        <v>14</v>
-      </c>
-      <c r="AI25" s="1" t="s">
+      <c r="AI25" s="6">
+        <v>14</v>
+      </c>
+      <c r="AJ25" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="75">
+    <row r="26" spans="1:36" ht="75">
       <c r="A26">
         <v>24</v>
       </c>
@@ -4236,89 +4310,92 @@
       <c r="H26">
         <v>0</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26">
+        <v>99999</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J26" s="1">
-        <v>14</v>
-      </c>
-      <c r="K26" s="1" t="s">
+      <c r="K26" s="1">
+        <v>14</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="L26">
-        <v>14</v>
-      </c>
       <c r="M26">
+        <v>14</v>
+      </c>
+      <c r="N26">
         <v>1</v>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" s="1" t="s">
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="P26" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q26" s="1" t="s">
+      <c r="Q26" s="1">
+        <v>14</v>
+      </c>
+      <c r="R26" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="R26" s="1">
-        <v>14</v>
-      </c>
-      <c r="S26" s="7" t="s">
+      <c r="S26" s="1">
+        <v>14</v>
+      </c>
+      <c r="T26" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="T26" s="1">
-        <v>14</v>
-      </c>
-      <c r="U26" s="8" t="s">
+      <c r="U26" s="1">
+        <v>14</v>
+      </c>
+      <c r="V26" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="V26" s="1">
-        <v>14</v>
-      </c>
-      <c r="W26" s="5" t="s">
+      <c r="W26" s="1">
+        <v>14</v>
+      </c>
+      <c r="X26" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="X26" s="1">
-        <v>14</v>
-      </c>
-      <c r="Y26" s="5" t="s">
+      <c r="Y26" s="1">
+        <v>14</v>
+      </c>
+      <c r="Z26" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="Z26" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA26" s="1" t="s">
+      <c r="AA26" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB26" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="AB26">
+      <c r="AC26">
         <v>12</v>
       </c>
-      <c r="AC26" s="1" t="s">
+      <c r="AD26" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="AD26" s="6">
-        <v>14</v>
-      </c>
-      <c r="AE26" s="1" t="s">
+      <c r="AE26" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF26" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="AF26">
+      <c r="AG26">
         <v>12</v>
       </c>
-      <c r="AG26" s="1" t="s">
+      <c r="AH26" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="AH26" s="6">
-        <v>14</v>
-      </c>
-      <c r="AI26" s="1" t="s">
+      <c r="AI26" s="6">
+        <v>14</v>
+      </c>
+      <c r="AJ26" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="56.25">
+    <row r="27" spans="1:36" ht="56.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -4340,89 +4417,92 @@
       <c r="H27">
         <v>0</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27">
+        <v>99999</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="J27" s="1">
-        <v>14</v>
-      </c>
-      <c r="K27" s="1" t="s">
+      <c r="K27" s="1">
+        <v>14</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="L27">
-        <v>14</v>
-      </c>
       <c r="M27">
+        <v>14</v>
+      </c>
+      <c r="N27">
         <v>1</v>
       </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" s="1" t="s">
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="P27" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q27" s="1" t="s">
+      <c r="Q27" s="1">
+        <v>14</v>
+      </c>
+      <c r="R27" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="R27" s="1">
-        <v>14</v>
-      </c>
-      <c r="S27" s="7" t="s">
+      <c r="S27" s="1">
+        <v>14</v>
+      </c>
+      <c r="T27" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="T27" s="1">
-        <v>14</v>
-      </c>
-      <c r="U27" s="8" t="s">
+      <c r="U27" s="1">
+        <v>14</v>
+      </c>
+      <c r="V27" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="V27" s="1">
-        <v>14</v>
-      </c>
-      <c r="W27" s="5" t="s">
+      <c r="W27" s="1">
+        <v>14</v>
+      </c>
+      <c r="X27" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="X27" s="1">
-        <v>14</v>
-      </c>
-      <c r="Y27" s="5" t="s">
+      <c r="Y27" s="1">
+        <v>14</v>
+      </c>
+      <c r="Z27" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="Z27" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA27" s="1" t="s">
+      <c r="AA27" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB27" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="AB27">
+      <c r="AC27">
         <v>12</v>
       </c>
-      <c r="AC27" s="1" t="s">
+      <c r="AD27" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="AD27" s="6">
-        <v>14</v>
-      </c>
-      <c r="AE27" s="1" t="s">
+      <c r="AE27" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF27" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="AF27">
+      <c r="AG27">
         <v>12</v>
       </c>
-      <c r="AG27" s="1" t="s">
+      <c r="AH27" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="AH27" s="6">
-        <v>14</v>
-      </c>
-      <c r="AI27" s="1" t="s">
+      <c r="AI27" s="6">
+        <v>14</v>
+      </c>
+      <c r="AJ27" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="75">
+    <row r="28" spans="1:36" ht="75">
       <c r="A28">
         <v>26</v>
       </c>
@@ -4444,104 +4524,107 @@
       <c r="H28">
         <v>0</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28">
+        <v>99999</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="J28" s="1">
-        <v>14</v>
-      </c>
-      <c r="K28" s="1" t="s">
+      <c r="K28" s="1">
+        <v>14</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="L28">
-        <v>14</v>
-      </c>
       <c r="M28">
+        <v>14</v>
+      </c>
+      <c r="N28">
         <v>1</v>
       </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28" s="1" t="s">
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="P28" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q28" s="1" t="s">
+      <c r="Q28" s="1">
+        <v>14</v>
+      </c>
+      <c r="R28" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="R28" s="1">
-        <v>14</v>
-      </c>
-      <c r="S28" s="7" t="s">
+      <c r="S28" s="1">
+        <v>14</v>
+      </c>
+      <c r="T28" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="T28" s="1">
-        <v>14</v>
-      </c>
-      <c r="U28" s="8" t="s">
+      <c r="U28" s="1">
+        <v>14</v>
+      </c>
+      <c r="V28" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="V28" s="1">
-        <v>14</v>
-      </c>
-      <c r="W28" s="5" t="s">
+      <c r="W28" s="1">
+        <v>14</v>
+      </c>
+      <c r="X28" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="X28" s="1">
-        <v>14</v>
-      </c>
-      <c r="Y28" s="5" t="s">
+      <c r="Y28" s="1">
+        <v>14</v>
+      </c>
+      <c r="Z28" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="Z28" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA28" s="1" t="s">
+      <c r="AA28" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB28" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="AB28">
+      <c r="AC28">
         <v>12</v>
       </c>
-      <c r="AC28" s="1" t="s">
+      <c r="AD28" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="AD28" s="6">
-        <v>14</v>
-      </c>
-      <c r="AE28" s="1" t="s">
+      <c r="AE28" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF28" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="AF28">
+      <c r="AG28">
         <v>12</v>
       </c>
-      <c r="AG28" s="1" t="s">
+      <c r="AH28" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="AH28" s="6">
-        <v>14</v>
-      </c>
-      <c r="AI28" s="1" t="s">
+      <c r="AI28" s="6">
+        <v>14</v>
+      </c>
+      <c r="AJ28" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="29" spans="1:35">
+    <row r="29" spans="1:36">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:35">
+    <row r="30" spans="1:36">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:35">
+    <row r="31" spans="1:36">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:35">
+    <row r="32" spans="1:36">
       <c r="A32">
         <v>30</v>
       </c>
@@ -9346,22 +9429,22 @@
         <v>990</v>
       </c>
     </row>
-    <row r="993" spans="1:35">
+    <row r="993" spans="1:36">
       <c r="A993">
         <v>991</v>
       </c>
     </row>
-    <row r="994" spans="1:35">
+    <row r="994" spans="1:36">
       <c r="A994">
         <v>992</v>
       </c>
     </row>
-    <row r="995" spans="1:35">
+    <row r="995" spans="1:36">
       <c r="A995">
         <v>993</v>
       </c>
     </row>
-    <row r="996" spans="1:35">
+    <row r="996" spans="1:36">
       <c r="A996">
         <v>994</v>
       </c>
@@ -9383,89 +9466,89 @@
       <c r="H996">
         <v>0</v>
       </c>
-      <c r="I996" s="1" t="s">
+      <c r="J996" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J996">
-        <v>14</v>
-      </c>
-      <c r="K996" t="s">
+      <c r="K996">
+        <v>14</v>
+      </c>
+      <c r="L996" t="s">
         <v>44</v>
       </c>
-      <c r="L996">
-        <v>14</v>
-      </c>
       <c r="M996">
+        <v>14</v>
+      </c>
+      <c r="N996">
         <v>1</v>
       </c>
-      <c r="N996">
-        <v>0</v>
-      </c>
-      <c r="O996" t="s">
+      <c r="O996">
+        <v>0</v>
+      </c>
+      <c r="P996" t="s">
         <v>43</v>
       </c>
-      <c r="P996">
-        <v>14</v>
-      </c>
-      <c r="Q996" t="s">
+      <c r="Q996">
+        <v>14</v>
+      </c>
+      <c r="R996" t="s">
         <v>44</v>
       </c>
-      <c r="R996">
-        <v>14</v>
-      </c>
-      <c r="S996" s="3" t="s">
+      <c r="S996">
+        <v>14</v>
+      </c>
+      <c r="T996" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="T996" s="4">
-        <v>14</v>
-      </c>
-      <c r="U996" s="4" t="s">
+      <c r="U996" s="4">
+        <v>14</v>
+      </c>
+      <c r="V996" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="V996" s="4">
-        <v>14</v>
-      </c>
-      <c r="W996" s="5" t="s">
+      <c r="W996" s="4">
+        <v>14</v>
+      </c>
+      <c r="X996" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="X996" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y996" s="6" t="s">
+      <c r="Y996" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z996" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="Z996" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA996" t="s">
+      <c r="AA996" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB996" t="s">
         <v>141</v>
       </c>
-      <c r="AB996">
-        <v>14</v>
-      </c>
-      <c r="AC996" t="s">
+      <c r="AC996">
+        <v>14</v>
+      </c>
+      <c r="AD996" t="s">
         <v>228</v>
       </c>
-      <c r="AD996">
-        <v>14</v>
-      </c>
-      <c r="AE996" t="s">
+      <c r="AE996">
+        <v>14</v>
+      </c>
+      <c r="AF996" t="s">
         <v>141</v>
       </c>
-      <c r="AF996">
-        <v>14</v>
-      </c>
-      <c r="AG996" t="s">
+      <c r="AG996">
+        <v>14</v>
+      </c>
+      <c r="AH996" t="s">
         <v>266</v>
       </c>
-      <c r="AH996">
-        <v>14</v>
-      </c>
-      <c r="AI996" t="s">
+      <c r="AI996">
+        <v>14</v>
+      </c>
+      <c r="AJ996" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="997" spans="1:35" ht="93.75">
+    <row r="997" spans="1:36" ht="93.75">
       <c r="A997">
         <v>995</v>
       </c>
@@ -9490,89 +9573,89 @@
       <c r="H997">
         <v>0</v>
       </c>
-      <c r="I997" s="1" t="s">
+      <c r="J997" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J997">
-        <v>14</v>
-      </c>
-      <c r="K997" t="s">
+      <c r="K997">
+        <v>14</v>
+      </c>
+      <c r="L997" t="s">
         <v>47</v>
       </c>
-      <c r="L997">
-        <v>14</v>
-      </c>
       <c r="M997">
+        <v>14</v>
+      </c>
+      <c r="N997">
         <v>1</v>
       </c>
-      <c r="N997">
-        <v>0</v>
-      </c>
-      <c r="O997" t="s">
+      <c r="O997">
+        <v>0</v>
+      </c>
+      <c r="P997" t="s">
         <v>48</v>
       </c>
-      <c r="P997">
-        <v>14</v>
-      </c>
-      <c r="Q997" t="s">
+      <c r="Q997">
+        <v>14</v>
+      </c>
+      <c r="R997" t="s">
         <v>47</v>
       </c>
-      <c r="R997">
-        <v>14</v>
-      </c>
-      <c r="S997" s="3" t="s">
+      <c r="S997">
+        <v>14</v>
+      </c>
+      <c r="T997" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="T997" s="4">
-        <v>14</v>
-      </c>
-      <c r="U997" s="4" t="s">
+      <c r="U997" s="4">
+        <v>14</v>
+      </c>
+      <c r="V997" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="V997" s="4">
-        <v>14</v>
-      </c>
-      <c r="W997" s="5" t="s">
+      <c r="W997" s="4">
+        <v>14</v>
+      </c>
+      <c r="X997" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="X997" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y997" s="6" t="s">
+      <c r="Y997" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z997" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="Z997" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA997" t="s">
+      <c r="AA997" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB997" t="s">
         <v>143</v>
       </c>
-      <c r="AB997">
-        <v>14</v>
-      </c>
-      <c r="AC997" t="s">
+      <c r="AC997">
+        <v>14</v>
+      </c>
+      <c r="AD997" t="s">
         <v>229</v>
       </c>
-      <c r="AD997">
-        <v>14</v>
-      </c>
-      <c r="AE997" t="s">
+      <c r="AE997">
+        <v>14</v>
+      </c>
+      <c r="AF997" t="s">
         <v>143</v>
       </c>
-      <c r="AF997">
-        <v>14</v>
-      </c>
-      <c r="AG997" t="s">
+      <c r="AG997">
+        <v>14</v>
+      </c>
+      <c r="AH997" t="s">
         <v>267</v>
       </c>
-      <c r="AH997">
-        <v>14</v>
-      </c>
-      <c r="AI997" s="1" t="s">
+      <c r="AI997">
+        <v>14</v>
+      </c>
+      <c r="AJ997" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="998" spans="1:35" ht="75">
+    <row r="998" spans="1:36" ht="75">
       <c r="A998">
         <v>996</v>
       </c>
@@ -9594,89 +9677,89 @@
       <c r="H998">
         <v>0</v>
       </c>
-      <c r="I998" s="1" t="s">
+      <c r="J998" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="J998">
-        <v>14</v>
-      </c>
-      <c r="K998" s="1" t="s">
+      <c r="K998">
+        <v>14</v>
+      </c>
+      <c r="L998" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L998">
-        <v>14</v>
-      </c>
       <c r="M998">
+        <v>14</v>
+      </c>
+      <c r="N998">
         <v>1</v>
       </c>
-      <c r="N998">
-        <v>0</v>
-      </c>
-      <c r="O998" t="s">
+      <c r="O998">
+        <v>0</v>
+      </c>
+      <c r="P998" t="s">
         <v>51</v>
       </c>
-      <c r="P998">
-        <v>14</v>
-      </c>
-      <c r="Q998" s="1" t="s">
+      <c r="Q998">
+        <v>14</v>
+      </c>
+      <c r="R998" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="R998">
-        <v>14</v>
-      </c>
-      <c r="S998" s="3" t="s">
+      <c r="S998">
+        <v>14</v>
+      </c>
+      <c r="T998" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="T998" s="4">
-        <v>14</v>
-      </c>
-      <c r="U998" s="3" t="s">
+      <c r="U998" s="4">
+        <v>14</v>
+      </c>
+      <c r="V998" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="V998" s="4">
-        <v>14</v>
-      </c>
-      <c r="W998" s="5" t="s">
+      <c r="W998" s="4">
+        <v>14</v>
+      </c>
+      <c r="X998" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="X998" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y998" s="5" t="s">
+      <c r="Y998" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z998" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="Z998" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA998" t="s">
+      <c r="AA998" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB998" t="s">
         <v>145</v>
       </c>
-      <c r="AB998">
-        <v>14</v>
-      </c>
-      <c r="AC998" s="1" t="s">
+      <c r="AC998">
+        <v>14</v>
+      </c>
+      <c r="AD998" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="AD998">
-        <v>14</v>
-      </c>
-      <c r="AE998" t="s">
+      <c r="AE998">
+        <v>14</v>
+      </c>
+      <c r="AF998" t="s">
         <v>145</v>
       </c>
-      <c r="AF998">
-        <v>14</v>
-      </c>
-      <c r="AG998" s="1" t="s">
+      <c r="AG998">
+        <v>14</v>
+      </c>
+      <c r="AH998" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="AH998">
-        <v>14</v>
-      </c>
-      <c r="AI998" s="1" t="s">
+      <c r="AI998">
+        <v>14</v>
+      </c>
+      <c r="AJ998" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="999" spans="1:35" ht="75">
+    <row r="999" spans="1:36" ht="75">
       <c r="A999">
         <v>997</v>
       </c>
@@ -9698,89 +9781,89 @@
       <c r="H999">
         <v>0</v>
       </c>
-      <c r="I999" s="1" t="s">
+      <c r="J999" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J999">
-        <v>14</v>
-      </c>
-      <c r="K999" s="1" t="s">
+      <c r="K999">
+        <v>14</v>
+      </c>
+      <c r="L999" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L999">
-        <v>14</v>
-      </c>
       <c r="M999">
+        <v>14</v>
+      </c>
+      <c r="N999">
         <v>1</v>
       </c>
-      <c r="N999">
-        <v>0</v>
-      </c>
-      <c r="O999" t="s">
+      <c r="O999">
+        <v>0</v>
+      </c>
+      <c r="P999" t="s">
         <v>54</v>
       </c>
-      <c r="P999">
-        <v>14</v>
-      </c>
-      <c r="Q999" s="1" t="s">
+      <c r="Q999">
+        <v>14</v>
+      </c>
+      <c r="R999" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R999">
-        <v>14</v>
-      </c>
-      <c r="S999" s="3" t="s">
+      <c r="S999">
+        <v>14</v>
+      </c>
+      <c r="T999" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="T999" s="4">
-        <v>14</v>
-      </c>
-      <c r="U999" s="3" t="s">
+      <c r="U999" s="4">
+        <v>14</v>
+      </c>
+      <c r="V999" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="V999" s="4">
-        <v>14</v>
-      </c>
-      <c r="W999" s="5" t="s">
+      <c r="W999" s="4">
+        <v>14</v>
+      </c>
+      <c r="X999" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="X999" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y999" s="5" t="s">
+      <c r="Y999" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z999" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="Z999" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA999" t="s">
+      <c r="AA999" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB999" t="s">
         <v>147</v>
       </c>
-      <c r="AB999">
-        <v>14</v>
-      </c>
-      <c r="AC999" s="1" t="s">
+      <c r="AC999">
+        <v>14</v>
+      </c>
+      <c r="AD999" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="AD999">
-        <v>14</v>
-      </c>
-      <c r="AE999" t="s">
+      <c r="AE999">
+        <v>14</v>
+      </c>
+      <c r="AF999" t="s">
         <v>147</v>
       </c>
-      <c r="AF999">
-        <v>14</v>
-      </c>
-      <c r="AG999" s="1" t="s">
+      <c r="AG999">
+        <v>14</v>
+      </c>
+      <c r="AH999" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="AH999">
-        <v>14</v>
-      </c>
-      <c r="AI999" s="1" t="s">
+      <c r="AI999">
+        <v>14</v>
+      </c>
+      <c r="AJ999" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="1000" spans="1:35" ht="75">
+    <row r="1000" spans="1:36" ht="75">
       <c r="A1000">
         <v>998</v>
       </c>
@@ -9802,89 +9885,89 @@
       <c r="H1000">
         <v>0</v>
       </c>
-      <c r="I1000" s="1" t="s">
+      <c r="J1000" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J1000">
-        <v>14</v>
-      </c>
-      <c r="K1000" s="1" t="s">
+      <c r="K1000">
+        <v>14</v>
+      </c>
+      <c r="L1000" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L1000">
-        <v>14</v>
-      </c>
       <c r="M1000">
+        <v>14</v>
+      </c>
+      <c r="N1000">
         <v>1</v>
       </c>
-      <c r="N1000">
-        <v>0</v>
-      </c>
-      <c r="O1000" s="1" t="s">
+      <c r="O1000">
+        <v>0</v>
+      </c>
+      <c r="P1000" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P1000">
-        <v>14</v>
-      </c>
-      <c r="Q1000" s="1" t="s">
+      <c r="Q1000">
+        <v>14</v>
+      </c>
+      <c r="R1000" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="R1000">
-        <v>14</v>
-      </c>
-      <c r="S1000" s="3" t="s">
+      <c r="S1000">
+        <v>14</v>
+      </c>
+      <c r="T1000" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="T1000" s="4">
-        <v>14</v>
-      </c>
-      <c r="U1000" s="3" t="s">
+      <c r="U1000" s="4">
+        <v>14</v>
+      </c>
+      <c r="V1000" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="V1000" s="4">
-        <v>14</v>
-      </c>
-      <c r="W1000" s="5" t="s">
+      <c r="W1000" s="4">
+        <v>14</v>
+      </c>
+      <c r="X1000" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="X1000" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y1000" s="5" t="s">
+      <c r="Y1000" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z1000" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="Z1000" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA1000" s="1" t="s">
+      <c r="AA1000" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB1000" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AB1000">
-        <v>14</v>
-      </c>
-      <c r="AC1000" s="1" t="s">
+      <c r="AC1000">
+        <v>14</v>
+      </c>
+      <c r="AD1000" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="AD1000">
-        <v>14</v>
-      </c>
-      <c r="AE1000" s="1" t="s">
+      <c r="AE1000">
+        <v>14</v>
+      </c>
+      <c r="AF1000" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AF1000">
-        <v>14</v>
-      </c>
-      <c r="AG1000" s="1" t="s">
+      <c r="AG1000">
+        <v>14</v>
+      </c>
+      <c r="AH1000" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="AH1000">
-        <v>14</v>
-      </c>
-      <c r="AI1000" s="1" t="s">
+      <c r="AI1000">
+        <v>14</v>
+      </c>
+      <c r="AJ1000" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="1001" spans="1:35">
+    <row r="1001" spans="1:36">
       <c r="A1001">
         <v>999</v>
       </c>
@@ -9906,89 +9989,89 @@
       <c r="H1001">
         <v>0</v>
       </c>
-      <c r="I1001" s="1" t="s">
+      <c r="J1001" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="J1001">
-        <v>14</v>
-      </c>
-      <c r="K1001" t="s">
+      <c r="K1001">
+        <v>14</v>
+      </c>
+      <c r="L1001" t="s">
         <v>57</v>
       </c>
-      <c r="L1001">
-        <v>14</v>
-      </c>
       <c r="M1001">
+        <v>14</v>
+      </c>
+      <c r="N1001">
         <v>1</v>
       </c>
-      <c r="N1001">
-        <v>0</v>
-      </c>
-      <c r="O1001" t="s">
+      <c r="O1001">
+        <v>0</v>
+      </c>
+      <c r="P1001" t="s">
         <v>56</v>
       </c>
-      <c r="P1001">
-        <v>14</v>
-      </c>
-      <c r="Q1001" t="s">
+      <c r="Q1001">
+        <v>14</v>
+      </c>
+      <c r="R1001" t="s">
         <v>57</v>
       </c>
-      <c r="R1001">
-        <v>14</v>
-      </c>
-      <c r="S1001" s="3" t="s">
+      <c r="S1001">
+        <v>14</v>
+      </c>
+      <c r="T1001" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="T1001" s="4">
-        <v>14</v>
-      </c>
-      <c r="U1001" s="4" t="s">
+      <c r="U1001" s="4">
+        <v>14</v>
+      </c>
+      <c r="V1001" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="V1001" s="4">
-        <v>14</v>
-      </c>
-      <c r="W1001" s="5" t="s">
+      <c r="W1001" s="4">
+        <v>14</v>
+      </c>
+      <c r="X1001" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="X1001" s="6">
-        <v>14</v>
-      </c>
-      <c r="Y1001" s="6" t="s">
+      <c r="Y1001" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z1001" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="Z1001" s="6">
-        <v>14</v>
-      </c>
-      <c r="AA1001" t="s">
+      <c r="AA1001" s="6">
+        <v>14</v>
+      </c>
+      <c r="AB1001" t="s">
         <v>151</v>
       </c>
-      <c r="AB1001">
-        <v>14</v>
-      </c>
-      <c r="AC1001" t="s">
+      <c r="AC1001">
+        <v>14</v>
+      </c>
+      <c r="AD1001" t="s">
         <v>233</v>
       </c>
-      <c r="AD1001">
-        <v>14</v>
-      </c>
-      <c r="AE1001" t="s">
+      <c r="AE1001">
+        <v>14</v>
+      </c>
+      <c r="AF1001" t="s">
         <v>151</v>
       </c>
-      <c r="AF1001">
-        <v>14</v>
-      </c>
-      <c r="AG1001" t="s">
+      <c r="AG1001">
+        <v>14</v>
+      </c>
+      <c r="AH1001" t="s">
         <v>271</v>
       </c>
-      <c r="AH1001">
-        <v>14</v>
-      </c>
-      <c r="AI1001" t="s">
+      <c r="AI1001">
+        <v>14</v>
+      </c>
+      <c r="AJ1001" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="1002" spans="1:35">
+    <row r="1002" spans="1:36">
       <c r="A1002">
         <v>1000</v>
       </c>
@@ -10010,73 +10093,73 @@
       <c r="H1002">
         <v>0</v>
       </c>
-      <c r="I1002" s="1" t="s">
+      <c r="J1002" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J1002">
-        <v>0</v>
-      </c>
-      <c r="K1002" s="1" t="s">
+      <c r="K1002">
+        <v>0</v>
+      </c>
+      <c r="L1002" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L1002">
-        <v>0</v>
-      </c>
       <c r="M1002">
         <v>0</v>
       </c>
       <c r="N1002">
         <v>0</v>
       </c>
-      <c r="O1002" t="s">
+      <c r="O1002">
+        <v>0</v>
+      </c>
+      <c r="P1002" t="s">
         <v>62</v>
       </c>
-      <c r="P1002">
-        <v>0</v>
-      </c>
-      <c r="Q1002" t="s">
+      <c r="Q1002">
+        <v>0</v>
+      </c>
+      <c r="R1002" t="s">
         <v>62</v>
       </c>
-      <c r="S1002" s="3" t="s">
+      <c r="T1002" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="T1002" s="4">
-        <v>0</v>
-      </c>
-      <c r="U1002" s="3" t="s">
+      <c r="U1002" s="4">
+        <v>0</v>
+      </c>
+      <c r="V1002" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="V1002" s="4">
-        <v>0</v>
-      </c>
-      <c r="W1002" s="5" t="s">
+      <c r="W1002" s="4">
+        <v>0</v>
+      </c>
+      <c r="X1002" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="X1002" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y1002" s="5" t="s">
+      <c r="Y1002" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z1002" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="Z1002" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA1002" t="s">
+      <c r="AA1002" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB1002" t="s">
         <v>62</v>
       </c>
-      <c r="AB1002">
-        <v>0</v>
-      </c>
-      <c r="AC1002" t="s">
+      <c r="AC1002">
+        <v>0</v>
+      </c>
+      <c r="AD1002" t="s">
         <v>153</v>
       </c>
-      <c r="AE1002" t="s">
+      <c r="AF1002" t="s">
         <v>62</v>
       </c>
-      <c r="AF1002">
-        <v>0</v>
-      </c>
-      <c r="AG1002" t="s">
+      <c r="AG1002">
+        <v>0</v>
+      </c>
+      <c r="AH1002" t="s">
         <v>153</v>
       </c>
     </row>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3615968-93DC-40C6-B705-8ADD3F5FA494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D567376-C804-42D5-A436-A408D7371D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="363">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -1454,6 +1454,109 @@
   </si>
   <si>
     <t>enemyInformationMessageId</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="せいせい"&gt;静声&lt;/r&gt;に&lt;r="ねっ"&gt;熱&lt;/r&gt;する&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>俺の名は…と言いたいところだが、名前を破棄されたせいで思い出せないんだ。
+このメモを読んでいる君と同じ状況だろう。
+この迷宮で起こった出来事をここにメモする。
+俺の他に何人か迷宮を探索している人がいたが、そのうちの1人が長身でスーツ姿の肌が赤い化け物に捕まっちまった。
+俺はいち早く逃げたが、そいつがその後どうなったかは分からない。
+今隠れながらこの状況を整理しているが、あの化け物の特徴を俺なりに分析してみる。
+まず化け物に捕まった者についてだが、恐怖に耐えきれずパニックになって走ったり大きな音を立てていた。
+化け物に見つかった原因は恐らくそれだろう。
+また、一度だけ化け物の近くで俺はうっかりライトを点けてしまったが、眩しい光を検知できていないからか居場所がバレなかった。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Vein-Vain Wanderer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I'd love to tell you my name... but having had it discarded, I can no longer remember it.
+You, reading this note, are likely in the exact same situation.
+I will write down what happened in this labyrinth right here.
+There were a few others exploring the labyrinth besides me, but one of them was caught by a tall monster in a suit with red skin.
+I was the first to run, so I don't know what happened to them after that.
+Now I'm hiding and taking stock of the situation, analyzing the characteristics of that monster in my own way.
+First, regarding the person who was caught—they couldn't handle the fear, panicked, ran, and made a lot of noise.
+That was likely the reason they were spotted by the monster.
+Also, I once accidentally turned on my light near the creature, but because it couldn't detect the bright glare, my location wasn't exposed.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>我想说出我的名字……但因为名字被毁弃了，我已经想不起来了。
+读着这张纸条的你，大概也是同样的境遇吧。
+在此，我将这迷宫里发生的事记录下来。
+除了我之外，还有几个人也在探索这座迷宫，但其中一人被一个身穿西装、皮肤发红的高大怪物给抓住了。
+我第一时间逃跑了，所以不知道那个人之后怎么样了。
+现在我正躲着整理当下的状况，试着用我自己的方式分析一下那个怪物的特征。
+首先是关于那个被抓的人，他无法承受恐惧，陷入恐慌并疯狂逃跑、发出很大的噪音。
+被怪物发现的原因恐怕就是这个。
+另外，有一次我在怪物附近不小心点亮了手电筒，但也许是因为它无法感知强烈的光线，我的位置并没有暴露。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沉溺寂声之徘徊者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沉溺寂聲之徘徊者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>我想說出我的名字……但因為名字被毀棄了，我已经想不起來了。
+讀著這張紙條的你，大概也是同樣的境遇吧。
+在此，我將這迷宮裡發生的事記錄下來。
+除了我之外，還有幾個人也在探索這座迷宮，但其中一人被一個身穿西裝、皮膚發紅的高大怪物給抓住了。
+我第一時間逃跑了，所以不知道那個人之後怎麼樣了。
+現在我正躲著整理當下的狀況，試著用我自己方式分析一下那個怪物的特徵。
+首先是關於那個被抓的人，他無法承受恐懼，陷入恐慌並瘋狂逃跑、發出很大的噪音。
+被怪物發現的原因恐怕就是這個。
+另外，有一次我在怪物附近不小心點亮了手電筒，但也許是因為它無法感知強烈的光線，我的位置並沒有暴露。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Errante que Arde en Silencio</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Me gustaría decirte mi nombre... pero como me lo destruyeron, ya no puedo recordarlo.
+Tú, que estás leyendo esta nota, probablemente te encuentres en la misma situación.
+Voy a anotar aquí lo que ha sucedido en este laberinto.
+Había otras personas explorando el laberinto conmigo, pero una de ellas fue atrapada por un monstruo alto, con traje y de piel roja.
+Huí lo antes posible, así que no sé qué fue de esa persona después de eso.
+Ahora estoy escondido organizando la situación e intentando analizar las características de ese monstruo a mi manera.
+En cuanto a la persona que fue atrapada, no pudo soportar el miedo, entró en pánico, corrió e hizo mucho ruido.
+Esa fue probablemente la razón por la que el monstruo la descubrió.
+Además, una vez encendí mi linterna por accidente cerca del monstruo, pero como no pareció detectar la luz deslumbrante, mi ubicación no quedó al descubierto.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Canto-Pranto, o Errante</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gostaria de dizer o meu nome... mas, como ele foi destruído, não consigo mais me lembrar.
+Você, que está lendo este bilhete, provavelmente está na mesma situação.
+Vou anotar aqui o que aconteceu neste labirinto.
+Havia outras pessoas explorando o labirinto além de mim, mas uma delas foi pega por um monstro alto, de terno e pele vermelha.
+Fui o primeiro a fugir, então não sei o que aconteceu com ela depois disso.
+Agora estou escondido tentando organizar a situação e analisando as características daquele monstro à minha maneira.
+Em relação à pessoa que foi pega, ela não aguentou o medo, entrou em pânico, saiu correndo e fez muito barulho.
+Essa provavelmente foi a razão pela qual o monstro a encontrou.
+Além disso, uma vez acendi minha lanterna sem querer perto dele, mas, talvez por ele não conseguir detectar a luz forte, minha localização não foi descoberta.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>静声に熱する彷徨う者の情報</t>
+    <rPh sb="11" eb="13">
+      <t>ジョウホウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4613,10 +4716,113 @@
       <c r="A29">
         <v>27</v>
       </c>
-    </row>
-    <row r="30" spans="1:36">
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" spans="1:36" ht="409.6">
       <c r="A30">
         <v>28</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="K30" s="1">
+        <v>10</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="M30" s="1">
+        <v>10</v>
+      </c>
+      <c r="N30" s="1">
+        <v>1</v>
+      </c>
+      <c r="O30" s="1">
+        <v>0</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>10</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="S30" s="1">
+        <v>10</v>
+      </c>
+      <c r="T30" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="U30" s="1">
+        <v>10</v>
+      </c>
+      <c r="V30" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="W30" s="1">
+        <v>10</v>
+      </c>
+      <c r="X30" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="Y30" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z30" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA30" s="1">
+        <v>10</v>
+      </c>
+      <c r="AB30" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="AC30" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD30" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AE30" s="1">
+        <v>10</v>
+      </c>
+      <c r="AF30" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AG30" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH30" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="AI30" s="1">
+        <v>10</v>
+      </c>
+      <c r="AJ30" s="1" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="31" spans="1:36">

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D567376-C804-42D5-A436-A408D7371D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E705AD42-CB9C-4471-9148-59829DDA0D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="364">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -1555,6 +1555,19 @@
   <si>
     <t>静声に熱する彷徨う者の情報</t>
     <rPh sb="11" eb="13">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デモ版用静声に熱する彷徨う者の情報</t>
+    <rPh sb="2" eb="3">
+      <t>バン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
       <t>ジョウホウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -4712,11 +4725,112 @@
         <v>282</v>
       </c>
     </row>
-    <row r="29" spans="1:36">
+    <row r="29" spans="1:36" ht="409.6">
       <c r="A29">
         <v>27</v>
       </c>
-      <c r="K29" s="1"/>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="K29" s="1">
+        <v>10</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="M29" s="1">
+        <v>10</v>
+      </c>
+      <c r="N29" s="1">
+        <v>1</v>
+      </c>
+      <c r="O29" s="1">
+        <v>0</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>10</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="S29" s="1">
+        <v>10</v>
+      </c>
+      <c r="T29" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="U29" s="1">
+        <v>10</v>
+      </c>
+      <c r="V29" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="W29" s="1">
+        <v>10</v>
+      </c>
+      <c r="X29" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="Y29" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z29" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA29" s="1">
+        <v>10</v>
+      </c>
+      <c r="AB29" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="AC29" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD29" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AE29" s="1">
+        <v>10</v>
+      </c>
+      <c r="AF29" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AG29" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH29" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="AI29" s="1">
+        <v>10</v>
+      </c>
+      <c r="AJ29" s="1" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="30" spans="1:36" ht="409.6">
       <c r="A30">
